--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2033.06</v>
+        <v>1624.92</v>
       </c>
       <c r="E2" t="n">
         <v>407.43</v>
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1506.42</v>
+        <v>1207.79</v>
       </c>
       <c r="E3" t="n">
         <v>297.67</v>
@@ -534,10 +534,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1402.32</v>
+        <v>1118.68</v>
       </c>
       <c r="E4" t="n">
         <v>281.52</v>
@@ -563,10 +563,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1298.3</v>
+        <v>1037.24</v>
       </c>
       <c r="E5" t="n">
         <v>259.68</v>
@@ -592,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1164.88</v>
+        <v>929.6</v>
       </c>
       <c r="E6" t="n">
         <v>232.1</v>
@@ -621,10 +621,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1112.19</v>
+        <v>889.6</v>
       </c>
       <c r="E7" t="n">
         <v>223.6</v>
@@ -650,10 +650,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1064.11</v>
+        <v>849.98</v>
       </c>
       <c r="E8" t="n">
         <v>212.59</v>
@@ -679,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1003.81</v>
+        <v>802.84</v>
       </c>
       <c r="E9" t="n">
         <v>201.81</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>884.84</v>
+        <v>710.53</v>
       </c>
       <c r="E10" t="n">
         <v>179.38</v>
@@ -737,10 +737,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>713.04</v>
+        <v>571.5</v>
       </c>
       <c r="E11" t="n">
         <v>144.53</v>
@@ -759,7 +759,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -769,10 +769,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>10.05</v>
+        <v>4.88</v>
       </c>
       <c r="E12" t="n">
-        <v>2.71</v>
+        <v>2.81</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>7.49</v>
+        <v>4.35</v>
       </c>
       <c r="E13" t="n">
-        <v>7.49</v>
+        <v>4.35</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,20 +817,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>6.77</v>
+        <v>3.72</v>
       </c>
       <c r="E14" t="n">
-        <v>3.01</v>
+        <v>3.72</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4.88</v>
+        <v>3.67</v>
       </c>
       <c r="E15" t="n">
-        <v>2.81</v>
+        <v>3.67</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4.66</v>
+        <v>3.33</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.05</v>
+        <v>3.33</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -897,14 +897,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.35</v>
+        <v>3.2</v>
       </c>
       <c r="E17" t="n">
-        <v>4.35</v>
+        <v>3.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.67</v>
+        <v>3.01</v>
       </c>
       <c r="E18" t="n">
-        <v>3.67</v>
+        <v>3.01</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="E19" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2</v>
+        <v>-2.47</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>EVIOSYS PACKAGING SIEM CI (SEMC)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.11</v>
+        <v>4.33</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EVIOSYS PACKAGING SIEM CI (SEMC)</t>
+          <t>BIIC BN (BICB)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.18</v>
+        <v>-0.8</v>
       </c>
       <c r="E25" t="n">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BIIC BN (BICB)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8</v>
+        <v>-1.01</v>
       </c>
       <c r="E26" t="n">
-        <v>2.45</v>
+        <v>-4.05</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.04</v>
+        <v>-1.94</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.47</v>
+        <v>-1.94</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,14 +1216,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1233,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.94</v>
+        <v>-2</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.94</v>
+        <v>-2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,20 +1252,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-2</v>
+        <v>-2.17</v>
       </c>
       <c r="E29" t="n">
-        <v>-2</v>
+        <v>2.89</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,27 +1274,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.17</v>
+        <v>-2.63</v>
       </c>
       <c r="E30" t="n">
-        <v>2.89</v>
+        <v>-2.65</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,20 +1310,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.44</v>
+        <v>-2.88</v>
       </c>
       <c r="E31" t="n">
-        <v>3.72</v>
+        <v>-2.88</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.63</v>
+        <v>-4.12</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.65</v>
+        <v>-4.12</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,27 +1361,27 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.88</v>
+        <v>-4.79</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.88</v>
+        <v>-1.79</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-4.12</v>
+        <v>-5.41</v>
       </c>
       <c r="E34" t="n">
-        <v>-4.12</v>
+        <v>-5.41</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,20 +1426,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-4.79</v>
+        <v>-6.11</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.79</v>
+        <v>-6.11</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,116 +1455,58 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>-5.04</v>
+        <v>-10.37</v>
       </c>
       <c r="E36" t="n">
-        <v>-5.04</v>
+        <v>-1.64</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>🟡 Observer</t>
+          <t>🔴 Vente</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>⚠️ Risque de décrochage</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>-10.37</v>
+        <v>-11.87</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.64</v>
+        <v>3.04</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>🔴 Vente</t>
+          <t>🟡 Observer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>⚠️ Risque de décrochage</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>SOGB CI (SOGC)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-12.91</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-5.41</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SAPH CI (SPHC)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-19.36</v>
-      </c>
-      <c r="E39" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>🔴 Vente</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>⚠️ Risque de décrochage</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1543,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>333612.73</v>
+        <v>65573.38</v>
       </c>
     </row>
     <row r="3">
@@ -1611,7 +1553,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>103921.59</v>
+        <v>25994.77</v>
       </c>
     </row>
     <row r="4">
@@ -1621,7 +1563,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79614.85000000001</v>
+        <v>20678.55</v>
       </c>
     </row>
     <row r="5">
@@ -1631,7 +1573,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60080.07</v>
+        <v>16567.61</v>
       </c>
     </row>
     <row r="6">
@@ -1641,7 +1583,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40830.49</v>
+        <v>12107.85</v>
       </c>
     </row>
     <row r="7">
@@ -1651,7 +1593,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34751.84</v>
+        <v>10703.76</v>
       </c>
     </row>
     <row r="8">
@@ -1661,7 +1603,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29854.2</v>
+        <v>9435.6</v>
       </c>
     </row>
     <row r="9">
@@ -1671,7 +1613,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24509.83</v>
+        <v>8076.84</v>
       </c>
     </row>
     <row r="10">
@@ -1681,7 +1623,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16196.44</v>
+        <v>5840.88</v>
       </c>
     </row>
     <row r="11">
@@ -1691,7 +1633,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8304.059999999999</v>
+        <v>3379.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1624.92</v>
+        <v>1626.51</v>
       </c>
       <c r="E2" t="n">
-        <v>407.43</v>
+        <v>407.68</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1207.79</v>
+        <v>1196.65</v>
       </c>
       <c r="E3" t="n">
-        <v>297.67</v>
+        <v>294.35</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1118.68</v>
+        <v>1121.55</v>
       </c>
       <c r="E4" t="n">
-        <v>281.52</v>
+        <v>281.01</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1037.24</v>
+        <v>1037.27</v>
       </c>
       <c r="E5" t="n">
-        <v>259.68</v>
+        <v>259.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>929.6</v>
+        <v>930.28</v>
       </c>
       <c r="E6" t="n">
-        <v>232.1</v>
+        <v>232.66</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>889.6</v>
+        <v>891.97</v>
       </c>
       <c r="E7" t="n">
-        <v>223.6</v>
+        <v>223.77</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>849.98</v>
+        <v>848.97</v>
       </c>
       <c r="E8" t="n">
-        <v>212.59</v>
+        <v>214.07</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>802.84</v>
+        <v>805.29</v>
       </c>
       <c r="E9" t="n">
-        <v>201.81</v>
+        <v>202.03</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>710.53</v>
+        <v>718.64</v>
       </c>
       <c r="E10" t="n">
-        <v>179.38</v>
+        <v>183.15</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>571.5</v>
+        <v>575.17</v>
       </c>
       <c r="E11" t="n">
-        <v>144.53</v>
+        <v>144.61</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -769,10 +769,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>4.88</v>
+        <v>11.16</v>
       </c>
       <c r="E12" t="n">
-        <v>2.81</v>
+        <v>7.49</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>4.35</v>
+        <v>7.45</v>
       </c>
       <c r="E13" t="n">
-        <v>4.35</v>
+        <v>7.45</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,20 +817,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3.72</v>
+        <v>4.88</v>
       </c>
       <c r="E14" t="n">
-        <v>3.72</v>
+        <v>2.81</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="E15" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.33</v>
+        <v>3.61</v>
       </c>
       <c r="E16" t="n">
-        <v>3.33</v>
+        <v>3.61</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="E19" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.47</v>
+        <v>2.71</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1049,20 +1049,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOLIBRA CI (SLBC)</t>
+          <t>EVIOSYS PACKAGING SIEM CI (SEMC)</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
       <c r="E22" t="n">
-        <v>1.34</v>
+        <v>-2.56</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1071,27 +1071,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>1.29</v>
+        <v>0.82</v>
       </c>
       <c r="E23" t="n">
-        <v>1.29</v>
+        <v>3.45</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,14 +1100,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EVIOSYS PACKAGING SIEM CI (SEMC)</t>
+          <t>BIIC BN (BICB)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.18</v>
+        <v>-0.8</v>
       </c>
       <c r="E24" t="n">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BIIC BN (BICB)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8</v>
+        <v>-1.28</v>
       </c>
       <c r="E25" t="n">
-        <v>2.45</v>
+        <v>-5.63</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.01</v>
+        <v>-1.94</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.05</v>
+        <v>-1.94</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,14 +1187,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.94</v>
+        <v>-2</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.94</v>
+        <v>-2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2</v>
+        <v>-2.17</v>
       </c>
       <c r="E28" t="n">
-        <v>-2</v>
+        <v>2.89</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,27 +1245,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.17</v>
+        <v>-2.47</v>
       </c>
       <c r="E29" t="n">
-        <v>2.89</v>
+        <v>-2.47</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,27 +1274,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.63</v>
+        <v>-2.88</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.65</v>
+        <v>-2.88</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,14 +1303,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>BANK OF AFRICA BF (BOABF)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.88</v>
+        <v>-3.23</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.88</v>
+        <v>-3.23</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-4.12</v>
+        <v>-4.05</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.12</v>
+        <v>-4.05</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,20 +1368,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-4.79</v>
+        <v>-4.12</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.79</v>
+        <v>-4.12</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,20 +1397,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>-5.41</v>
+        <v>-4.79</v>
       </c>
       <c r="E34" t="n">
-        <v>-5.41</v>
+        <v>-1.79</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,85 +1426,56 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>-6.11</v>
+        <v>-6.78</v>
       </c>
       <c r="E35" t="n">
-        <v>-6.11</v>
+        <v>-3.7</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>🟡 Observer</t>
+          <t>🔴 Vente</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>⚠️ Risque de décrochage</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>-10.37</v>
+        <v>-6.83</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.64</v>
+        <v>-2.41</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>🔴 Vente</t>
+          <t>🟡 Observer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
-        <is>
-          <t>⚠️ Risque de décrochage</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>SAPH CI (SPHC)</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-11.87</v>
-      </c>
-      <c r="E37" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
         <is>
           <t>👀 À surveiller</t>
         </is>
@@ -1543,7 +1514,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65573.38</v>
+        <v>65779.71000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1553,7 +1524,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25994.77</v>
+        <v>25277.87</v>
       </c>
     </row>
     <row r="4">
@@ -1563,7 +1534,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20678.55</v>
+        <v>20836.26</v>
       </c>
     </row>
     <row r="5">
@@ -1573,7 +1544,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16567.61</v>
+        <v>16569</v>
       </c>
     </row>
     <row r="6">
@@ -1583,7 +1554,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12107.85</v>
+        <v>12132.86</v>
       </c>
     </row>
     <row r="7">
@@ -1593,7 +1564,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10703.76</v>
+        <v>10783.42</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1574,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9435.6</v>
+        <v>9405.040000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1613,7 +1584,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8076.84</v>
+        <v>8143.71</v>
       </c>
     </row>
     <row r="10">
@@ -1623,7 +1594,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5840.88</v>
+        <v>6016.06</v>
       </c>
     </row>
     <row r="11">
@@ -1633,7 +1604,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3379.36</v>
+        <v>3432.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1626.51</v>
+        <v>1220.32</v>
       </c>
       <c r="E2" t="n">
         <v>407.68</v>
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1196.65</v>
+        <v>1179.34</v>
       </c>
       <c r="E3" t="n">
-        <v>294.35</v>
+        <v>290.53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1121.55</v>
+        <v>1034.63</v>
       </c>
       <c r="E4" t="n">
-        <v>281.01</v>
+        <v>257.16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1037.27</v>
+        <v>925.9299999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>259.8</v>
+        <v>227.44</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>930.28</v>
+        <v>852.27</v>
       </c>
       <c r="E6" t="n">
-        <v>232.66</v>
+        <v>213.93</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,20 +614,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>891.97</v>
+        <v>842.63</v>
       </c>
       <c r="E7" t="n">
-        <v>223.77</v>
+        <v>281.01</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>848.97</v>
+        <v>805.25</v>
       </c>
       <c r="E8" t="n">
-        <v>214.07</v>
+        <v>200.55</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>805.29</v>
+        <v>728.28</v>
       </c>
       <c r="E9" t="n">
-        <v>202.03</v>
+        <v>187.18</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>718.64</v>
+        <v>669.87</v>
       </c>
       <c r="E10" t="n">
-        <v>183.15</v>
+        <v>223.77</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>575.17</v>
+        <v>577.77</v>
       </c>
       <c r="E11" t="n">
-        <v>144.61</v>
+        <v>144.62</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,20 +759,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>BRVM-PRINCIPAL  (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.16</v>
+        <v>405.35</v>
       </c>
       <c r="E12" t="n">
-        <v>7.49</v>
+        <v>405.35</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,20 +788,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.45</v>
+        <v>278.85</v>
       </c>
       <c r="E13" t="n">
-        <v>7.45</v>
+        <v>278.85</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,20 +817,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.88</v>
+        <v>222.62</v>
       </c>
       <c r="E14" t="n">
-        <v>2.81</v>
+        <v>222.62</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3.72</v>
+        <v>13.65</v>
       </c>
       <c r="E15" t="n">
-        <v>3.72</v>
+        <v>6.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.61</v>
+        <v>7.49</v>
       </c>
       <c r="E16" t="n">
-        <v>3.61</v>
+        <v>7.49</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2</v>
+        <v>4.87</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2</v>
+        <v>-3.34</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -926,27 +926,27 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.01</v>
+        <v>4.44</v>
       </c>
       <c r="E18" t="n">
-        <v>3.01</v>
+        <v>6.44</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -955,14 +955,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2.83</v>
+        <v>3.61</v>
       </c>
       <c r="E19" t="n">
-        <v>2.83</v>
+        <v>3.61</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="E20" t="n">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="E21" t="n">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,20 +1049,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EVIOSYS PACKAGING SIEM CI (SEMC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1.77</v>
+        <v>2.81</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.56</v>
+        <v>2.81</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1071,27 +1071,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.82</v>
+        <v>2.71</v>
       </c>
       <c r="E23" t="n">
-        <v>3.45</v>
+        <v>2.71</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,10 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8</v>
+        <v>2.45</v>
       </c>
       <c r="E24" t="n">
         <v>2.45</v>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.28</v>
+        <v>2.25</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.63</v>
+        <v>2.25</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,27 +1158,27 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.94</v>
+        <v>1.24</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.94</v>
+        <v>1.24</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-2</v>
+        <v>1.23</v>
       </c>
       <c r="E27" t="n">
-        <v>-2</v>
+        <v>1.23</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1233,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.17</v>
+        <v>0.63</v>
       </c>
       <c r="E28" t="n">
-        <v>2.89</v>
+        <v>-2.41</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,20 +1252,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.47</v>
+        <v>0.27</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.47</v>
+        <v>1.55</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.88</v>
+        <v>-1.94</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.88</v>
+        <v>-1.94</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,20 +1310,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
+          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.23</v>
+        <v>-2.17</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.23</v>
+        <v>2.89</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,14 +1332,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-4.05</v>
+        <v>-2.47</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.05</v>
+        <v>-2.47</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>EVIOSYS PACKAGING SIEM CI (SEMC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-4.12</v>
+        <v>-2.56</v>
       </c>
       <c r="E33" t="n">
-        <v>-4.12</v>
+        <v>-2.56</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,20 +1397,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-4.79</v>
+        <v>-2.88</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.79</v>
+        <v>-2.88</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,58 +1426,174 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>BANK OF AFRICA BF (BOABF)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-6.78</v>
+        <v>-3.23</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.7</v>
+        <v>-3.23</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>🔴 Vente</t>
+          <t>🟡 Observer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>⚠️ Risque de décrochage</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-3.59</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>👀 À surveiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BANK OF AFRICA NG (BOAN)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CIE CI (CIEC)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SUCRIVOIRE (SCRC)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
         <v>2</v>
       </c>
-      <c r="D36" t="n">
-        <v>-6.83</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-2.41</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
+      <c r="D39" t="n">
+        <v>-7.74</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-5.95</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BICI CI (BICC)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-10.07</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-5.95</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1510,101 +1626,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65779.71000000001</v>
+        <v>24200.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25277.87</v>
+        <v>16446.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20836.26</v>
+        <v>12914.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16569</v>
+        <v>11972.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12132.86</v>
+        <v>9506.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10783.42</v>
+        <v>8142.61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9405.040000000001</v>
+        <v>6228.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8143.71</v>
+        <v>5425.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6016.06</v>
+        <v>3470.31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3432.36</v>
+        <v>3278.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,20 +469,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1220.32</v>
+        <v>1165.74</v>
       </c>
       <c r="E2" t="n">
-        <v>407.68</v>
+        <v>283.19</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1179.34</v>
+        <v>1033.91</v>
       </c>
       <c r="E3" t="n">
-        <v>290.53</v>
+        <v>257.27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1034.63</v>
+        <v>922.89</v>
       </c>
       <c r="E4" t="n">
-        <v>257.16</v>
+        <v>230.69</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>925.9299999999999</v>
+        <v>852.39</v>
       </c>
       <c r="E5" t="n">
-        <v>227.44</v>
+        <v>211.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,20 +585,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>852.27</v>
+        <v>834.89</v>
       </c>
       <c r="E6" t="n">
-        <v>213.93</v>
+        <v>272.36</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,20 +614,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>842.63</v>
+        <v>815.11</v>
       </c>
       <c r="E7" t="n">
-        <v>281.01</v>
+        <v>407.68</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>805.25</v>
+        <v>804.95</v>
       </c>
       <c r="E8" t="n">
-        <v>200.55</v>
+        <v>200.56</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>728.28</v>
+        <v>736.6799999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>187.18</v>
+        <v>186.97</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>669.87</v>
+        <v>668.63</v>
       </c>
       <c r="E10" t="n">
-        <v>223.77</v>
+        <v>221.26</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>577.77</v>
+        <v>577.17</v>
       </c>
       <c r="E11" t="n">
-        <v>144.62</v>
+        <v>143.41</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>278.85</v>
+        <v>401.17</v>
       </c>
       <c r="E13" t="n">
-        <v>278.85</v>
+        <v>401.17</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>222.62</v>
+        <v>278.85</v>
       </c>
       <c r="E14" t="n">
-        <v>222.62</v>
+        <v>278.85</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>13.65</v>
+        <v>222.62</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2</v>
+        <v>222.62</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.49</v>
+        <v>13.65</v>
       </c>
       <c r="E16" t="n">
-        <v>7.49</v>
+        <v>6.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.87</v>
+        <v>3.67</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.34</v>
+        <v>3.67</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -926,27 +926,27 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4.44</v>
+        <v>3.61</v>
       </c>
       <c r="E18" t="n">
-        <v>6.44</v>
+        <v>3.61</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -955,27 +955,27 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.61</v>
+        <v>2.95</v>
       </c>
       <c r="E19" t="n">
-        <v>3.61</v>
+        <v>-3.49</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,14 +984,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="E21" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="E22" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1088,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="E23" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1233,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.41</v>
+        <v>2.83</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,20 +1252,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.27</v>
+        <v>0.63</v>
       </c>
       <c r="E29" t="n">
-        <v>1.55</v>
+        <v>-2.41</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.94</v>
+        <v>0.27</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.94</v>
+        <v>1.55</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,14 +1303,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.17</v>
+        <v>0.02</v>
       </c>
       <c r="E31" t="n">
-        <v>2.89</v>
+        <v>-7.47</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.47</v>
+        <v>-2.54</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.47</v>
+        <v>-3.34</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
@@ -1426,20 +1426,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-3.23</v>
+        <v>-3.86</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.23</v>
+        <v>2.09</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1448,27 +1448,27 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-3.59</v>
+        <v>-3.86</v>
       </c>
       <c r="E36" t="n">
-        <v>-4.23</v>
+        <v>-3.86</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1477,14 +1477,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>SITAB CI (STBC)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1494,10 +1494,10 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-3.86</v>
+        <v>-4.57</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.86</v>
+        <v>-4.57</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1513,20 +1513,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>BANK OF AFRICA BF (BOABF)</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>-4.05</v>
+        <v>-7.29</v>
       </c>
       <c r="E38" t="n">
-        <v>-4.05</v>
+        <v>-4.06</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1542,20 +1542,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-7.74</v>
+        <v>-7.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-5.95</v>
+        <v>-7.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1581,7 +1581,7 @@
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>-10.07</v>
+        <v>-7.74</v>
       </c>
       <c r="E40" t="n">
         <v>-5.95</v>
@@ -1594,6 +1594,35 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SAFCA CI (SAFC)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-9.57</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>🔴 Vente</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>⚠️ Risque de décrochage</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1659,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24200.76</v>
+        <v>23367.85</v>
       </c>
     </row>
     <row r="3">
@@ -1640,87 +1669,87 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16446.69</v>
+        <v>16413.41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12914.82</v>
+        <v>11862.51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11972.48</v>
+        <v>9509.709999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9506.02</v>
+        <v>8134.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8142.61</v>
+        <v>6419.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6228.49</v>
+        <v>5312.73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5425.25</v>
+        <v>3461.53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3470.31</v>
+        <v>3265.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3278.9</v>
+        <v>2476.12</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1165.74</v>
+        <v>1146.93</v>
       </c>
       <c r="E2" t="n">
-        <v>283.19</v>
+        <v>278.86</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1033.91</v>
+        <v>1029.17</v>
       </c>
       <c r="E3" t="n">
-        <v>257.27</v>
+        <v>254.94</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>922.89</v>
+        <v>916.85</v>
       </c>
       <c r="E4" t="n">
-        <v>230.69</v>
+        <v>226.06</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>852.39</v>
+        <v>847.87</v>
       </c>
       <c r="E5" t="n">
-        <v>211.8</v>
+        <v>208.07</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,20 +585,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>834.89</v>
+        <v>802.5599999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>272.36</v>
+        <v>199.42</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -624,10 +624,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>815.11</v>
+        <v>801.3200000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>407.68</v>
+        <v>400.15</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>804.95</v>
+        <v>740.46</v>
       </c>
       <c r="E8" t="n">
-        <v>200.56</v>
+        <v>183.16</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>736.6799999999999</v>
+        <v>576.42</v>
       </c>
       <c r="E9" t="n">
-        <v>186.97</v>
+        <v>143.78</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>668.63</v>
+        <v>553.37</v>
       </c>
       <c r="E10" t="n">
-        <v>221.26</v>
+        <v>272.36</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -730,20 +730,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>577.17</v>
+        <v>445.03</v>
       </c>
       <c r="E11" t="n">
-        <v>143.41</v>
+        <v>221.26</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL  (**)</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>405.35</v>
+        <v>407.68</v>
       </c>
       <c r="E12" t="n">
-        <v>405.35</v>
+        <v>407.68</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM-PRINCIPAL  (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>401.17</v>
+        <v>405.35</v>
       </c>
       <c r="E13" t="n">
-        <v>401.17</v>
+        <v>405.35</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>222.62</v>
+        <v>277.42</v>
       </c>
       <c r="E15" t="n">
-        <v>222.62</v>
+        <v>277.42</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>13.65</v>
+        <v>222.62</v>
       </c>
       <c r="E16" t="n">
-        <v>6.2</v>
+        <v>222.62</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.67</v>
+        <v>220.71</v>
       </c>
       <c r="E17" t="n">
-        <v>3.67</v>
+        <v>220.71</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,49 +933,49 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.61</v>
+        <v>15.36</v>
       </c>
       <c r="E18" t="n">
-        <v>3.61</v>
+        <v>1.71</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟡 Observer</t>
+          <t>🟢 Achat</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>✅ Renforcer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2.95</v>
+        <v>3.67</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.49</v>
+        <v>3.67</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,14 +984,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2.91</v>
+        <v>3.61</v>
       </c>
       <c r="E20" t="n">
-        <v>2.91</v>
+        <v>3.61</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="E21" t="n">
-        <v>2.89</v>
+        <v>-3.49</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,14 +1042,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="E22" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BIIC BN (BICB)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="E24" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>2.25</v>
+        <v>1.38</v>
       </c>
       <c r="E25" t="n">
-        <v>2.25</v>
+        <v>1.38</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SITAB CI (STBC)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1233,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.89</v>
+        <v>0.55</v>
       </c>
       <c r="E28" t="n">
-        <v>2.83</v>
+        <v>5.12</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.63</v>
+        <v>0.02</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.41</v>
+        <v>-7.47</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1.55</v>
+        <v>7.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.02</v>
+        <v>-0.25</v>
       </c>
       <c r="E31" t="n">
-        <v>-7.47</v>
+        <v>-3.08</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.54</v>
+        <v>-0.97</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.34</v>
+        <v>-3.8</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EVIOSYS PACKAGING SIEM CI (SEMC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.56</v>
+        <v>-2.41</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.56</v>
+        <v>-2.41</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>EVIOSYS PACKAGING SIEM CI (SEMC)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-2.88</v>
+        <v>-2.56</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.88</v>
+        <v>-2.56</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,11 +1426,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -1439,7 +1439,7 @@
         <v>-3.86</v>
       </c>
       <c r="E35" t="n">
-        <v>2.09</v>
+        <v>-3.86</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1448,18 +1448,18 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1468,7 +1468,7 @@
         <v>-3.86</v>
       </c>
       <c r="E36" t="n">
-        <v>-3.86</v>
+        <v>2.09</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1477,14 +1477,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SITAB CI (STBC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1494,10 +1494,10 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-4.57</v>
+        <v>-3.9</v>
       </c>
       <c r="E37" t="n">
-        <v>-4.57</v>
+        <v>-3.9</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1513,20 +1513,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>-7.29</v>
+        <v>-4.08</v>
       </c>
       <c r="E38" t="n">
-        <v>-4.06</v>
+        <v>1.55</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1535,14 +1535,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1552,10 +1552,10 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-7.5</v>
+        <v>-5.95</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.5</v>
+        <v>-5.95</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1571,20 +1571,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>-7.74</v>
+        <v>-6.99</v>
       </c>
       <c r="E40" t="n">
-        <v>-5.95</v>
+        <v>-7.1</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1593,34 +1593,63 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>BANK OF AFRICA BF (BOABF)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="n">
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
         <v>3</v>
       </c>
-      <c r="D41" t="n">
-        <v>-9.57</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-4.23</v>
-      </c>
-      <c r="F41" t="inlineStr">
+      <c r="D42" t="n">
+        <v>-10.94</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>🔴 Vente</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>⚠️ Risque de décrochage</t>
         </is>
@@ -1659,7 +1688,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23367.85</v>
+        <v>22257.81</v>
       </c>
     </row>
     <row r="3">
@@ -1669,7 +1698,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16413.41</v>
+        <v>16195.79</v>
       </c>
     </row>
     <row r="4">
@@ -1679,7 +1708,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11862.51</v>
+        <v>11644.94</v>
       </c>
     </row>
     <row r="5">
@@ -1689,7 +1718,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9509.709999999999</v>
+        <v>9370.76</v>
       </c>
     </row>
     <row r="6">
@@ -1699,7 +1728,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8134.39</v>
+        <v>8069.19</v>
       </c>
     </row>
     <row r="7">
@@ -1709,47 +1738,47 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6419.32</v>
+        <v>6507.53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5312.73</v>
+        <v>3450.61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3461.53</v>
+        <v>2406.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3265.9</v>
+        <v>1318.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2476.12</v>
+        <v>940.14</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,13 +476,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1146.93</v>
+        <v>1418.96</v>
       </c>
       <c r="E2" t="n">
-        <v>278.86</v>
+        <v>272.03</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1029.17</v>
+        <v>1283.78</v>
       </c>
       <c r="E3" t="n">
-        <v>254.94</v>
+        <v>254.61</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -534,13 +534,13 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>916.85</v>
+        <v>1137.62</v>
       </c>
       <c r="E4" t="n">
-        <v>226.06</v>
+        <v>220.77</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -563,13 +563,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>847.87</v>
+        <v>1052.92</v>
       </c>
       <c r="E5" t="n">
-        <v>208.07</v>
+        <v>205.05</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -592,13 +592,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>802.5599999999999</v>
+        <v>1005.57</v>
       </c>
       <c r="E6" t="n">
-        <v>199.42</v>
+        <v>203.01</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,20 +614,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>801.3200000000001</v>
+        <v>919.14</v>
       </c>
       <c r="E7" t="n">
-        <v>400.15</v>
+        <v>178.68</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>740.46</v>
+        <v>801.3200000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>183.16</v>
+        <v>400.15</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -679,13 +679,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>576.42</v>
+        <v>725.88</v>
       </c>
       <c r="E9" t="n">
-        <v>143.78</v>
+        <v>149.46</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
+          <t>BRVM-PRINCIPAL    (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>278.85</v>
+        <v>396.35</v>
       </c>
       <c r="E14" t="n">
-        <v>278.85</v>
+        <v>396.35</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>277.42</v>
+        <v>278.85</v>
       </c>
       <c r="E15" t="n">
-        <v>277.42</v>
+        <v>278.85</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>222.62</v>
+        <v>277.42</v>
       </c>
       <c r="E16" t="n">
-        <v>222.62</v>
+        <v>277.42</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE    (**)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>220.71</v>
+        <v>274.88</v>
       </c>
       <c r="E17" t="n">
-        <v>220.71</v>
+        <v>274.88</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,49 +933,49 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN    (**)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>15.36</v>
+        <v>222.98</v>
       </c>
       <c r="E18" t="n">
-        <v>1.71</v>
+        <v>222.98</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟢 Achat</t>
+          <t>🟡 Observer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>✅ Renforcer</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.67</v>
+        <v>222.62</v>
       </c>
       <c r="E19" t="n">
-        <v>3.67</v>
+        <v>222.62</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.61</v>
+        <v>220.71</v>
       </c>
       <c r="E20" t="n">
-        <v>3.61</v>
+        <v>220.71</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,36 +1020,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.95</v>
+        <v>7.98</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.49</v>
+        <v>-7.38</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟡 Observer</t>
+          <t>🟢 Achat</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>✅ Renforcer</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2.91</v>
+        <v>7.49</v>
       </c>
       <c r="E22" t="n">
-        <v>2.91</v>
+        <v>7.49</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2.64</v>
+        <v>5.28</v>
       </c>
       <c r="E23" t="n">
-        <v>2.64</v>
+        <v>2.37</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2.12</v>
+        <v>3.67</v>
       </c>
       <c r="E24" t="n">
-        <v>2.12</v>
+        <v>3.67</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1.38</v>
+        <v>3.61</v>
       </c>
       <c r="E25" t="n">
-        <v>1.38</v>
+        <v>3.61</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.24</v>
+        <v>2.98</v>
       </c>
       <c r="E26" t="n">
-        <v>1.24</v>
+        <v>3.95</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,14 +1187,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1204,10 +1204,10 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1.23</v>
+        <v>2.64</v>
       </c>
       <c r="E27" t="n">
-        <v>1.23</v>
+        <v>2.64</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SITAB CI (STBC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.55</v>
+        <v>2.12</v>
       </c>
       <c r="E28" t="n">
-        <v>5.12</v>
+        <v>2.12</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,27 +1245,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02</v>
+        <v>1.38</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.47</v>
+        <v>1.38</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,27 +1274,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="E30" t="n">
-        <v>7.5</v>
+        <v>1.24</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,14 +1303,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SITAB CI (STBC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.25</v>
+        <v>0.55</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.08</v>
+        <v>5.12</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.97</v>
+        <v>0.02</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.8</v>
+        <v>-7.47</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,20 +1368,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.41</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.41</v>
+        <v>7.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1390,27 +1390,27 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EVIOSYS PACKAGING SIEM CI (SEMC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-2.56</v>
+        <v>-0.25</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.56</v>
+        <v>-3.08</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1419,27 +1419,27 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-3.86</v>
+        <v>-2.13</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.86</v>
+        <v>-3.36</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1448,27 +1448,27 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-3.86</v>
+        <v>-2.41</v>
       </c>
       <c r="E36" t="n">
-        <v>2.09</v>
+        <v>-2.41</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1477,27 +1477,27 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-3.9</v>
+        <v>-2.5</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.9</v>
+        <v>1.36</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1506,27 +1506,27 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>EVIOSYS PACKAGING SIEM CI (SEMC)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>-4.08</v>
+        <v>-2.56</v>
       </c>
       <c r="E38" t="n">
-        <v>1.55</v>
+        <v>-2.56</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1535,14 +1535,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1552,10 +1552,10 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-5.95</v>
+        <v>-3.86</v>
       </c>
       <c r="E39" t="n">
-        <v>-5.95</v>
+        <v>-3.86</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1571,20 +1571,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>-6.99</v>
+        <v>-3.9</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.1</v>
+        <v>-3.9</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1593,27 +1593,27 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>-7.29</v>
+        <v>-3.91</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.06</v>
+        <v>-3.91</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1629,27 +1629,201 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-4.08</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>👀 À surveiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SODE CI (SDCC)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>👀 À surveiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SUCRIVOIRE (SCRC)</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-5.95</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-5.95</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SETAO CI (STAC)</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-6.57</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-6.57</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NEI-CEDA CI (NEIC)</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-6.99</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>👀 À surveiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BANK OF AFRICA BF (BOABF)</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="n">
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
         <v>3</v>
       </c>
-      <c r="D42" t="n">
-        <v>-10.94</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="F42" t="inlineStr">
+      <c r="D48" t="n">
+        <v>-7.94</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>🔴 Vente</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>⚠️ Risque de décrochage</t>
         </is>
@@ -1688,7 +1862,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22257.81</v>
+        <v>83077.74000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1698,7 +1872,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16195.79</v>
+        <v>57686.51</v>
       </c>
     </row>
     <row r="4">
@@ -1708,7 +1882,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11644.94</v>
+        <v>37574.25</v>
       </c>
     </row>
     <row r="5">
@@ -1718,7 +1892,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9370.76</v>
+        <v>28790.55</v>
       </c>
     </row>
     <row r="6">
@@ -1728,7 +1902,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8069.19</v>
+        <v>24653.45</v>
       </c>
     </row>
     <row r="7">
@@ -1738,7 +1912,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6507.53</v>
+        <v>18313.87</v>
       </c>
     </row>
     <row r="8">
@@ -1748,7 +1922,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3450.61</v>
+        <v>8757.35</v>
       </c>
     </row>
     <row r="9">

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1418.96</v>
+        <v>1124.61</v>
       </c>
       <c r="E2" t="n">
         <v>272.03</v>
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1283.78</v>
+        <v>1023.98</v>
       </c>
       <c r="E3" t="n">
         <v>254.61</v>
@@ -534,10 +534,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1137.62</v>
+        <v>904.96</v>
       </c>
       <c r="E4" t="n">
         <v>220.77</v>
@@ -563,10 +563,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1052.92</v>
+        <v>838.85</v>
       </c>
       <c r="E5" t="n">
         <v>205.05</v>
@@ -592,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1005.57</v>
+        <v>803.54</v>
       </c>
       <c r="E6" t="n">
         <v>203.01</v>
@@ -614,20 +614,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>919.14</v>
+        <v>801.3200000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>178.68</v>
+        <v>400.15</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>801.3200000000001</v>
+        <v>735.99</v>
       </c>
       <c r="E8" t="n">
-        <v>400.15</v>
+        <v>178.68</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -679,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>725.88</v>
+        <v>581.27</v>
       </c>
       <c r="E9" t="n">
         <v>149.46</v>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM-PRINCIPAL  (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>553.37</v>
+        <v>405.35</v>
       </c>
       <c r="E10" t="n">
-        <v>272.36</v>
+        <v>405.35</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -730,20 +730,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM-PRINCIPAL    (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>445.03</v>
+        <v>396.35</v>
       </c>
       <c r="E11" t="n">
-        <v>221.26</v>
+        <v>396.35</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>407.68</v>
+        <v>278.85</v>
       </c>
       <c r="E12" t="n">
-        <v>407.68</v>
+        <v>278.85</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL  (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>405.35</v>
+        <v>277.42</v>
       </c>
       <c r="E13" t="n">
-        <v>405.35</v>
+        <v>277.42</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL    (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE    (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>396.35</v>
+        <v>274.88</v>
       </c>
       <c r="E14" t="n">
-        <v>396.35</v>
+        <v>274.88</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>278.85</v>
+        <v>272.36</v>
       </c>
       <c r="E15" t="n">
-        <v>278.85</v>
+        <v>272.36</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN    (**)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>277.42</v>
+        <v>222.98</v>
       </c>
       <c r="E16" t="n">
-        <v>277.42</v>
+        <v>222.98</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE    (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>274.88</v>
+        <v>222.62</v>
       </c>
       <c r="E17" t="n">
-        <v>274.88</v>
+        <v>222.62</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN    (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="E18" t="n">
-        <v>222.98</v>
+        <v>221.26</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>222.62</v>
+        <v>220.71</v>
       </c>
       <c r="E19" t="n">
-        <v>222.62</v>
+        <v>220.71</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>220.71</v>
+        <v>7.49</v>
       </c>
       <c r="E20" t="n">
-        <v>220.71</v>
+        <v>7.49</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,36 +1020,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.98</v>
+        <v>5.28</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.38</v>
+        <v>2.37</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢 Achat</t>
+          <t>🟡 Observer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>✅ Renforcer</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>7.49</v>
+        <v>3.67</v>
       </c>
       <c r="E22" t="n">
-        <v>7.49</v>
+        <v>3.67</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>5.28</v>
+        <v>2.64</v>
       </c>
       <c r="E23" t="n">
-        <v>2.37</v>
+        <v>2.64</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>3.67</v>
+        <v>2.12</v>
       </c>
       <c r="E24" t="n">
-        <v>3.67</v>
+        <v>2.12</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>3.61</v>
+        <v>1.55</v>
       </c>
       <c r="E25" t="n">
-        <v>3.61</v>
+        <v>1.55</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>2.98</v>
+        <v>1.38</v>
       </c>
       <c r="E26" t="n">
-        <v>3.95</v>
+        <v>1.38</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,14 +1187,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1204,10 +1204,10 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>2.64</v>
+        <v>1.24</v>
       </c>
       <c r="E27" t="n">
-        <v>2.64</v>
+        <v>1.24</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>SITAB CI (STBC)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>2.12</v>
+        <v>0.55</v>
       </c>
       <c r="E28" t="n">
-        <v>2.12</v>
+        <v>5.12</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,27 +1245,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1.38</v>
+        <v>0.53</v>
       </c>
       <c r="E29" t="n">
-        <v>1.38</v>
+        <v>-7.38</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,27 +1274,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1.24</v>
+        <v>0.15</v>
       </c>
       <c r="E30" t="n">
-        <v>1.24</v>
+        <v>3.95</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,14 +1303,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SITAB CI (STBC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>5.12</v>
+        <v>7.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02</v>
+        <v>-0.25</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.47</v>
+        <v>-3.08</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>-2.13</v>
       </c>
       <c r="E33" t="n">
-        <v>7.5</v>
+        <v>-3.36</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,20 +1397,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.25</v>
+        <v>-2.5</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.08</v>
+        <v>1.36</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,20 +1426,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-2.13</v>
+        <v>-3.86</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.36</v>
+        <v>-3.86</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1448,14 +1448,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1465,10 +1465,10 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-2.41</v>
+        <v>-3.9</v>
       </c>
       <c r="E36" t="n">
-        <v>-2.41</v>
+        <v>-3.9</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1484,20 +1484,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-2.5</v>
+        <v>-3.91</v>
       </c>
       <c r="E37" t="n">
-        <v>1.36</v>
+        <v>-3.91</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1506,14 +1506,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EVIOSYS PACKAGING SIEM CI (SEMC)</t>
+          <t>BANK OF AFRICA BF (BOABF)</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1523,10 +1523,10 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>-2.56</v>
+        <v>-4.06</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.56</v>
+        <v>-4.06</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1542,20 +1542,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>-3.86</v>
+        <v>-4.24</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.86</v>
+        <v>3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1564,27 +1564,27 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>-3.9</v>
+        <v>-4.53</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.9</v>
+        <v>-7.48</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1593,14 +1593,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1610,10 +1610,10 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>-3.91</v>
+        <v>-5.95</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.91</v>
+        <v>-5.95</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1629,20 +1629,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>-4.08</v>
+        <v>-6.57</v>
       </c>
       <c r="E42" t="n">
-        <v>1.55</v>
+        <v>-6.57</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1651,27 +1651,27 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>-4.53</v>
+        <v>-7.47</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.48</v>
+        <v>-7.47</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1680,27 +1680,27 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>-5.95</v>
+        <v>-10.44</v>
       </c>
       <c r="E44" t="n">
-        <v>-5.95</v>
+        <v>-7.1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1710,122 +1710,6 @@
       <c r="G44" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>SETAO CI (STAC)</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="n">
-        <v>-6.57</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-6.57</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>NEI-CEDA CI (NEIC)</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="n">
-        <v>2</v>
-      </c>
-      <c r="D46" t="n">
-        <v>-6.99</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-7.29</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-4.06</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>SAFCA CI (SAFC)</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="n">
-        <v>3</v>
-      </c>
-      <c r="D48" t="n">
-        <v>-7.94</v>
-      </c>
-      <c r="E48" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>🔴 Vente</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>⚠️ Risque de décrochage</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1746,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83077.74000000001</v>
+        <v>20992.37</v>
       </c>
     </row>
     <row r="3">
@@ -1872,7 +1756,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57686.51</v>
+        <v>15960.73</v>
       </c>
     </row>
     <row r="4">
@@ -1882,7 +1766,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37574.25</v>
+        <v>11225.15</v>
       </c>
     </row>
     <row r="5">
@@ -1892,7 +1776,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28790.55</v>
+        <v>9098.76</v>
       </c>
     </row>
     <row r="6">
@@ -1902,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24653.45</v>
+        <v>8095.69</v>
       </c>
     </row>
     <row r="7">
@@ -1912,7 +1796,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18313.87</v>
+        <v>6403.22</v>
       </c>
     </row>
     <row r="8">
@@ -1922,7 +1806,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8757.35</v>
+        <v>3521.01</v>
       </c>
     </row>
     <row r="9">
@@ -1938,21 +1822,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM-PRINCIPAL  (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1318.73</v>
+        <v>405.35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM-PRINCIPAL    (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>940.14</v>
+        <v>396.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -479,10 +479,10 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1124.61</v>
+        <v>1114.8</v>
       </c>
       <c r="E2" t="n">
-        <v>272.03</v>
+        <v>280.72</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1023.98</v>
+        <v>1017.67</v>
       </c>
       <c r="E3" t="n">
-        <v>254.61</v>
+        <v>250.85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>904.96</v>
+        <v>890.67</v>
       </c>
       <c r="E4" t="n">
-        <v>220.77</v>
+        <v>213.15</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>838.85</v>
+        <v>827.22</v>
       </c>
       <c r="E5" t="n">
-        <v>205.05</v>
+        <v>202.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>803.54</v>
+        <v>802.49</v>
       </c>
       <c r="E6" t="n">
-        <v>203.01</v>
+        <v>199.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>735.99</v>
+        <v>727.78</v>
       </c>
       <c r="E8" t="n">
-        <v>178.68</v>
+        <v>178.97</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>581.27</v>
+        <v>582.39</v>
       </c>
       <c r="E9" t="n">
-        <v>149.46</v>
+        <v>145.74</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL  (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>405.35</v>
+        <v>545.3</v>
       </c>
       <c r="E10" t="n">
-        <v>405.35</v>
+        <v>272.94</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -730,20 +730,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL    (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>396.35</v>
+        <v>440.06</v>
       </c>
       <c r="E11" t="n">
-        <v>396.35</v>
+        <v>219.35</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
+          <t>BRVM-PRINCIPAL    (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>278.85</v>
+        <v>396.35</v>
       </c>
       <c r="E12" t="n">
-        <v>278.85</v>
+        <v>396.35</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>277.42</v>
+        <v>391.55</v>
       </c>
       <c r="E13" t="n">
-        <v>277.42</v>
+        <v>391.55</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE    (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>274.88</v>
+        <v>277.42</v>
       </c>
       <c r="E14" t="n">
-        <v>274.88</v>
+        <v>277.42</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE    (**)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>272.36</v>
+        <v>274.88</v>
       </c>
       <c r="E15" t="n">
-        <v>272.36</v>
+        <v>274.88</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>222.62</v>
+        <v>221.26</v>
       </c>
       <c r="E17" t="n">
-        <v>222.62</v>
+        <v>221.26</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,20 +933,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>221.26</v>
+        <v>7.49</v>
       </c>
       <c r="E18" t="n">
-        <v>221.26</v>
+        <v>7.49</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>220.71</v>
+        <v>5.57</v>
       </c>
       <c r="E19" t="n">
-        <v>220.71</v>
+        <v>3.45</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.49</v>
+        <v>5.28</v>
       </c>
       <c r="E20" t="n">
-        <v>7.49</v>
+        <v>2.37</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>5.28</v>
+        <v>4.19</v>
       </c>
       <c r="E21" t="n">
-        <v>2.37</v>
+        <v>4.19</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2.64</v>
+        <v>3.45</v>
       </c>
       <c r="E23" t="n">
-        <v>2.64</v>
+        <v>1.36</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2.12</v>
+        <v>2.64</v>
       </c>
       <c r="E24" t="n">
-        <v>2.12</v>
+        <v>2.64</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="E25" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>SITAB CI (STBC)</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.38</v>
+        <v>0.55</v>
       </c>
       <c r="E26" t="n">
-        <v>1.38</v>
+        <v>5.12</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,14 +1187,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1204,10 +1204,10 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1.24</v>
+        <v>0.51</v>
       </c>
       <c r="E27" t="n">
-        <v>1.24</v>
+        <v>0.51</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SITAB CI (STBC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="E28" t="n">
-        <v>5.12</v>
+        <v>0.51</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,27 +1245,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.53</v>
+        <v>0.15</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.38</v>
+        <v>3.95</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>3.95</v>
+        <v>7.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E31" t="n">
-        <v>7.5</v>
+        <v>-3.08</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.25</v>
+        <v>-0.96</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.08</v>
+        <v>4.71</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.13</v>
+        <v>-3.36</v>
       </c>
       <c r="E33" t="n">
         <v>-3.36</v>
@@ -1390,27 +1390,27 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-2.5</v>
+        <v>-3.9</v>
       </c>
       <c r="E34" t="n">
-        <v>1.36</v>
+        <v>-3.9</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1419,14 +1419,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-3.86</v>
+        <v>-3.91</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.86</v>
+        <v>-3.91</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>BANK OF AFRICA BF (BOABF)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1465,10 +1465,10 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-3.9</v>
+        <v>-4.06</v>
       </c>
       <c r="E36" t="n">
-        <v>-3.9</v>
+        <v>-4.06</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1494,10 +1494,10 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-3.91</v>
+        <v>-5.41</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.91</v>
+        <v>-5.41</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1523,10 +1523,10 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>-4.06</v>
+        <v>-6.67</v>
       </c>
       <c r="E38" t="n">
-        <v>-4.06</v>
+        <v>-6.67</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1542,20 +1542,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-4.24</v>
+        <v>-7.1</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>-7.1</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1564,27 +1564,27 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>-4.53</v>
+        <v>-7.38</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.48</v>
+        <v>-7.38</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1593,27 +1593,27 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>-5.95</v>
+        <v>-7.44</v>
       </c>
       <c r="E41" t="n">
-        <v>-5.95</v>
+        <v>-7.43</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1622,14 +1622,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1639,10 +1639,10 @@
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>-6.57</v>
+        <v>-7.47</v>
       </c>
       <c r="E42" t="n">
-        <v>-6.57</v>
+        <v>-7.47</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1658,20 +1658,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>-7.47</v>
+        <v>-10.97</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.47</v>
+        <v>-7.48</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1697,10 +1697,10 @@
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>-10.44</v>
+        <v>-14.04</v>
       </c>
       <c r="E44" t="n">
-        <v>-7.1</v>
+        <v>-7.47</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20992.37</v>
+        <v>20462.53</v>
       </c>
     </row>
     <row r="3">
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15960.73</v>
+        <v>15676.98</v>
       </c>
     </row>
     <row r="4">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11225.15</v>
+        <v>10730.9</v>
       </c>
     </row>
     <row r="5">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9098.76</v>
+        <v>8757.98</v>
       </c>
     </row>
     <row r="6">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8095.69</v>
+        <v>8067.06</v>
       </c>
     </row>
     <row r="7">
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6403.22</v>
+        <v>6217.3</v>
       </c>
     </row>
     <row r="8">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3521.01</v>
+        <v>3537.59</v>
       </c>
     </row>
     <row r="9">
@@ -1822,21 +1822,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL  (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>405.35</v>
+        <v>1288.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL    (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>396.35</v>
+        <v>924.1900000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1114.8</v>
+        <v>1096.62</v>
       </c>
       <c r="E2" t="n">
-        <v>280.72</v>
+        <v>265.01</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1017.67</v>
+        <v>1005.63</v>
       </c>
       <c r="E3" t="n">
-        <v>250.85</v>
+        <v>245.23</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>890.67</v>
+        <v>872.34</v>
       </c>
       <c r="E4" t="n">
-        <v>213.15</v>
+        <v>212.36</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>827.22</v>
+        <v>816.49</v>
       </c>
       <c r="E5" t="n">
-        <v>202.3</v>
+        <v>201.07</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>802.49</v>
+        <v>800.47</v>
       </c>
       <c r="E6" t="n">
-        <v>199.5</v>
+        <v>198.54</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -624,10 +624,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>801.3200000000001</v>
+        <v>771.3099999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>400.15</v>
+        <v>379.76</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>727.78</v>
+        <v>712.37</v>
       </c>
       <c r="E8" t="n">
-        <v>178.97</v>
+        <v>171.56</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>582.39</v>
+        <v>583.6900000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>145.74</v>
+        <v>144.71</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>545.3</v>
+        <v>543.13</v>
       </c>
       <c r="E10" t="n">
-        <v>272.94</v>
+        <v>270.19</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL    (**)</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>396.35</v>
+        <v>400.15</v>
       </c>
       <c r="E12" t="n">
-        <v>396.35</v>
+        <v>400.15</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM-PRINCIPAL    (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>391.55</v>
+        <v>396.35</v>
       </c>
       <c r="E13" t="n">
-        <v>391.55</v>
+        <v>396.35</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>221.26</v>
+        <v>215.81</v>
       </c>
       <c r="E17" t="n">
-        <v>221.26</v>
+        <v>215.81</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.49</v>
+        <v>7.5</v>
       </c>
       <c r="E18" t="n">
-        <v>7.49</v>
+        <v>7.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.57</v>
+        <v>7.49</v>
       </c>
       <c r="E19" t="n">
-        <v>3.45</v>
+        <v>7.49</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>5.28</v>
+        <v>5.57</v>
       </c>
       <c r="E20" t="n">
-        <v>2.37</v>
+        <v>3.45</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>SITAB CI (STBC)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4.19</v>
+        <v>5.12</v>
       </c>
       <c r="E21" t="n">
-        <v>4.19</v>
+        <v>5.12</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,11 +1049,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
         <v>3.67</v>
       </c>
       <c r="E22" t="n">
-        <v>3.67</v>
+        <v>1.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>3.45</v>
+        <v>1.38</v>
       </c>
       <c r="E23" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2.64</v>
+        <v>1.36</v>
       </c>
       <c r="E24" t="n">
-        <v>2.64</v>
+        <v>1.36</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1.38</v>
+        <v>0.85</v>
       </c>
       <c r="E25" t="n">
-        <v>1.38</v>
+        <v>0.85</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SITAB CI (STBC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="E26" t="n">
-        <v>5.12</v>
+        <v>0.13</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.51</v>
+        <v>0.15</v>
       </c>
       <c r="E28" t="n">
-        <v>0.51</v>
+        <v>3.95</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.15</v>
+        <v>-1.65</v>
       </c>
       <c r="E29" t="n">
-        <v>3.95</v>
+        <v>1.43</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>-2.06</v>
       </c>
       <c r="E30" t="n">
-        <v>7.5</v>
+        <v>-6.25</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,20 +1310,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.25</v>
+        <v>-3.36</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.08</v>
+        <v>-3.36</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.96</v>
+        <v>-3.9</v>
       </c>
       <c r="E32" t="n">
-        <v>4.71</v>
+        <v>-3.9</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,14 +1361,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-3.36</v>
+        <v>-3.91</v>
       </c>
       <c r="E33" t="n">
-        <v>-3.36</v>
+        <v>-3.91</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-3.9</v>
+        <v>-5.41</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.9</v>
+        <v>-5.41</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-3.91</v>
+        <v>-6.67</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.91</v>
+        <v>-6.67</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1465,10 +1465,10 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-4.06</v>
+        <v>-6.83</v>
       </c>
       <c r="E36" t="n">
-        <v>-4.06</v>
+        <v>-6.83</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1494,10 +1494,10 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-5.41</v>
+        <v>-7.1</v>
       </c>
       <c r="E37" t="n">
-        <v>-5.41</v>
+        <v>-7.1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1523,10 +1523,10 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>-6.67</v>
+        <v>-7.38</v>
       </c>
       <c r="E38" t="n">
-        <v>-6.67</v>
+        <v>-7.38</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1552,10 +1552,10 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-7.1</v>
+        <v>-7.48</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.1</v>
+        <v>-7.48</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>BIIC BN (BICB)</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1581,10 +1581,10 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>-7.38</v>
+        <v>-7.5</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.38</v>
+        <v>-7.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1600,20 +1600,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="E41" t="n">
         <v>-7.44</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-7.43</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1629,20 +1629,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>-7.47</v>
+        <v>-13.56</v>
       </c>
       <c r="E42" t="n">
-        <v>-7.47</v>
+        <v>0.48</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1651,65 +1651,36 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>-10.97</v>
+        <v>-14.16</v>
       </c>
       <c r="E43" t="n">
-        <v>-7.48</v>
+        <v>-6.72</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>🟡 Observer</t>
+          <t>🔴 Vente</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SETAO CI (STAC)</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-14.04</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-7.47</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
+          <t>⚠️ Risque de décrochage</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1717,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20462.53</v>
+        <v>19486.97</v>
       </c>
     </row>
     <row r="3">
@@ -1756,7 +1727,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15676.98</v>
+        <v>15145.3</v>
       </c>
     </row>
     <row r="4">
@@ -1766,7 +1737,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10730.9</v>
+        <v>10130.55</v>
       </c>
     </row>
     <row r="5">
@@ -1776,7 +1747,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8757.98</v>
+        <v>8453.15</v>
       </c>
     </row>
     <row r="6">
@@ -1786,7 +1757,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8067.06</v>
+        <v>8012.17</v>
       </c>
     </row>
     <row r="7">
@@ -1796,7 +1767,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6217.3</v>
+        <v>5878.07</v>
       </c>
     </row>
     <row r="8">
@@ -1806,17 +1777,17 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3537.59</v>
+        <v>3557.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2406.6</v>
+        <v>2258.26</v>
       </c>
     </row>
     <row r="10">
@@ -1826,7 +1797,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1288.68</v>
+        <v>1280.59</v>
       </c>
     </row>
     <row r="11">

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,20 +469,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1096.62</v>
+        <v>1131.33</v>
       </c>
       <c r="E2" t="n">
-        <v>265.01</v>
+        <v>360.02</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1005.63</v>
+        <v>1075.09</v>
       </c>
       <c r="E3" t="n">
-        <v>245.23</v>
+        <v>257.33</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>872.34</v>
+        <v>983.22</v>
       </c>
       <c r="E4" t="n">
-        <v>212.36</v>
+        <v>232.53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>816.49</v>
+        <v>857.77</v>
       </c>
       <c r="E5" t="n">
-        <v>201.07</v>
+        <v>211.49</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,20 +585,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>800.47</v>
+        <v>804.73</v>
       </c>
       <c r="E6" t="n">
-        <v>198.54</v>
+        <v>261.6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,20 +614,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>771.3099999999999</v>
+        <v>798.6900000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>379.76</v>
+        <v>190.27</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>712.37</v>
+        <v>794.23</v>
       </c>
       <c r="E8" t="n">
-        <v>171.56</v>
+        <v>193.18</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>583.6900000000001</v>
+        <v>693.3200000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>144.71</v>
+        <v>164.11</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>543.13</v>
+        <v>581.72</v>
       </c>
       <c r="E10" t="n">
-        <v>270.19</v>
+        <v>141.81</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -740,10 +740,10 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>440.06</v>
+        <v>423.72</v>
       </c>
       <c r="E11" t="n">
-        <v>219.35</v>
+        <v>207.91</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM-PRINCIPAL    (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>400.15</v>
+        <v>396.35</v>
       </c>
       <c r="E12" t="n">
-        <v>400.15</v>
+        <v>396.35</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL    (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE    (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>396.35</v>
+        <v>274.88</v>
       </c>
       <c r="E13" t="n">
-        <v>396.35</v>
+        <v>274.88</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN    (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>277.42</v>
+        <v>222.98</v>
       </c>
       <c r="E14" t="n">
-        <v>277.42</v>
+        <v>222.98</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE    (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>274.88</v>
+        <v>219.35</v>
       </c>
       <c r="E15" t="n">
-        <v>274.88</v>
+        <v>219.35</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN    (**)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>222.98</v>
+        <v>7.49</v>
       </c>
       <c r="E16" t="n">
-        <v>222.98</v>
+        <v>7.49</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>215.81</v>
+        <v>4.57</v>
       </c>
       <c r="E17" t="n">
-        <v>215.81</v>
+        <v>4.57</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.5</v>
+        <v>3.95</v>
       </c>
       <c r="E18" t="n">
-        <v>7.5</v>
+        <v>3.95</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7.49</v>
+        <v>3.67</v>
       </c>
       <c r="E19" t="n">
-        <v>7.49</v>
+        <v>1.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>5.57</v>
+        <v>3.45</v>
       </c>
       <c r="E20" t="n">
         <v>3.45</v>
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SITAB CI (STBC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>5.12</v>
+        <v>1.43</v>
       </c>
       <c r="E21" t="n">
-        <v>5.12</v>
+        <v>1.43</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,20 +1049,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3.67</v>
+        <v>1.36</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1088,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1.38</v>
+        <v>0.85</v>
       </c>
       <c r="E23" t="n">
-        <v>1.38</v>
+        <v>0.85</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,20 +1107,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1.36</v>
+        <v>0.64</v>
       </c>
       <c r="E24" t="n">
-        <v>1.36</v>
+        <v>0.13</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.85</v>
+        <v>0.51</v>
       </c>
       <c r="E25" t="n">
-        <v>0.85</v>
+        <v>0.51</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.64</v>
+        <v>-2.06</v>
       </c>
       <c r="E26" t="n">
-        <v>0.13</v>
+        <v>-6.25</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,27 +1187,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.51</v>
+        <v>-2.12</v>
       </c>
       <c r="E27" t="n">
-        <v>0.51</v>
+        <v>4.71</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.15</v>
+        <v>-3.36</v>
       </c>
       <c r="E28" t="n">
-        <v>3.95</v>
+        <v>-3.36</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,27 +1245,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.65</v>
+        <v>-3.91</v>
       </c>
       <c r="E29" t="n">
-        <v>1.43</v>
+        <v>-3.91</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,27 +1274,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.06</v>
+        <v>-5.41</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.25</v>
+        <v>-5.41</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,14 +1303,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.36</v>
+        <v>-6.67</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.36</v>
+        <v>-6.67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-3.9</v>
+        <v>-7.38</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.9</v>
+        <v>-7.38</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-3.91</v>
+        <v>-7.48</v>
       </c>
       <c r="E33" t="n">
-        <v>-3.91</v>
+        <v>-7.48</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-5.41</v>
+        <v>-7.48</v>
       </c>
       <c r="E34" t="n">
-        <v>-5.41</v>
+        <v>-7.48</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-6.67</v>
+        <v>-7.49</v>
       </c>
       <c r="E35" t="n">
-        <v>-6.67</v>
+        <v>-7.49</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>BIIC BN (BICB)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1465,10 +1465,10 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-6.83</v>
+        <v>-7.5</v>
       </c>
       <c r="E36" t="n">
-        <v>-6.83</v>
+        <v>-7.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1494,10 +1494,10 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-7.1</v>
+        <v>-7.5</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.1</v>
+        <v>-7.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1523,10 +1523,10 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>-7.38</v>
+        <v>-7.5</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.38</v>
+        <v>-7.5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1552,10 +1552,10 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-7.48</v>
+        <v>-7.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.48</v>
+        <v>-7.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1571,20 +1571,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BIIC BN (BICB)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>-7.5</v>
+        <v>-10.11</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.5</v>
+        <v>-7.44</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1593,27 +1593,27 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>-8.4</v>
+        <v>-11.15</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.44</v>
+        <v>-6.72</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1652,35 +1652,6 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SAFCA CI (SAFC)</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
-        <v>3</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-14.16</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-6.72</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>🔴 Vente</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>⚠️ Risque de décrochage</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1688,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19486.97</v>
+        <v>18373.87</v>
       </c>
     </row>
     <row r="3">
@@ -1727,87 +1698,87 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15145.3</v>
+        <v>14182.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10130.55</v>
+        <v>10748.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8453.15</v>
+        <v>9673.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8012.17</v>
+        <v>7958.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5878.07</v>
+        <v>7843.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3557.01</v>
+        <v>5475.89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2258.26</v>
+        <v>4892.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1280.59</v>
+        <v>3527.46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>924.1900000000001</v>
+        <v>872.41</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1075.09</v>
+        <v>1071.38</v>
       </c>
       <c r="E3" t="n">
-        <v>257.33</v>
+        <v>266.65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>983.22</v>
+        <v>1062.47</v>
       </c>
       <c r="E4" t="n">
-        <v>232.53</v>
+        <v>259.41</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>857.77</v>
+        <v>968.8099999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>211.49</v>
+        <v>240.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,20 +585,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>804.73</v>
+        <v>850.63</v>
       </c>
       <c r="E6" t="n">
-        <v>261.6</v>
+        <v>213.63</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -624,10 +624,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>798.6900000000001</v>
+        <v>788.96</v>
       </c>
       <c r="E7" t="n">
-        <v>190.27</v>
+        <v>197.74</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>794.23</v>
+        <v>788.9400000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>193.18</v>
+        <v>195.3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>693.3200000000001</v>
+        <v>679.85</v>
       </c>
       <c r="E9" t="n">
-        <v>164.11</v>
+        <v>165.21</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>581.72</v>
+        <v>637.87</v>
       </c>
       <c r="E10" t="n">
-        <v>141.81</v>
+        <v>214.15</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -730,20 +730,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>423.72</v>
+        <v>578.78</v>
       </c>
       <c r="E11" t="n">
-        <v>207.91</v>
+        <v>146.52</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL    (**)</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>396.35</v>
+        <v>372.08</v>
       </c>
       <c r="E12" t="n">
-        <v>396.35</v>
+        <v>372.08</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE    (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>274.88</v>
+        <v>219.35</v>
       </c>
       <c r="E13" t="n">
-        <v>274.88</v>
+        <v>219.35</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,20 +817,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN    (**)</t>
+          <t>BANK OF AFRICA BF (BOABF)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>222.98</v>
+        <v>7.43</v>
       </c>
       <c r="E14" t="n">
-        <v>222.98</v>
+        <v>7.43</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>219.35</v>
+        <v>7.43</v>
       </c>
       <c r="E15" t="n">
-        <v>219.35</v>
+        <v>7.43</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.49</v>
+        <v>4.57</v>
       </c>
       <c r="E16" t="n">
-        <v>7.49</v>
+        <v>4.57</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.57</v>
+        <v>2.02</v>
       </c>
       <c r="E17" t="n">
-        <v>4.57</v>
+        <v>-1.43</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -926,14 +926,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.95</v>
+        <v>1.43</v>
       </c>
       <c r="E18" t="n">
-        <v>3.95</v>
+        <v>1.43</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.67</v>
+        <v>1.3</v>
       </c>
       <c r="E19" t="n">
         <v>1.3</v>
@@ -991,7 +991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3.45</v>
+        <v>0.51</v>
       </c>
       <c r="E20" t="n">
-        <v>3.45</v>
+        <v>0.51</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.43</v>
+        <v>0.15</v>
       </c>
       <c r="E21" t="n">
-        <v>1.43</v>
+        <v>7.14</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,27 +1042,27 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.36</v>
+        <v>0.12</v>
       </c>
       <c r="E22" t="n">
-        <v>1.36</v>
+        <v>7.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1071,27 +1071,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.85</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.85</v>
+        <v>7.43</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,27 +1100,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.64</v>
+        <v>-0.34</v>
       </c>
       <c r="E24" t="n">
-        <v>0.13</v>
+        <v>-1.19</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.51</v>
+        <v>-2.06</v>
       </c>
       <c r="E25" t="n">
-        <v>0.51</v>
+        <v>-6.25</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,14 +1158,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.06</v>
+        <v>-2.12</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.25</v>
+        <v>4.71</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.12</v>
+        <v>-2.67</v>
       </c>
       <c r="E27" t="n">
-        <v>4.71</v>
+        <v>-3.31</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.36</v>
+        <v>-2.73</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.36</v>
+        <v>-7.44</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.91</v>
+        <v>-2.86</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.91</v>
+        <v>-2.86</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-7.38</v>
+        <v>-7.48</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.38</v>
+        <v>-7.48</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-7.48</v>
+        <v>-7.49</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.48</v>
+        <v>-7.49</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-7.48</v>
+        <v>-7.5</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.48</v>
+        <v>-7.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-7.49</v>
+        <v>-7.5</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.49</v>
+        <v>-7.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,20 +1455,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BIIC BN (BICB)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>-7.5</v>
+        <v>-14.15</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.5</v>
+        <v>-6.72</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1484,20 +1484,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>BIIC BN (BICB)</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>-7.5</v>
+        <v>-14.98</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.5</v>
+        <v>-7.48</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1507,151 +1507,6 @@
       <c r="G37" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-10.11</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-7.44</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>SAFCA CI (SAFC)</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-11.15</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-6.72</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SETAO CI (STAC)</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" t="n">
-        <v>-13.56</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
@@ -1684,51 +1539,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18373.87</v>
+        <v>18203.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14182.75</v>
+        <v>17747.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10748.47</v>
+        <v>13602.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9673.4</v>
+        <v>10748.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7958.96</v>
+        <v>9455.85</v>
       </c>
     </row>
     <row r="7">
@@ -1738,27 +1593,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7843.11</v>
+        <v>7704.96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5475.89</v>
+        <v>7701.38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4892.2</v>
+        <v>5206.38</v>
       </c>
     </row>
     <row r="10">
@@ -1768,7 +1623,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3527.46</v>
+        <v>3484.71</v>
       </c>
     </row>
     <row r="11">
@@ -1778,7 +1633,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>872.41</v>
+        <v>2954.83</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,13 +476,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1131.33</v>
+        <v>1513.55</v>
       </c>
       <c r="E2" t="n">
-        <v>360.02</v>
+        <v>382.22</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1071.38</v>
+        <v>1341.87</v>
       </c>
       <c r="E3" t="n">
-        <v>266.65</v>
+        <v>270.49</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -534,13 +534,13 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1062.47</v>
+        <v>1331.15</v>
       </c>
       <c r="E4" t="n">
-        <v>259.41</v>
+        <v>268.68</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -563,13 +563,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>968.8099999999999</v>
+        <v>1215.38</v>
       </c>
       <c r="E5" t="n">
-        <v>240.2</v>
+        <v>246.57</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -592,13 +592,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>850.63</v>
+        <v>1066.97</v>
       </c>
       <c r="E6" t="n">
-        <v>213.63</v>
+        <v>216.34</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -621,13 +621,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>788.96</v>
+        <v>988.87</v>
       </c>
       <c r="E7" t="n">
-        <v>197.74</v>
+        <v>199.91</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -650,13 +650,13 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>788.9400000000001</v>
+        <v>987.62</v>
       </c>
       <c r="E8" t="n">
-        <v>195.3</v>
+        <v>198.68</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>679.85</v>
+        <v>855.7</v>
       </c>
       <c r="E9" t="n">
-        <v>165.21</v>
+        <v>217.83</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>637.87</v>
+        <v>846.5</v>
       </c>
       <c r="E10" t="n">
-        <v>214.15</v>
+        <v>166.65</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>578.78</v>
+        <v>726.29</v>
       </c>
       <c r="E11" t="n">
-        <v>146.52</v>
+        <v>147.51</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -817,20 +817,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>7.43</v>
+        <v>14.7</v>
       </c>
       <c r="E14" t="n">
-        <v>7.43</v>
+        <v>7.27</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>BANK OF AFRICA BF (BOABF)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4.57</v>
+        <v>7.32</v>
       </c>
       <c r="E16" t="n">
-        <v>4.57</v>
+        <v>7.32</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2.02</v>
+        <v>4.57</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.43</v>
+        <v>4.57</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -926,27 +926,27 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="E18" t="n">
-        <v>1.43</v>
+        <v>-1.43</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -955,14 +955,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.51</v>
+        <v>1.3</v>
       </c>
       <c r="E20" t="n">
-        <v>0.51</v>
+        <v>1.3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.15</v>
+        <v>0.51</v>
       </c>
       <c r="E21" t="n">
-        <v>7.14</v>
+        <v>0.51</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1136,20 +1136,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>SITAB CI (STBC)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.06</v>
+        <v>-0.47</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.25</v>
+        <v>-0.47</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,14 +1158,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.12</v>
+        <v>-2.06</v>
       </c>
       <c r="E26" t="n">
-        <v>4.71</v>
+        <v>-6.25</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.67</v>
+        <v>-2.12</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.31</v>
+        <v>4.71</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.73</v>
+        <v>-2.67</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.44</v>
+        <v>-3.31</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>-5.41</v>
+        <v>-4.95</v>
       </c>
       <c r="E30" t="n">
-        <v>-5.41</v>
+        <v>-2.22</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,27 +1303,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>-6.67</v>
+        <v>-6.13</v>
       </c>
       <c r="E31" t="n">
-        <v>-6.67</v>
+        <v>-0.72</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>-7.48</v>
+        <v>-6.65</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.48</v>
+        <v>7.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,27 +1361,27 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>-7.49</v>
+        <v>-7.18</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.49</v>
+        <v>-7.33</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1390,14 +1390,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-7.5</v>
+        <v>-7.48</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.5</v>
+        <v>-7.48</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-7.5</v>
+        <v>-7.49</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.5</v>
+        <v>-7.49</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,20 +1455,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-14.15</v>
+        <v>-7.5</v>
       </c>
       <c r="E36" t="n">
-        <v>-6.72</v>
+        <v>-7.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1484,27 +1484,85 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>BIIC BN (BICB)</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
         <v>2</v>
       </c>
-      <c r="D37" t="n">
-        <v>-14.98</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-7.48</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="D38" t="n">
+        <v>-7.53</v>
+      </c>
+      <c r="E38" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>👀 À surveiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-10.98</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-4.31</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1543,7 +1601,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18203.91</v>
+        <v>67714.14</v>
       </c>
     </row>
     <row r="3">
@@ -1553,27 +1611,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17747.2</v>
+        <v>65699.06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13602.35</v>
+        <v>52213.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10748.47</v>
+        <v>47388.24</v>
       </c>
     </row>
     <row r="6">
@@ -1583,7 +1641,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9455.85</v>
+        <v>30128.99</v>
       </c>
     </row>
     <row r="7">
@@ -1593,7 +1651,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7704.96</v>
+        <v>23307.87</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1661,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7701.38</v>
+        <v>23201.15</v>
       </c>
     </row>
     <row r="9">
@@ -1613,27 +1671,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5206.38</v>
+        <v>14049.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3484.71</v>
+        <v>9609.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2954.83</v>
+        <v>8772.51</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1513.55</v>
+        <v>1122</v>
       </c>
       <c r="E2" t="n">
         <v>382.22</v>
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1341.87</v>
+        <v>1068.93</v>
       </c>
       <c r="E3" t="n">
         <v>270.49</v>
@@ -534,10 +534,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1331.15</v>
+        <v>1050.43</v>
       </c>
       <c r="E4" t="n">
         <v>268.68</v>
@@ -563,10 +563,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1215.38</v>
+        <v>964.53</v>
       </c>
       <c r="E5" t="n">
         <v>246.57</v>
@@ -585,20 +585,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1066.97</v>
+        <v>855.7</v>
       </c>
       <c r="E6" t="n">
-        <v>216.34</v>
+        <v>217.83</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,20 +614,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>988.87</v>
+        <v>853.8200000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>199.91</v>
+        <v>216.34</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>987.62</v>
+        <v>789.37</v>
       </c>
       <c r="E8" t="n">
-        <v>198.68</v>
+        <v>199.91</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>855.7</v>
+        <v>785.3200000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>217.83</v>
+        <v>198.68</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>846.5</v>
+        <v>667.53</v>
       </c>
       <c r="E10" t="n">
         <v>166.65</v>
@@ -737,10 +737,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>726.29</v>
+        <v>580.55</v>
       </c>
       <c r="E11" t="n">
         <v>147.51</v>
@@ -788,20 +788,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>219.35</v>
+        <v>14.7</v>
       </c>
       <c r="E13" t="n">
-        <v>219.35</v>
+        <v>7.27</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,20 +817,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>14.7</v>
+        <v>7.5</v>
       </c>
       <c r="E14" t="n">
-        <v>7.27</v>
+        <v>7.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -933,20 +933,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.02</v>
+        <v>1.43</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.43</v>
+        <v>1.43</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -955,14 +955,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3</v>
+        <v>0.78</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,27 +1013,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="E21" t="n">
-        <v>0.51</v>
+        <v>-7.33</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,14 +1042,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.12</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>7.5</v>
+        <v>7.43</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1088,10 +1088,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="E23" t="n">
-        <v>7.43</v>
+        <v>-1.19</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,20 +1107,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>SITAB CI (STBC)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.34</v>
+        <v>-0.47</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.19</v>
+        <v>-0.47</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SITAB CI (STBC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.47</v>
+        <v>-0.72</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.47</v>
+        <v>-0.72</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.06</v>
+        <v>-1.43</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.25</v>
+        <v>-1.43</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.67</v>
+        <v>-2.86</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.31</v>
+        <v>-2.86</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,27 +1245,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.86</v>
+        <v>-3.18</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.86</v>
+        <v>-3.31</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,27 +1274,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-4.95</v>
+        <v>-4.31</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.22</v>
+        <v>-4.31</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,27 +1303,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-6.13</v>
+        <v>-6.25</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.72</v>
+        <v>-6.25</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-6.65</v>
+        <v>-7.48</v>
       </c>
       <c r="E32" t="n">
-        <v>7.5</v>
+        <v>-7.48</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,27 +1361,27 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-7.18</v>
+        <v>-7.49</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.33</v>
+        <v>-7.49</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1390,14 +1390,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-7.48</v>
+        <v>-7.5</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.48</v>
+        <v>-7.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-7.49</v>
+        <v>-7.5</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.49</v>
+        <v>-7.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,20 +1455,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>BIIC BN (BICB)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>-7.5</v>
+        <v>-7.53</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.5</v>
+        <v>7.45</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1477,27 +1477,27 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>-7.5</v>
+        <v>-9.66</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.5</v>
+        <v>-2.22</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1505,64 +1505,6 @@
         </is>
       </c>
       <c r="G37" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>BIIC BN (BICB)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-7.53</v>
-      </c>
-      <c r="E38" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-10.98</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-4.31</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1601,7 +1543,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67714.14</v>
+        <v>18083.66</v>
       </c>
     </row>
     <row r="3">
@@ -1611,77 +1553,77 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65699.06</v>
+        <v>17182.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52213.49</v>
+        <v>13435.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47388.24</v>
+        <v>10542.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30128.99</v>
+        <v>9609.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23307.87</v>
+        <v>9553.200000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23201.15</v>
+        <v>7715.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14049.45</v>
+        <v>7607.96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9609.16</v>
+        <v>4972.03</v>
       </c>
     </row>
     <row r="11">
@@ -1691,7 +1633,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8772.51</v>
+        <v>3510.53</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,20 +469,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1122</v>
+        <v>1057.27</v>
       </c>
       <c r="E2" t="n">
-        <v>382.22</v>
+        <v>271.85</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1068.93</v>
+        <v>968.17</v>
       </c>
       <c r="E3" t="n">
-        <v>270.49</v>
+        <v>248.87</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,20 +527,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>7 499.25    197 470</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1050.43</v>
+        <v>898</v>
       </c>
       <c r="E4" t="n">
-        <v>268.68</v>
+        <v>898</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>964.53</v>
+        <v>867.1900000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>246.57</v>
+        <v>225.73</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,20 +585,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>855.7</v>
+        <v>798.74</v>
       </c>
       <c r="E6" t="n">
-        <v>217.83</v>
+        <v>270.49</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -624,10 +624,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>853.8200000000001</v>
+        <v>791.61</v>
       </c>
       <c r="E7" t="n">
-        <v>216.34</v>
+        <v>200.78</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>789.37</v>
+        <v>786.1900000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>199.91</v>
+        <v>201.94</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,20 +672,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>785.3200000000001</v>
+        <v>742.24</v>
       </c>
       <c r="E9" t="n">
-        <v>198.68</v>
+        <v>382.22</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>667.53</v>
+        <v>663.77</v>
       </c>
       <c r="E10" t="n">
-        <v>166.65</v>
+        <v>167.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -730,20 +730,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>580.55</v>
+        <v>639.89</v>
       </c>
       <c r="E11" t="n">
-        <v>147.51</v>
+        <v>217.83</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,20 +759,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>372.08</v>
+        <v>584.89</v>
       </c>
       <c r="E12" t="n">
-        <v>372.08</v>
+        <v>149.05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,20 +788,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>BRVM-PRINCIPAL   (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.7</v>
+        <v>386.48</v>
       </c>
       <c r="E13" t="n">
-        <v>7.27</v>
+        <v>386.48</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,20 +817,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.5</v>
+        <v>372.08</v>
       </c>
       <c r="E14" t="n">
-        <v>7.5</v>
+        <v>372.08</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
+          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.43</v>
+        <v>268.66</v>
       </c>
       <c r="E15" t="n">
-        <v>7.43</v>
+        <v>268.66</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.32</v>
+        <v>219.7</v>
       </c>
       <c r="E16" t="n">
-        <v>7.32</v>
+        <v>219.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.57</v>
+        <v>14.94</v>
       </c>
       <c r="E17" t="n">
-        <v>4.57</v>
+        <v>7.44</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,20 +933,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.43</v>
+        <v>14.73</v>
       </c>
       <c r="E18" t="n">
-        <v>1.43</v>
+        <v>7.41</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3</v>
+        <v>10.83</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3</v>
+        <v>-3.87</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,24 +984,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.78</v>
+        <v>7.5</v>
       </c>
       <c r="E20" t="n">
         <v>7.5</v>
@@ -1013,27 +1013,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>BANK OF AFRICA BF (BOABF)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.29</v>
+        <v>7.43</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.33</v>
+        <v>7.43</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,24 +1042,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>7.24</v>
       </c>
       <c r="E22" t="n">
         <v>7.43</v>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.34</v>
+        <v>6.72</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.19</v>
+        <v>6.72</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,27 +1100,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SITAB CI (STBC)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.47</v>
+        <v>4.71</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.47</v>
+        <v>4.71</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,20 +1136,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.72</v>
+        <v>4.57</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.72</v>
+        <v>4.57</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>BIIC BN (BICB)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.43</v>
+        <v>-0.03</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.43</v>
+        <v>7.45</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,27 +1187,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>SITAB CI (STBC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.12</v>
+        <v>-0.47</v>
       </c>
       <c r="E27" t="n">
-        <v>4.71</v>
+        <v>-0.47</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,14 +1216,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1233,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.86</v>
+        <v>-0.72</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.86</v>
+        <v>-0.72</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,20 +1252,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.18</v>
+        <v>-1.19</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.31</v>
+        <v>-1.19</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-4.31</v>
+        <v>-1.43</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.31</v>
+        <v>-1.43</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,20 +1310,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>-6.25</v>
+        <v>-2.21</v>
       </c>
       <c r="E31" t="n">
-        <v>-6.25</v>
+        <v>-2.14</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,14 +1332,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-7.48</v>
+        <v>-2.22</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.48</v>
+        <v>-2.22</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-7.49</v>
+        <v>-2.86</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.49</v>
+        <v>-2.86</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-7.5</v>
+        <v>-3.16</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.5</v>
+        <v>-3.16</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-7.5</v>
+        <v>-3.31</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.5</v>
+        <v>-3.31</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,20 +1455,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BIIC BN (BICB)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-7.53</v>
+        <v>-3.8</v>
       </c>
       <c r="E36" t="n">
-        <v>7.45</v>
+        <v>-3.8</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1477,27 +1477,27 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-9.66</v>
+        <v>-4.31</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.22</v>
+        <v>-4.31</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1505,6 +1505,151 @@
         </is>
       </c>
       <c r="G37" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SMB CI (SMBC)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CFAO MOTORS CI (CFAC)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1539,101 +1684,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18083.66</v>
+        <v>17506.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17182.79</v>
+        <v>13577.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13435.2</v>
+        <v>9966.389999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10542.56</v>
+        <v>7774.29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9609.16</v>
+        <v>7630.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9553.200000000001</v>
+        <v>4901.81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7715.65</v>
+        <v>4811.98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7607.96</v>
+        <v>3574.56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4972.03</v>
+        <v>2974.37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3510.53</v>
+        <v>2118.31</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1057.27</v>
+        <v>1074.58</v>
       </c>
       <c r="E2" t="n">
-        <v>271.85</v>
+        <v>274.64</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>968.17</v>
+        <v>986.34</v>
       </c>
       <c r="E3" t="n">
-        <v>248.87</v>
+        <v>250.7</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>867.1900000000001</v>
+        <v>880.52</v>
       </c>
       <c r="E5" t="n">
-        <v>225.73</v>
+        <v>224.82</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>798.74</v>
+        <v>804.76</v>
       </c>
       <c r="E6" t="n">
-        <v>270.49</v>
+        <v>267.62</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>791.61</v>
+        <v>800.5700000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>200.78</v>
+        <v>202.14</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>786.1900000000001</v>
+        <v>795.04</v>
       </c>
       <c r="E8" t="n">
-        <v>201.94</v>
+        <v>199.12</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>742.24</v>
+        <v>769.83</v>
       </c>
       <c r="E9" t="n">
-        <v>382.22</v>
+        <v>387.61</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>663.77</v>
+        <v>667.86</v>
       </c>
       <c r="E10" t="n">
-        <v>167.8</v>
+        <v>168.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>639.89</v>
+        <v>652.76</v>
       </c>
       <c r="E11" t="n">
-        <v>217.83</v>
+        <v>220.78</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>584.89</v>
+        <v>593.01</v>
       </c>
       <c r="E12" t="n">
-        <v>149.05</v>
+        <v>149.93</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -962,49 +962,49 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>10.83</v>
+        <v>13.49</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.87</v>
+        <v>6.25</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟡 Observer</t>
+          <t>🟢 Achat</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>✅ Renforcer</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>7.5</v>
+        <v>10.83</v>
       </c>
       <c r="E20" t="n">
-        <v>7.5</v>
+        <v>-3.87</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
@@ -1049,20 +1049,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>7.24</v>
+        <v>7.37</v>
       </c>
       <c r="E22" t="n">
-        <v>7.43</v>
+        <v>7.37</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1107,20 +1107,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.71</v>
+        <v>5.29</v>
       </c>
       <c r="E24" t="n">
-        <v>4.71</v>
+        <v>-2.14</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.57</v>
+        <v>3.5</v>
       </c>
       <c r="E25" t="n">
-        <v>4.57</v>
+        <v>-4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,14 +1158,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BIIC BN (BICB)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03</v>
+        <v>2.69</v>
       </c>
       <c r="E26" t="n">
-        <v>7.45</v>
+        <v>7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SITAB CI (STBC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.47</v>
+        <v>0.74</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.47</v>
+        <v>4.54</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>BIIC BN (BICB)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.72</v>
+        <v>-0.03</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.72</v>
+        <v>7.45</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>SITAB CI (STBC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.19</v>
+        <v>-0.47</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.19</v>
+        <v>-0.47</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.43</v>
+        <v>-0.72</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.43</v>
+        <v>-0.72</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,20 +1310,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.21</v>
+        <v>-1.19</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.14</v>
+        <v>-1.19</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,14 +1332,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.22</v>
+        <v>-1.43</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.22</v>
+        <v>-1.43</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.86</v>
+        <v>-2.22</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.86</v>
+        <v>-2.22</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-3.31</v>
+        <v>-4.06</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.31</v>
+        <v>-4.06</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1465,10 +1465,10 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-3.8</v>
+        <v>-4.61</v>
       </c>
       <c r="E36" t="n">
-        <v>-3.8</v>
+        <v>-4.61</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1494,10 +1494,10 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-4.31</v>
+        <v>-7.42</v>
       </c>
       <c r="E37" t="n">
-        <v>-4.31</v>
+        <v>-7.42</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1513,20 +1513,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>-4.61</v>
+        <v>-8.5</v>
       </c>
       <c r="E38" t="n">
-        <v>-4.61</v>
+        <v>-5.19</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1542,20 +1542,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>-7.48</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.48</v>
+        <v>-6.02</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1563,93 +1563,6 @@
         </is>
       </c>
       <c r="G39" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-7.49</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-7.49</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1688,7 +1601,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17506.66</v>
+        <v>18359.57</v>
       </c>
     </row>
     <row r="3">
@@ -1698,7 +1611,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13577.91</v>
+        <v>14325.29</v>
       </c>
     </row>
     <row r="4">
@@ -1708,7 +1621,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9966.389999999999</v>
+        <v>10397.17</v>
       </c>
     </row>
     <row r="5">
@@ -1718,7 +1631,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7774.29</v>
+        <v>8014.94</v>
       </c>
     </row>
     <row r="6">
@@ -1728,7 +1641,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7630.23</v>
+        <v>7865.92</v>
       </c>
     </row>
     <row r="7">
@@ -1738,7 +1651,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4901.81</v>
+        <v>4979.26</v>
       </c>
     </row>
     <row r="8">
@@ -1748,7 +1661,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4811.98</v>
+        <v>4893.76</v>
       </c>
     </row>
     <row r="9">
@@ -1758,7 +1671,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3574.56</v>
+        <v>3697.96</v>
       </c>
     </row>
     <row r="10">
@@ -1768,7 +1681,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2974.37</v>
+        <v>3102.87</v>
       </c>
     </row>
     <row r="11">
@@ -1778,7 +1691,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2118.31</v>
+        <v>2251.35</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -469,20 +469,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1074.58</v>
+        <v>1151.63</v>
       </c>
       <c r="E2" t="n">
-        <v>274.64</v>
+        <v>381.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>986.34</v>
+        <v>1089.86</v>
       </c>
       <c r="E3" t="n">
-        <v>250.7</v>
+        <v>274.69</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,20 +527,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7 499.25    197 470</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>898</v>
+        <v>993.62</v>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>247.48</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,20 +556,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>7 499.25    197 470</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>880.52</v>
+        <v>898</v>
       </c>
       <c r="E5" t="n">
-        <v>224.82</v>
+        <v>898</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,20 +585,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>804.76</v>
+        <v>889.79</v>
       </c>
       <c r="E6" t="n">
-        <v>267.62</v>
+        <v>222.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>800.5700000000001</v>
+        <v>806.62</v>
       </c>
       <c r="E7" t="n">
-        <v>202.14</v>
+        <v>203.79</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>795.04</v>
+        <v>804.9299999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>199.12</v>
+        <v>266.82</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,20 +672,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>769.83</v>
+        <v>795.21</v>
       </c>
       <c r="E9" t="n">
-        <v>387.61</v>
+        <v>195.47</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>667.86</v>
+        <v>670.99</v>
       </c>
       <c r="E10" t="n">
-        <v>168.2</v>
+        <v>168.34</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>652.76</v>
+        <v>659.53</v>
       </c>
       <c r="E11" t="n">
-        <v>220.78</v>
+        <v>220.92</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>593.01</v>
+        <v>599.39</v>
       </c>
       <c r="E12" t="n">
-        <v>149.93</v>
+        <v>152.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>372.08</v>
+        <v>268.66</v>
       </c>
       <c r="E14" t="n">
-        <v>372.08</v>
+        <v>268.66</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>268.66</v>
+        <v>219.7</v>
       </c>
       <c r="E15" t="n">
-        <v>268.66</v>
+        <v>219.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>219.7</v>
+        <v>14.73</v>
       </c>
       <c r="E16" t="n">
-        <v>219.7</v>
+        <v>7.41</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>BIIC BN (BICB)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>14.94</v>
+        <v>11.54</v>
       </c>
       <c r="E17" t="n">
-        <v>7.44</v>
+        <v>4.09</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,20 +933,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>14.73</v>
+        <v>10.67</v>
       </c>
       <c r="E18" t="n">
-        <v>7.41</v>
+        <v>-4.27</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -955,43 +955,43 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>13.49</v>
+        <v>6.72</v>
       </c>
       <c r="E19" t="n">
-        <v>6.25</v>
+        <v>6.72</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢 Achat</t>
+          <t>🟡 Observer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>✅ Renforcer</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>10.83</v>
+        <v>6.35</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.87</v>
+        <v>6.25</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.43</v>
+        <v>4.66</v>
       </c>
       <c r="E21" t="n">
-        <v>7.43</v>
+        <v>4.66</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>BANK OF AFRICA BN (BOAB)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>7.37</v>
+        <v>3.72</v>
       </c>
       <c r="E22" t="n">
-        <v>7.37</v>
+        <v>3.72</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.72</v>
+        <v>3.4</v>
       </c>
       <c r="E23" t="n">
-        <v>6.72</v>
+        <v>-3.87</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,14 +1100,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.29</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.14</v>
+        <v>-6.56</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.5</v>
+        <v>0.74</v>
       </c>
       <c r="E25" t="n">
-        <v>-4</v>
+        <v>4.54</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>SITAB CI (STBC)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2.69</v>
+        <v>-0.47</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>-0.47</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,27 +1187,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.74</v>
+        <v>-0.72</v>
       </c>
       <c r="E27" t="n">
-        <v>4.54</v>
+        <v>-0.72</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,14 +1216,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BIIC BN (BICB)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1233,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.03</v>
+        <v>-0.89</v>
       </c>
       <c r="E28" t="n">
-        <v>7.45</v>
+        <v>5.13</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,20 +1252,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SITAB CI (STBC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.47</v>
+        <v>-1.5</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.47</v>
+        <v>2.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.72</v>
+        <v>-2.14</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.72</v>
+        <v>-2.14</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.19</v>
+        <v>-2.22</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.19</v>
+        <v>-2.22</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.43</v>
+        <v>-3.16</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.43</v>
+        <v>-3.16</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,20 +1368,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.22</v>
+        <v>-3.85</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.22</v>
+        <v>-6.54</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1390,14 +1390,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-3.16</v>
+        <v>-4.06</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.16</v>
+        <v>-4.06</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-4.06</v>
+        <v>-4.61</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.06</v>
+        <v>-4.61</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1465,10 +1465,10 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-4.61</v>
+        <v>-5.19</v>
       </c>
       <c r="E36" t="n">
-        <v>-4.61</v>
+        <v>-5.19</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1494,10 +1494,10 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-7.42</v>
+        <v>-5.78</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.42</v>
+        <v>-5.78</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1513,20 +1513,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>-8.5</v>
+        <v>-7.42</v>
       </c>
       <c r="E38" t="n">
-        <v>-5.19</v>
+        <v>-7.42</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1542,20 +1542,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-8.880000000000001</v>
+        <v>-7.48</v>
       </c>
       <c r="E39" t="n">
-        <v>-6.02</v>
+        <v>-7.48</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18359.57</v>
+        <v>19144.37</v>
       </c>
     </row>
     <row r="3">
@@ -1611,87 +1611,87 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14325.29</v>
+        <v>14633.98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10397.17</v>
+        <v>11228.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8014.94</v>
+        <v>10707.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7865.92</v>
+        <v>8179.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4979.26</v>
+        <v>7870.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4893.76</v>
+        <v>5039.21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3697.96</v>
+        <v>4896.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3102.87</v>
+        <v>3796.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2251.35</v>
+        <v>3171.89</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,20 +469,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1151.63</v>
+        <v>1097.17</v>
       </c>
       <c r="E2" t="n">
-        <v>381.8</v>
+        <v>275.99</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1089.86</v>
+        <v>994.4299999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>274.69</v>
+        <v>247.38</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,20 +527,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>7 499.25    197 470</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>993.62</v>
+        <v>898</v>
       </c>
       <c r="E4" t="n">
-        <v>247.48</v>
+        <v>898</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,20 +556,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7 499.25    197 470</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>898</v>
+        <v>890.98</v>
       </c>
       <c r="E5" t="n">
-        <v>898</v>
+        <v>217.53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>889.79</v>
+        <v>810.65</v>
       </c>
       <c r="E6" t="n">
-        <v>222.9</v>
+        <v>203.94</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -624,10 +624,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>806.62</v>
+        <v>788</v>
       </c>
       <c r="E7" t="n">
-        <v>203.79</v>
+        <v>191.47</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>804.9299999999999</v>
+        <v>769.41</v>
       </c>
       <c r="E8" t="n">
-        <v>266.82</v>
+        <v>381.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>795.21</v>
+        <v>668.51</v>
       </c>
       <c r="E9" t="n">
-        <v>195.47</v>
+        <v>164.17</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>670.99</v>
+        <v>605.64</v>
       </c>
       <c r="E10" t="n">
-        <v>168.34</v>
+        <v>153.76</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -730,20 +730,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>659.53</v>
+        <v>534.4400000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>220.92</v>
+        <v>266.82</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,20 +759,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>599.39</v>
+        <v>441.7</v>
       </c>
       <c r="E12" t="n">
-        <v>152.9</v>
+        <v>220.92</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>268.66</v>
+        <v>381.72</v>
       </c>
       <c r="E14" t="n">
-        <v>268.66</v>
+        <v>381.72</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>219.7</v>
+        <v>268.66</v>
       </c>
       <c r="E15" t="n">
-        <v>219.7</v>
+        <v>268.66</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>14.73</v>
+        <v>268.5</v>
       </c>
       <c r="E16" t="n">
-        <v>7.41</v>
+        <v>268.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BIIC BN (BICB)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>11.54</v>
+        <v>221.18</v>
       </c>
       <c r="E17" t="n">
-        <v>4.09</v>
+        <v>221.18</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,20 +933,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>10.67</v>
+        <v>219.7</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.27</v>
+        <v>219.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -955,27 +955,27 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>6.72</v>
+        <v>7.16</v>
       </c>
       <c r="E19" t="n">
-        <v>6.72</v>
+        <v>-6.52</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,27 +984,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.35</v>
+        <v>6.72</v>
       </c>
       <c r="E20" t="n">
-        <v>6.25</v>
+        <v>6.72</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1049,20 +1049,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BN (BOAB)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.72</v>
+        <v>4.48</v>
       </c>
       <c r="E22" t="n">
-        <v>3.72</v>
+        <v>3.67</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1071,27 +1071,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>BIIC BN (BICB)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>3.4</v>
+        <v>4.09</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.87</v>
+        <v>4.09</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,27 +1100,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>BANK OF AFRICA BN (BOAB)</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.72</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.56</v>
+        <v>3.72</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.74</v>
+        <v>3.45</v>
       </c>
       <c r="E25" t="n">
-        <v>4.54</v>
+        <v>3.45</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,27 +1158,27 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SITAB CI (STBC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.47</v>
+        <v>3.17</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.47</v>
+        <v>-4.27</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,27 +1187,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.72</v>
+        <v>1.75</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.72</v>
+        <v>-5.66</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.89</v>
+        <v>1.4</v>
       </c>
       <c r="E28" t="n">
-        <v>5.13</v>
+        <v>1.4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.5</v>
+        <v>0.74</v>
       </c>
       <c r="E29" t="n">
-        <v>2.5</v>
+        <v>4.54</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.14</v>
+        <v>0.46</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.14</v>
+        <v>-6.54</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,27 +1303,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.22</v>
+        <v>-0.05</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.22</v>
+        <v>7.37</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-3.16</v>
+        <v>-1.5</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.16</v>
+        <v>2.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,27 +1361,27 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-3.85</v>
+        <v>-1.73</v>
       </c>
       <c r="E33" t="n">
-        <v>-6.54</v>
+        <v>2.33</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-4.06</v>
+        <v>-2.14</v>
       </c>
       <c r="E34" t="n">
-        <v>-4.06</v>
+        <v>-2.14</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-4.61</v>
+        <v>-3.16</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.61</v>
+        <v>-3.16</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1465,10 +1465,10 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-5.19</v>
+        <v>-3.87</v>
       </c>
       <c r="E36" t="n">
-        <v>-5.19</v>
+        <v>-3.87</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1494,10 +1494,10 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-5.78</v>
+        <v>-4.61</v>
       </c>
       <c r="E37" t="n">
-        <v>-5.78</v>
+        <v>-4.61</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1513,20 +1513,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>-7.42</v>
+        <v>-5.65</v>
       </c>
       <c r="E38" t="n">
-        <v>-7.42</v>
+        <v>-4.76</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1535,34 +1535,121 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>BERNABE CI (BNBC)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-5.94</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-5.94</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
         <v>-7.48</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E41" t="n">
         <v>-7.48</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-12.61</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1601,7 +1688,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19144.37</v>
+        <v>19525.93</v>
       </c>
     </row>
     <row r="3">
@@ -1611,77 +1698,77 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14633.98</v>
+        <v>14668.42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11228.82</v>
+        <v>10748.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10707.44</v>
+        <v>8291.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8179.83</v>
+        <v>7678.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7870.5</v>
+        <v>4991.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5039.21</v>
+        <v>3894.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4896.07</v>
+        <v>2249.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3796.25</v>
+        <v>1248.5</v>
       </c>
     </row>
     <row r="11">
@@ -1691,7 +1778,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3171.89</v>
+        <v>929.45</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1097.17</v>
+        <v>825.3200000000001</v>
       </c>
       <c r="E2" t="n">
         <v>275.99</v>
@@ -498,20 +498,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>994.4299999999999</v>
+        <v>769.41</v>
       </c>
       <c r="E3" t="n">
-        <v>247.38</v>
+        <v>381.8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,20 +527,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7 499.25    197 470</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>898</v>
+        <v>745.5599999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>247.38</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -563,10 +563,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>890.98</v>
+        <v>665.25</v>
       </c>
       <c r="E5" t="n">
         <v>217.53</v>
@@ -592,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>810.65</v>
+        <v>609.87</v>
       </c>
       <c r="E6" t="n">
         <v>203.94</v>
@@ -621,10 +621,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>788</v>
+        <v>586.0599999999999</v>
       </c>
       <c r="E7" t="n">
         <v>191.47</v>
@@ -643,7 +643,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -653,10 +653,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>769.41</v>
+        <v>534.4400000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>381.8</v>
+        <v>266.82</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -679,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>668.51</v>
+        <v>500.71</v>
       </c>
       <c r="E9" t="n">
         <v>164.17</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>605.64</v>
+        <v>456.59</v>
       </c>
       <c r="E10" t="n">
         <v>153.76</v>
@@ -730,7 +730,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -740,10 +740,10 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>534.4400000000001</v>
+        <v>441.7</v>
       </c>
       <c r="E11" t="n">
-        <v>266.82</v>
+        <v>220.92</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,20 +759,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>441.7</v>
+        <v>381.72</v>
       </c>
       <c r="E12" t="n">
-        <v>220.92</v>
+        <v>381.72</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL   (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>386.48</v>
+        <v>268.5</v>
       </c>
       <c r="E13" t="n">
-        <v>386.48</v>
+        <v>268.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>381.72</v>
+        <v>221.18</v>
       </c>
       <c r="E14" t="n">
-        <v>381.72</v>
+        <v>221.18</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE  (**)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>268.66</v>
+        <v>4.66</v>
       </c>
       <c r="E15" t="n">
-        <v>268.66</v>
+        <v>4.66</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>268.5</v>
+        <v>4.54</v>
       </c>
       <c r="E16" t="n">
-        <v>268.5</v>
+        <v>4.54</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>221.18</v>
+        <v>4.48</v>
       </c>
       <c r="E17" t="n">
-        <v>221.18</v>
+        <v>3.67</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -926,27 +926,27 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN  (**)</t>
+          <t>BIIC BN (BICB)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>219.7</v>
+        <v>4.09</v>
       </c>
       <c r="E18" t="n">
-        <v>219.7</v>
+        <v>4.09</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>BANK OF AFRICA BN (BOAB)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7.16</v>
+        <v>3.72</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.52</v>
+        <v>3.72</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,14 +984,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.72</v>
+        <v>3.45</v>
       </c>
       <c r="E20" t="n">
-        <v>6.72</v>
+        <v>3.45</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4.66</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
-        <v>4.66</v>
+        <v>1.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,20 +1049,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>4.48</v>
+        <v>0.46</v>
       </c>
       <c r="E22" t="n">
-        <v>3.67</v>
+        <v>-6.54</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BIIC BN (BICB)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.09</v>
+        <v>-0.05</v>
       </c>
       <c r="E23" t="n">
-        <v>4.09</v>
+        <v>7.37</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,27 +1100,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BN (BOAB)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.72</v>
+        <v>-0.27</v>
       </c>
       <c r="E24" t="n">
-        <v>3.72</v>
+        <v>-6.52</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.45</v>
+        <v>-1.5</v>
       </c>
       <c r="E25" t="n">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,14 +1158,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.17</v>
+        <v>-1.73</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.27</v>
+        <v>2.33</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.75</v>
+        <v>-4.27</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.66</v>
+        <v>-4.27</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>1.4</v>
+        <v>-5.65</v>
       </c>
       <c r="E28" t="n">
-        <v>1.4</v>
+        <v>-4.76</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,27 +1245,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.74</v>
+        <v>-5.66</v>
       </c>
       <c r="E29" t="n">
-        <v>4.54</v>
+        <v>-5.66</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,27 +1274,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.46</v>
+        <v>-5.78</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.54</v>
+        <v>-5.78</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,27 +1303,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.05</v>
+        <v>-5.94</v>
       </c>
       <c r="E31" t="n">
-        <v>7.37</v>
+        <v>-5.94</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.5</v>
+        <v>-7.48</v>
       </c>
       <c r="E32" t="n">
-        <v>2.5</v>
+        <v>-7.48</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,27 +1361,27 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.73</v>
+        <v>-12.61</v>
       </c>
       <c r="E33" t="n">
-        <v>2.33</v>
+        <v>-7.42</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1389,267 +1389,6 @@
         </is>
       </c>
       <c r="G33" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-2.14</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-2.14</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SAPH CI (SPHC)</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="n">
-        <v>-3.16</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-3.16</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>SUCRIVOIRE (SCRC)</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-3.87</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-3.87</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-4.61</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-4.61</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-5.65</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-4.76</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>BERNABE CI (BNBC)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-5.78</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-5.78</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-5.94</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-5.94</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-7.48</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-7.48</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" t="n">
-        <v>-12.61</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-7.42</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1688,7 +1427,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19525.93</v>
+        <v>5177.92</v>
       </c>
     </row>
     <row r="3">
@@ -1698,7 +1437,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14668.42</v>
+        <v>4133.22</v>
       </c>
     </row>
     <row r="4">
@@ -1708,7 +1447,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10748.09</v>
+        <v>3230.39</v>
       </c>
     </row>
     <row r="5">
@@ -1718,7 +1457,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8291.09</v>
+        <v>2689.78</v>
       </c>
     </row>
     <row r="6">
@@ -1728,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7678.1</v>
+        <v>2476.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4991.41</v>
+        <v>2249.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3894.63</v>
+        <v>1801.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2249.3</v>
+        <v>1503.95</v>
       </c>
     </row>
     <row r="10">

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>825.3200000000001</v>
+        <v>823.45</v>
       </c>
       <c r="E2" t="n">
-        <v>275.99</v>
+        <v>272.77</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,20 +498,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>769.41</v>
+        <v>740.49</v>
       </c>
       <c r="E3" t="n">
-        <v>381.8</v>
+        <v>245.63</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,10 +537,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>745.5599999999999</v>
+        <v>662.58</v>
       </c>
       <c r="E4" t="n">
-        <v>247.38</v>
+        <v>222.15</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,10 +566,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>665.25</v>
+        <v>608.03</v>
       </c>
       <c r="E5" t="n">
-        <v>217.53</v>
+        <v>200.3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -595,10 +595,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>609.87</v>
+        <v>573.01</v>
       </c>
       <c r="E6" t="n">
-        <v>203.94</v>
+        <v>186.07</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -624,10 +624,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>586.0599999999999</v>
+        <v>495.89</v>
       </c>
       <c r="E7" t="n">
-        <v>191.47</v>
+        <v>163.38</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>534.4400000000001</v>
+        <v>454.89</v>
       </c>
       <c r="E8" t="n">
-        <v>266.82</v>
+        <v>148.23</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,20 +672,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>500.71</v>
+        <v>381.8</v>
       </c>
       <c r="E9" t="n">
-        <v>164.17</v>
+        <v>381.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>456.59</v>
+        <v>381.72</v>
       </c>
       <c r="E10" t="n">
-        <v>153.76</v>
+        <v>381.72</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -730,20 +730,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM-PRINCIPAL        (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>441.7</v>
+        <v>377.36</v>
       </c>
       <c r="E11" t="n">
-        <v>220.92</v>
+        <v>377.36</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>381.72</v>
+        <v>268.5</v>
       </c>
       <c r="E12" t="n">
-        <v>381.72</v>
+        <v>268.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>268.5</v>
+        <v>266.82</v>
       </c>
       <c r="E13" t="n">
-        <v>268.5</v>
+        <v>266.82</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE       (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>221.18</v>
+        <v>266.58</v>
       </c>
       <c r="E14" t="n">
-        <v>221.18</v>
+        <v>266.58</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.66</v>
+        <v>221.18</v>
       </c>
       <c r="E15" t="n">
-        <v>4.66</v>
+        <v>221.18</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.54</v>
+        <v>220.92</v>
       </c>
       <c r="E16" t="n">
-        <v>4.54</v>
+        <v>220.92</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN       (**)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.48</v>
+        <v>217.21</v>
       </c>
       <c r="E17" t="n">
-        <v>3.67</v>
+        <v>217.21</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -926,14 +926,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BIIC BN (BICB)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4.09</v>
+        <v>4.66</v>
       </c>
       <c r="E18" t="n">
-        <v>4.09</v>
+        <v>4.66</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BN (BOAB)</t>
+          <t>BIIC BN (BICB)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.72</v>
+        <v>4.09</v>
       </c>
       <c r="E19" t="n">
-        <v>3.72</v>
+        <v>4.09</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3.45</v>
+        <v>3.89</v>
       </c>
       <c r="E20" t="n">
-        <v>3.45</v>
+        <v>3.89</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4</v>
+        <v>3.73</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4</v>
+        <v>3.73</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,20 +1049,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>BANK OF AFRICA BN (BOAB)</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.46</v>
+        <v>3.72</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.54</v>
+        <v>3.72</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1071,27 +1071,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05</v>
+        <v>3.45</v>
       </c>
       <c r="E23" t="n">
-        <v>7.37</v>
+        <v>3.45</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,27 +1100,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.27</v>
+        <v>2.5</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.52</v>
+        <v>2.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.5</v>
+        <v>2.33</v>
       </c>
       <c r="E25" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,27 +1158,27 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.73</v>
+        <v>1.7</v>
       </c>
       <c r="E26" t="n">
-        <v>2.33</v>
+        <v>1.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,27 +1187,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.27</v>
+        <v>1.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.27</v>
+        <v>1.4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.65</v>
+        <v>1.08</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.76</v>
+        <v>-6.29</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,20 +1252,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-5.66</v>
+        <v>0.37</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.66</v>
+        <v>-4.76</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-5.78</v>
+        <v>-4.27</v>
       </c>
       <c r="E30" t="n">
-        <v>-5.78</v>
+        <v>-4.27</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-5.94</v>
+        <v>-5.66</v>
       </c>
       <c r="E31" t="n">
-        <v>-5.94</v>
+        <v>-5.66</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-7.48</v>
+        <v>-5.94</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.48</v>
+        <v>-5.94</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,27 +1368,201 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>SETAO CI (STAC)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-6.54</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-6.54</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FILTISAC CI (FTSC)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-6.57</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-6.57</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BICI CI (BICC)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-10.27</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-7.38</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>👀 À surveiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BERNABE CI (BNBC)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-12.96</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-7.18</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
         <v>2</v>
       </c>
-      <c r="D33" t="n">
-        <v>-12.61</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-7.42</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="D39" t="n">
+        <v>-13.13</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1427,7 +1601,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5177.92</v>
+        <v>5151.57</v>
       </c>
     </row>
     <row r="3">
@@ -1437,7 +1611,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4133.22</v>
+        <v>4072.02</v>
       </c>
     </row>
     <row r="4">
@@ -1447,7 +1621,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3230.39</v>
+        <v>3203.02</v>
       </c>
     </row>
     <row r="5">
@@ -1457,7 +1631,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2689.78</v>
+        <v>2672.79</v>
       </c>
     </row>
     <row r="6">
@@ -1467,57 +1641,57 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2476.04</v>
+        <v>2363.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2249.3</v>
+        <v>1767.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1801.2</v>
+        <v>1493.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1503.95</v>
+        <v>381.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1248.5</v>
+        <v>381.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM-PRINCIPAL        (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>929.45</v>
+        <v>377.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>823.45</v>
+        <v>815.05</v>
       </c>
       <c r="E2" t="n">
-        <v>272.77</v>
+        <v>266.29</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>740.49</v>
+        <v>738.47</v>
       </c>
       <c r="E3" t="n">
-        <v>245.63</v>
+        <v>245.46</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>662.58</v>
+        <v>660.05</v>
       </c>
       <c r="E4" t="n">
-        <v>222.15</v>
+        <v>220.37</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>608.03</v>
+        <v>607.17</v>
       </c>
       <c r="E5" t="n">
-        <v>200.3</v>
+        <v>202.93</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>573.01</v>
+        <v>570.14</v>
       </c>
       <c r="E6" t="n">
-        <v>186.07</v>
+        <v>192.6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>495.89</v>
+        <v>489.73</v>
       </c>
       <c r="E7" t="n">
-        <v>163.38</v>
+        <v>162.18</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>454.89</v>
+        <v>454.55</v>
       </c>
       <c r="E8" t="n">
-        <v>148.23</v>
+        <v>152.56</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -682,10 +682,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>381.8</v>
+        <v>381.72</v>
       </c>
       <c r="E9" t="n">
-        <v>381.8</v>
+        <v>381.72</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -711,10 +711,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>381.72</v>
+        <v>377.92</v>
       </c>
       <c r="E10" t="n">
-        <v>381.72</v>
+        <v>377.92</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>266.82</v>
+        <v>267.21</v>
       </c>
       <c r="E13" t="n">
-        <v>266.82</v>
+        <v>267.21</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>220.92</v>
+        <v>219.51</v>
       </c>
       <c r="E16" t="n">
-        <v>220.92</v>
+        <v>219.51</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -933,20 +933,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4.66</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>4.66</v>
+        <v>7.49</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BIIC BN (BICB)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.09</v>
+        <v>5.14</v>
       </c>
       <c r="E19" t="n">
-        <v>4.09</v>
+        <v>5.14</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3.73</v>
+        <v>3.45</v>
       </c>
       <c r="E21" t="n">
-        <v>3.73</v>
+        <v>3.45</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,20 +1049,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BN (BOAB)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.72</v>
+        <v>2.64</v>
       </c>
       <c r="E22" t="n">
-        <v>3.72</v>
+        <v>7.4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1071,27 +1071,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.45</v>
+        <v>2.26</v>
       </c>
       <c r="E23" t="n">
-        <v>3.45</v>
+        <v>-1.47</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,14 +1100,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="E24" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,20 +1136,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.33</v>
+        <v>1.08</v>
       </c>
       <c r="E25" t="n">
-        <v>2.33</v>
+        <v>-6.29</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,27 +1158,27 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.7</v>
+        <v>0.19</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7</v>
+        <v>6.76</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,27 +1187,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.4</v>
+        <v>-2.21</v>
       </c>
       <c r="E27" t="n">
-        <v>1.4</v>
+        <v>4.97</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,14 +1216,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1233,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1.08</v>
+        <v>-2.65</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.29</v>
+        <v>-4.98</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,20 +1252,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.37</v>
+        <v>-3.13</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.76</v>
+        <v>-3.13</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,27 +1274,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-4.27</v>
+        <v>-3.71</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.27</v>
+        <v>-7.38</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-5.94</v>
+        <v>-5.85</v>
       </c>
       <c r="E32" t="n">
-        <v>-5.94</v>
+        <v>-5.85</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-6.52</v>
+        <v>-5.94</v>
       </c>
       <c r="E33" t="n">
-        <v>-6.52</v>
+        <v>-5.94</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,20 +1397,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>-6.54</v>
+        <v>-11.07</v>
       </c>
       <c r="E34" t="n">
-        <v>-6.54</v>
+        <v>-4.55</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,20 +1426,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>-6.57</v>
+        <v>-13.13</v>
       </c>
       <c r="E35" t="n">
-        <v>-6.57</v>
+        <v>-5.71</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1447,122 +1447,6 @@
         </is>
       </c>
       <c r="G35" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-7.48</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-7.48</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>BICI CI (BICC)</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-10.27</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-7.38</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>BERNABE CI (BNBC)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-12.96</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-7.18</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-13.13</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1601,7 +1485,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5151.57</v>
+        <v>5033.84</v>
       </c>
     </row>
     <row r="3">
@@ -1611,7 +1495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4072.02</v>
+        <v>4047.76</v>
       </c>
     </row>
     <row r="4">
@@ -1621,7 +1505,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3203.02</v>
+        <v>3177.14</v>
       </c>
     </row>
     <row r="5">
@@ -1631,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2672.79</v>
+        <v>2664.94</v>
       </c>
     </row>
     <row r="6">
@@ -1641,7 +1525,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2363.65</v>
+        <v>2339.72</v>
       </c>
     </row>
     <row r="7">
@@ -1651,7 +1535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1767.03</v>
+        <v>1724.17</v>
       </c>
     </row>
     <row r="8">
@@ -1661,27 +1545,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1493.04</v>
+        <v>1490.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>381.8</v>
+        <v>381.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>381.72</v>
+        <v>377.92</v>
       </c>
     </row>
     <row r="11">

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>815.05</v>
+        <v>815.36</v>
       </c>
       <c r="E2" t="n">
-        <v>266.29</v>
+        <v>276.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,20 +498,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>738.47</v>
+        <v>758.48</v>
       </c>
       <c r="E3" t="n">
-        <v>245.46</v>
+        <v>380.56</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,10 +537,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>660.05</v>
+        <v>737.01</v>
       </c>
       <c r="E4" t="n">
-        <v>220.37</v>
+        <v>245.92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,10 +566,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>607.17</v>
+        <v>663.89</v>
       </c>
       <c r="E5" t="n">
-        <v>202.93</v>
+        <v>221.37</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -595,10 +595,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>570.14</v>
+        <v>606.45</v>
       </c>
       <c r="E6" t="n">
-        <v>192.6</v>
+        <v>203.22</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -624,10 +624,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>489.73</v>
+        <v>571.9299999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>162.18</v>
+        <v>193.26</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>454.55</v>
+        <v>534.58</v>
       </c>
       <c r="E8" t="n">
-        <v>152.56</v>
+        <v>267.37</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,20 +672,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>381.72</v>
+        <v>487.95</v>
       </c>
       <c r="E9" t="n">
-        <v>381.72</v>
+        <v>162.39</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>377.92</v>
+        <v>454.87</v>
       </c>
       <c r="E10" t="n">
-        <v>377.92</v>
+        <v>154.08</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -730,20 +730,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL        (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>377.36</v>
+        <v>440.24</v>
       </c>
       <c r="E11" t="n">
-        <v>377.36</v>
+        <v>220.73</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
+          <t>BRVM-PRINCIPAL        (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>268.5</v>
+        <v>377.36</v>
       </c>
       <c r="E12" t="n">
-        <v>268.5</v>
+        <v>377.36</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE       (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>267.21</v>
+        <v>266.58</v>
       </c>
       <c r="E13" t="n">
-        <v>267.21</v>
+        <v>266.58</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE       (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN       (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>266.58</v>
+        <v>217.21</v>
       </c>
       <c r="E14" t="n">
-        <v>266.58</v>
+        <v>217.21</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>221.18</v>
+        <v>12.36</v>
       </c>
       <c r="E15" t="n">
-        <v>221.18</v>
+        <v>4.96</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>219.51</v>
+        <v>10.34</v>
       </c>
       <c r="E16" t="n">
-        <v>219.51</v>
+        <v>2.85</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN       (**)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>217.21</v>
+        <v>5.14</v>
       </c>
       <c r="E17" t="n">
-        <v>217.21</v>
+        <v>5.14</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,20 +933,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8.890000000000001</v>
+        <v>3.89</v>
       </c>
       <c r="E18" t="n">
-        <v>7.49</v>
+        <v>3.89</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>5.14</v>
+        <v>2.26</v>
       </c>
       <c r="E19" t="n">
-        <v>5.14</v>
+        <v>-1.47</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,27 +984,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.89</v>
+        <v>1.71</v>
       </c>
       <c r="E20" t="n">
-        <v>3.89</v>
+        <v>4.84</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,14 +1013,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="E21" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.64</v>
+        <v>0.19</v>
       </c>
       <c r="E22" t="n">
-        <v>7.4</v>
+        <v>6.76</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.26</v>
+        <v>-1.52</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.47</v>
+        <v>-1.52</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,27 +1100,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.7</v>
+        <v>-2.21</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7</v>
+        <v>4.97</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.08</v>
+        <v>-2.72</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.29</v>
+        <v>3.13</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>SOCIETE IVOIRIENNE DE BANQUE  (SIBC)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.19</v>
+        <v>-2.78</v>
       </c>
       <c r="E26" t="n">
-        <v>6.76</v>
+        <v>-2.78</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,27 +1187,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.21</v>
+        <v>-3.23</v>
       </c>
       <c r="E27" t="n">
-        <v>4.97</v>
+        <v>-3.23</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1227,13 +1227,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.65</v>
+        <v>-4.98</v>
       </c>
       <c r="E28" t="n">
         <v>-4.98</v>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.13</v>
+        <v>-5.71</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.13</v>
+        <v>-5.71</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-3.71</v>
+        <v>-5.94</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.38</v>
+        <v>-5.94</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,27 +1303,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>-5.66</v>
+        <v>-6.22</v>
       </c>
       <c r="E31" t="n">
-        <v>-5.66</v>
+        <v>-1.67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-5.85</v>
+        <v>-6.29</v>
       </c>
       <c r="E32" t="n">
-        <v>-5.85</v>
+        <v>-6.29</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-5.94</v>
+        <v>-7.38</v>
       </c>
       <c r="E33" t="n">
-        <v>-5.94</v>
+        <v>-7.38</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1389,64 +1389,6 @@
         </is>
       </c>
       <c r="G33" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SETAO CI (STAC)</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-11.07</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-4.55</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="n">
-        <v>-13.13</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1485,7 +1427,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5033.84</v>
+        <v>5038.07</v>
       </c>
     </row>
     <row r="3">
@@ -1495,7 +1437,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4047.76</v>
+        <v>4030.33</v>
       </c>
     </row>
     <row r="4">
@@ -1505,7 +1447,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3177.14</v>
+        <v>3216.77</v>
       </c>
     </row>
     <row r="5">
@@ -1515,7 +1457,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2664.94</v>
+        <v>2658.39</v>
       </c>
     </row>
     <row r="6">
@@ -1525,57 +1467,57 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2339.72</v>
+        <v>2354.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1724.17</v>
+        <v>2196.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1490.9</v>
+        <v>1711.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>381.72</v>
+        <v>1492.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>377.92</v>
+        <v>1249.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL        (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>377.36</v>
+        <v>924.76</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,13 +476,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>815.36</v>
+        <v>1088.39</v>
       </c>
       <c r="E2" t="n">
-        <v>276.3</v>
+        <v>273.03</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,20 +498,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>758.48</v>
+        <v>983.92</v>
       </c>
       <c r="E3" t="n">
-        <v>380.56</v>
+        <v>246.91</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,20 +527,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>737.01</v>
+        <v>880.55</v>
       </c>
       <c r="E4" t="n">
-        <v>245.92</v>
+        <v>216.66</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,20 +556,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>663.89</v>
+        <v>810.0599999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>221.37</v>
+        <v>203.61</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,20 +585,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>606.45</v>
+        <v>764.54</v>
       </c>
       <c r="E6" t="n">
-        <v>203.22</v>
+        <v>192.61</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,20 +614,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>571.9299999999999</v>
+        <v>758.48</v>
       </c>
       <c r="E7" t="n">
-        <v>193.26</v>
+        <v>380.56</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>534.58</v>
+        <v>651.03</v>
       </c>
       <c r="E8" t="n">
-        <v>267.37</v>
+        <v>163.08</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,20 +672,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>487.95</v>
+        <v>609.15</v>
       </c>
       <c r="E9" t="n">
-        <v>162.39</v>
+        <v>154.28</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>454.87</v>
+        <v>534.58</v>
       </c>
       <c r="E10" t="n">
-        <v>154.08</v>
+        <v>267.37</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL        (**)</t>
+          <t>BRVM-PRINCIPAL      (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>377.36</v>
+        <v>380.78</v>
       </c>
       <c r="E12" t="n">
-        <v>377.36</v>
+        <v>380.78</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE       (**)</t>
+          <t>BRVM-PRINCIPAL        (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>266.58</v>
+        <v>377.36</v>
       </c>
       <c r="E13" t="n">
-        <v>266.58</v>
+        <v>377.36</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN       (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE       (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>217.21</v>
+        <v>266.58</v>
       </c>
       <c r="E14" t="n">
-        <v>217.21</v>
+        <v>266.58</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>12.36</v>
+        <v>265.49</v>
       </c>
       <c r="E15" t="n">
-        <v>4.96</v>
+        <v>265.49</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>10.34</v>
+        <v>220.93</v>
       </c>
       <c r="E16" t="n">
-        <v>2.85</v>
+        <v>220.93</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN       (**)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.14</v>
+        <v>217.21</v>
       </c>
       <c r="E17" t="n">
-        <v>5.14</v>
+        <v>217.21</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,20 +933,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.89</v>
+        <v>12.36</v>
       </c>
       <c r="E18" t="n">
-        <v>3.89</v>
+        <v>4.96</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2.26</v>
+        <v>10.34</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.47</v>
+        <v>2.85</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,27 +984,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1.71</v>
+        <v>5.26</v>
       </c>
       <c r="E20" t="n">
-        <v>4.84</v>
+        <v>5.26</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,14 +1013,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1.7</v>
+        <v>5.14</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7</v>
+        <v>5.14</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,20 +1049,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.19</v>
+        <v>3.89</v>
       </c>
       <c r="E22" t="n">
-        <v>6.76</v>
+        <v>3.89</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1071,27 +1071,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>ECOBANK TRANS. INCORP. TG (ETIT)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.52</v>
+        <v>3.03</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.52</v>
+        <v>3.03</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.21</v>
+        <v>2.26</v>
       </c>
       <c r="E24" t="n">
-        <v>4.97</v>
+        <v>-1.47</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.72</v>
+        <v>1.71</v>
       </c>
       <c r="E25" t="n">
-        <v>3.13</v>
+        <v>4.84</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SOCIETE IVOIRIENNE DE BANQUE  (SIBC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.78</v>
+        <v>1.7</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.78</v>
+        <v>1.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.23</v>
+        <v>0.38</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.23</v>
+        <v>6.32</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.98</v>
+        <v>0.08</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.98</v>
+        <v>6.3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-5.71</v>
+        <v>-1.52</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.71</v>
+        <v>-1.52</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-5.94</v>
+        <v>-2.21</v>
       </c>
       <c r="E30" t="n">
-        <v>-5.94</v>
+        <v>4.97</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,27 +1303,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-6.22</v>
+        <v>-2.72</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.67</v>
+        <v>3.13</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,14 +1332,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>SOCIETE IVOIRIENNE DE BANQUE  (SIBC)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-6.29</v>
+        <v>-2.78</v>
       </c>
       <c r="E32" t="n">
-        <v>-6.29</v>
+        <v>-2.78</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,27 +1368,259 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>BANK OF AFRICA NG (BOAN)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FILTISAC CI (FTSC)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-4.89</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-5.08</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>👀 À surveiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SAFCA CI (SAFC)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>UNILEVER CI (UNLC)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>BICI CI (BICC)</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="n">
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
         <v>-7.38</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E39" t="n">
         <v>-7.38</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PALM CI (PALC)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-7.46</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-7.46</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SUCRIVOIRE (SCRC)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-10.27</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-7.04</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1427,7 +1659,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5038.07</v>
+        <v>19066.55</v>
       </c>
     </row>
     <row r="3">
@@ -1437,7 +1669,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4030.33</v>
+        <v>14228.53</v>
       </c>
     </row>
     <row r="4">
@@ -1447,7 +1679,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3216.77</v>
+        <v>10402.88</v>
       </c>
     </row>
     <row r="5">
@@ -1457,7 +1689,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2658.39</v>
+        <v>8274.74</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1699,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2354.71</v>
+        <v>7082.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2196.69</v>
+        <v>4666.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1711.88</v>
+        <v>3950.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1492.9</v>
+        <v>2196.69</v>
       </c>
     </row>
     <row r="10">

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,13 +476,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1088.39</v>
+        <v>1358.21</v>
       </c>
       <c r="E2" t="n">
-        <v>273.03</v>
+        <v>269.82</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>983.92</v>
+        <v>1230.29</v>
       </c>
       <c r="E3" t="n">
-        <v>246.91</v>
+        <v>246.37</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,20 +527,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>880.55</v>
+        <v>1137.61</v>
       </c>
       <c r="E4" t="n">
-        <v>216.66</v>
+        <v>379.13</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,20 +556,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>810.0599999999999</v>
+        <v>1092.91</v>
       </c>
       <c r="E5" t="n">
-        <v>203.61</v>
+        <v>212.36</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,20 +585,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>764.54</v>
+        <v>1013.14</v>
       </c>
       <c r="E6" t="n">
-        <v>192.61</v>
+        <v>203.08</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,20 +614,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>758.48</v>
+        <v>951.95</v>
       </c>
       <c r="E7" t="n">
-        <v>380.56</v>
+        <v>187.41</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -650,13 +650,13 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>651.03</v>
+        <v>810.12</v>
       </c>
       <c r="E8" t="n">
-        <v>163.08</v>
+        <v>159.09</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,20 +672,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>609.15</v>
+        <v>799.41</v>
       </c>
       <c r="E9" t="n">
-        <v>154.28</v>
+        <v>264.83</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>534.58</v>
+        <v>763.53</v>
       </c>
       <c r="E10" t="n">
-        <v>267.37</v>
+        <v>154.38</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>440.24</v>
+        <v>660.54</v>
       </c>
       <c r="E11" t="n">
-        <v>220.73</v>
+        <v>220.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>12.36</v>
+        <v>10.34</v>
       </c>
       <c r="E18" t="n">
-        <v>4.96</v>
+        <v>2.85</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>10.34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>2.85</v>
+        <v>-4.16</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,14 +984,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>5.26</v>
+        <v>5.14</v>
       </c>
       <c r="E20" t="n">
-        <v>5.26</v>
+        <v>5.14</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>5.14</v>
+        <v>3.89</v>
       </c>
       <c r="E21" t="n">
-        <v>5.14</v>
+        <v>3.89</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3.89</v>
+        <v>3.81</v>
       </c>
       <c r="E22" t="n">
-        <v>3.89</v>
+        <v>3.81</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1107,20 +1107,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.47</v>
+        <v>2.04</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,20 +1136,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>SOLIBRA CI (SLBC)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="E25" t="n">
-        <v>4.84</v>
+        <v>2.32</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,27 +1158,27 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7</v>
+        <v>-1.47</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,14 +1187,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.38</v>
+        <v>1.71</v>
       </c>
       <c r="E27" t="n">
-        <v>6.32</v>
+        <v>4.84</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08</v>
+        <v>1.7</v>
       </c>
       <c r="E28" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,27 +1245,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.52</v>
+        <v>1.31</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.52</v>
+        <v>-3.95</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,27 +1274,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.21</v>
+        <v>-1.52</v>
       </c>
       <c r="E30" t="n">
-        <v>4.97</v>
+        <v>-1.52</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,14 +1303,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.72</v>
+        <v>-2.63</v>
       </c>
       <c r="E31" t="n">
-        <v>3.13</v>
+        <v>4.75</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SOCIETE IVOIRIENNE DE BANQUE  (SIBC)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.78</v>
+        <v>-2.72</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.78</v>
+        <v>3.13</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,14 +1361,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>SOCIETE IVOIRIENNE DE BANQUE  (SIBC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-4</v>
+        <v>-2.78</v>
       </c>
       <c r="E33" t="n">
-        <v>-4</v>
+        <v>-2.78</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,20 +1397,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>-4.89</v>
+        <v>-3.79</v>
       </c>
       <c r="E34" t="n">
-        <v>-5.08</v>
+        <v>-3.87</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-4.98</v>
+        <v>-4</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.98</v>
+        <v>-4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1465,10 +1465,10 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-5.7</v>
+        <v>-4.14</v>
       </c>
       <c r="E36" t="n">
-        <v>-5.7</v>
+        <v>-4.14</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1484,20 +1484,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>-5.71</v>
+        <v>-4.89</v>
       </c>
       <c r="E37" t="n">
-        <v>-5.71</v>
+        <v>-5.08</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1506,14 +1506,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1523,10 +1523,10 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>-6.29</v>
+        <v>-4.98</v>
       </c>
       <c r="E38" t="n">
-        <v>-6.29</v>
+        <v>-4.98</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1552,10 +1552,10 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-7.38</v>
+        <v>-5.7</v>
       </c>
       <c r="E39" t="n">
-        <v>-7.38</v>
+        <v>-5.7</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1581,10 +1581,10 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>-7.46</v>
+        <v>-5.71</v>
       </c>
       <c r="E40" t="n">
-        <v>-7.46</v>
+        <v>-5.71</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1600,27 +1600,114 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>UNILEVER CI (UNLC)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-6.29</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PALM CI (PALC)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-7.46</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-7.46</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BERNABE CI (BNBC)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-5.51</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>👀 À surveiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="n">
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
         <v>2</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D44" t="n">
         <v>-10.27</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E44" t="n">
         <v>-7.04</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1659,7 +1746,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19066.55</v>
+        <v>70781.74000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1669,7 +1756,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14228.53</v>
+        <v>49529.74</v>
       </c>
     </row>
     <row r="4">
@@ -1679,7 +1766,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10402.88</v>
+        <v>32706.8</v>
       </c>
     </row>
     <row r="5">
@@ -1689,7 +1776,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8274.74</v>
+        <v>25282.17</v>
       </c>
     </row>
     <row r="6">
@@ -1699,7 +1786,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7082.71</v>
+        <v>20543.84</v>
       </c>
     </row>
     <row r="7">
@@ -1709,27 +1796,27 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4666.7</v>
+        <v>12250.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3950.43</v>
+        <v>10904.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2196.69</v>
+        <v>10203.49</v>
       </c>
     </row>
     <row r="10">
@@ -1739,7 +1826,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1249.02</v>
+        <v>4821.63</v>
       </c>
     </row>
     <row r="11">
@@ -1749,7 +1836,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>924.76</v>
+        <v>3182.32</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,20 +469,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1358.21</v>
+        <v>1137.61</v>
       </c>
       <c r="E2" t="n">
-        <v>269.82</v>
+        <v>379.13</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,20 +498,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1230.29</v>
+        <v>1085.44</v>
       </c>
       <c r="E3" t="n">
-        <v>246.37</v>
+        <v>269.82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,20 +527,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1137.61</v>
+        <v>984.66</v>
       </c>
       <c r="E4" t="n">
-        <v>379.13</v>
+        <v>246.37</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -563,10 +563,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1092.91</v>
+        <v>870.76</v>
       </c>
       <c r="E5" t="n">
         <v>212.36</v>
@@ -592,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1013.14</v>
+        <v>812.84</v>
       </c>
       <c r="E6" t="n">
         <v>203.08</v>
@@ -614,20 +614,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>951.95</v>
+        <v>799.41</v>
       </c>
       <c r="E7" t="n">
-        <v>187.41</v>
+        <v>264.83</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>810.12</v>
+        <v>765.88</v>
       </c>
       <c r="E8" t="n">
-        <v>159.09</v>
+        <v>187.41</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -682,10 +682,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>799.41</v>
+        <v>660.54</v>
       </c>
       <c r="E9" t="n">
-        <v>264.83</v>
+        <v>220.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>763.53</v>
+        <v>646.74</v>
       </c>
       <c r="E10" t="n">
-        <v>154.38</v>
+        <v>159.09</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -730,20 +730,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>660.54</v>
+        <v>615.3</v>
       </c>
       <c r="E11" t="n">
-        <v>220.3</v>
+        <v>154.38</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL        (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>377.36</v>
+        <v>265.49</v>
       </c>
       <c r="E13" t="n">
-        <v>377.36</v>
+        <v>265.49</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE       (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>266.58</v>
+        <v>220.93</v>
       </c>
       <c r="E14" t="n">
-        <v>266.58</v>
+        <v>220.93</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>265.49</v>
+        <v>10.34</v>
       </c>
       <c r="E15" t="n">
-        <v>265.49</v>
+        <v>2.85</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>220.93</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>220.93</v>
+        <v>-4.16</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -897,27 +897,27 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN       (**)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>217.21</v>
+        <v>5.14</v>
       </c>
       <c r="E17" t="n">
-        <v>217.21</v>
+        <v>5.14</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,20 +933,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>10.34</v>
+        <v>4.75</v>
       </c>
       <c r="E18" t="n">
-        <v>2.85</v>
+        <v>4.75</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>8.199999999999999</v>
+        <v>3.81</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.16</v>
+        <v>3.81</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,14 +984,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>ECOBANK TRANS. INCORP. TG (ETIT)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>5.14</v>
+        <v>3.03</v>
       </c>
       <c r="E20" t="n">
-        <v>5.14</v>
+        <v>3.03</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.89</v>
+        <v>2.42</v>
       </c>
       <c r="E21" t="n">
-        <v>3.89</v>
+        <v>2.04</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,14 +1042,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>SOLIBRA CI (SLBC)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3.81</v>
+        <v>2.32</v>
       </c>
       <c r="E22" t="n">
-        <v>3.81</v>
+        <v>2.32</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ECOBANK TRANS. INCORP. TG (ETIT)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.03</v>
+        <v>1.71</v>
       </c>
       <c r="E23" t="n">
-        <v>3.03</v>
+        <v>4.84</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,27 +1100,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.42</v>
+        <v>1.68</v>
       </c>
       <c r="E24" t="n">
-        <v>2.04</v>
+        <v>-5.08</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,20 +1136,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SOLIBRA CI (SLBC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.32</v>
+        <v>1.31</v>
       </c>
       <c r="E25" t="n">
-        <v>2.32</v>
+        <v>-3.95</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,14 +1158,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2.26</v>
+        <v>-0.54</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.47</v>
+        <v>-5.51</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.71</v>
+        <v>-1.47</v>
       </c>
       <c r="E27" t="n">
-        <v>4.84</v>
+        <v>-1.47</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1.7</v>
+        <v>-1.52</v>
       </c>
       <c r="E28" t="n">
-        <v>1.7</v>
+        <v>-1.52</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1.31</v>
+        <v>-2.72</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.95</v>
+        <v>3.13</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>SOCIETE IVOIRIENNE DE BANQUE  (SIBC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.52</v>
+        <v>-2.78</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.52</v>
+        <v>-2.78</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,20 +1310,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.63</v>
+        <v>-3.79</v>
       </c>
       <c r="E31" t="n">
-        <v>4.75</v>
+        <v>-3.87</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.72</v>
+        <v>-4</v>
       </c>
       <c r="E32" t="n">
-        <v>3.13</v>
+        <v>-4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,14 +1361,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SOCIETE IVOIRIENNE DE BANQUE  (SIBC)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.78</v>
+        <v>-4.14</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.78</v>
+        <v>-4.14</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,20 +1397,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-3.79</v>
+        <v>-4.98</v>
       </c>
       <c r="E34" t="n">
-        <v>-3.87</v>
+        <v>-4.98</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1419,14 +1419,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-4</v>
+        <v>-5.7</v>
       </c>
       <c r="E35" t="n">
-        <v>-4</v>
+        <v>-5.7</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1465,10 +1465,10 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-4.14</v>
+        <v>-7.46</v>
       </c>
       <c r="E36" t="n">
-        <v>-4.14</v>
+        <v>-7.46</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1484,20 +1484,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>-4.89</v>
+        <v>-10.27</v>
       </c>
       <c r="E37" t="n">
-        <v>-5.08</v>
+        <v>-7.04</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1505,209 +1505,6 @@
         </is>
       </c>
       <c r="G37" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-4.98</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-4.98</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SAFCA CI (SAFC)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>UNILEVER CI (UNLC)</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-6.29</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-6.29</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>PALM CI (PALC)</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="n">
-        <v>-7.46</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-7.46</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>BERNABE CI (BNBC)</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-7.72</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-5.51</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SUCRIVOIRE (SCRC)</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-10.27</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-7.04</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1746,7 +1543,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70781.74000000001</v>
+        <v>18914.87</v>
       </c>
     </row>
     <row r="3">
@@ -1756,77 +1553,77 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49529.74</v>
+        <v>14259.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32706.8</v>
+        <v>10904.14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25282.17</v>
+        <v>10083.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20543.84</v>
+        <v>8352.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12250.03</v>
+        <v>7116.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10904.14</v>
+        <v>4821.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10203.49</v>
+        <v>4589.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4821.63</v>
+        <v>4050.78</v>
       </c>
     </row>
     <row r="11">

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1137.61</v>
+        <v>1137.65</v>
       </c>
       <c r="E2" t="n">
-        <v>379.13</v>
+        <v>377.96</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1085.44</v>
+        <v>1086.73</v>
       </c>
       <c r="E3" t="n">
-        <v>269.82</v>
+        <v>267.58</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>984.66</v>
+        <v>984.62</v>
       </c>
       <c r="E4" t="n">
-        <v>246.37</v>
+        <v>245.42</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>870.76</v>
+        <v>866.89</v>
       </c>
       <c r="E5" t="n">
-        <v>212.36</v>
+        <v>216.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>812.84</v>
+        <v>812.47</v>
       </c>
       <c r="E6" t="n">
-        <v>203.08</v>
+        <v>202.56</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>799.41</v>
+        <v>795.71</v>
       </c>
       <c r="E7" t="n">
-        <v>264.83</v>
+        <v>263.51</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>765.88</v>
+        <v>760.95</v>
       </c>
       <c r="E8" t="n">
-        <v>187.41</v>
+        <v>187.67</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>660.54</v>
+        <v>660.77</v>
       </c>
       <c r="E9" t="n">
-        <v>220.3</v>
+        <v>219.74</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>646.74</v>
+        <v>644.39</v>
       </c>
       <c r="E10" t="n">
-        <v>159.09</v>
+        <v>159.83</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>615.3</v>
+        <v>616.87</v>
       </c>
       <c r="E11" t="n">
-        <v>154.38</v>
+        <v>154.13</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>10.34</v>
+        <v>4.84</v>
       </c>
       <c r="E15" t="n">
-        <v>2.85</v>
+        <v>4.84</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.199999999999999</v>
+        <v>4.53</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.16</v>
+        <v>4.53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -897,14 +897,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.14</v>
+        <v>4.2</v>
       </c>
       <c r="E17" t="n">
-        <v>5.14</v>
+        <v>4.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4.75</v>
+        <v>3.41</v>
       </c>
       <c r="E18" t="n">
-        <v>4.75</v>
+        <v>3.41</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>SMB CI (SMBC)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.81</v>
+        <v>3.13</v>
       </c>
       <c r="E19" t="n">
-        <v>3.81</v>
+        <v>3.13</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2.42</v>
+        <v>2.85</v>
       </c>
       <c r="E21" t="n">
-        <v>2.04</v>
+        <v>2.85</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,27 +1042,27 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOLIBRA CI (SLBC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="E22" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1071,27 +1071,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>SOLIBRA CI (SLBC)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1.71</v>
+        <v>2.32</v>
       </c>
       <c r="E23" t="n">
-        <v>4.84</v>
+        <v>2.32</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,14 +1100,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.08</v>
+        <v>3.46</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.54</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.51</v>
+        <v>-4.16</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.47</v>
+        <v>0.21</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.47</v>
+        <v>-4.54</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.52</v>
+        <v>-0.79</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.52</v>
+        <v>4.72</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.72</v>
+        <v>-2.19</v>
       </c>
       <c r="E29" t="n">
-        <v>3.13</v>
+        <v>-6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SOCIETE IVOIRIENNE DE BANQUE  (SIBC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.78</v>
+        <v>-2.5</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.78</v>
+        <v>-2.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,20 +1310,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>SOCIETE IVOIRIENNE DE BANQUE  (SIBC)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.79</v>
+        <v>-2.78</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.87</v>
+        <v>-2.78</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,14 +1332,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-4</v>
+        <v>-4.14</v>
       </c>
       <c r="E32" t="n">
-        <v>-4</v>
+        <v>-4.14</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,20 +1368,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>-4.14</v>
+        <v>-4.22</v>
       </c>
       <c r="E33" t="n">
-        <v>-4.14</v>
+        <v>-4.98</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1390,14 +1390,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-4.98</v>
+        <v>-5.08</v>
       </c>
       <c r="E34" t="n">
-        <v>-4.98</v>
+        <v>-5.08</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1505,6 +1505,35 @@
         </is>
       </c>
       <c r="G37" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BANK OF AFRICA NG (BOAN)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-10.48</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-6.48</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1543,7 +1572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18914.87</v>
+        <v>18981.84</v>
       </c>
     </row>
     <row r="3">
@@ -1553,7 +1582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14259.21</v>
+        <v>14257.55</v>
       </c>
     </row>
     <row r="4">
@@ -1563,7 +1592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10904.14</v>
+        <v>10905.06</v>
       </c>
     </row>
     <row r="5">
@@ -1573,7 +1602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10083.7</v>
+        <v>9960.690000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1583,7 +1612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8352.27</v>
+        <v>8341.950000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1593,7 +1622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7116.36</v>
+        <v>6994.77</v>
       </c>
     </row>
     <row r="8">
@@ -1603,7 +1632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4821.63</v>
+        <v>4772.04</v>
       </c>
     </row>
     <row r="9">
@@ -1613,7 +1642,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4589.05</v>
+        <v>4547.03</v>
       </c>
     </row>
     <row r="10">
@@ -1623,7 +1652,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4050.78</v>
+        <v>4076.59</v>
       </c>
     </row>
     <row r="11">
@@ -1633,7 +1662,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3182.32</v>
+        <v>3184.68</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1137.65</v>
+        <v>1133.17</v>
       </c>
       <c r="E2" t="n">
-        <v>377.96</v>
+        <v>376.08</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1086.73</v>
+        <v>1076.4</v>
       </c>
       <c r="E3" t="n">
-        <v>267.58</v>
+        <v>265.97</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>984.62</v>
+        <v>982.38</v>
       </c>
       <c r="E4" t="n">
-        <v>245.42</v>
+        <v>243.68</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>866.89</v>
+        <v>863.0599999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>216.5</v>
+        <v>217.54</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>812.47</v>
+        <v>811.59</v>
       </c>
       <c r="E6" t="n">
-        <v>202.56</v>
+        <v>202.34</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>795.71</v>
+        <v>792.89</v>
       </c>
       <c r="E7" t="n">
-        <v>263.51</v>
+        <v>264.55</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>760.95</v>
+        <v>753.3099999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>187.67</v>
+        <v>185.62</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>660.77</v>
+        <v>659.16</v>
       </c>
       <c r="E9" t="n">
-        <v>219.74</v>
+        <v>219.12</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>644.39</v>
+        <v>645.38</v>
       </c>
       <c r="E10" t="n">
-        <v>159.83</v>
+        <v>163.38</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>616.87</v>
+        <v>616.73</v>
       </c>
       <c r="E11" t="n">
-        <v>154.13</v>
+        <v>153.94</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4.84</v>
+        <v>11.36</v>
       </c>
       <c r="E15" t="n">
-        <v>4.84</v>
+        <v>6.83</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4.53</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>4.53</v>
+        <v>2.04</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>ECOBANK TRANS. INCORP. TG (ETIT)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="E18" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SMB CI (SMBC)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.13</v>
+        <v>2.67</v>
       </c>
       <c r="E19" t="n">
-        <v>3.13</v>
+        <v>2.67</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ECOBANK TRANS. INCORP. TG (ETIT)</t>
+          <t>SOLIBRA CI (SLBC)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3.03</v>
+        <v>2.32</v>
       </c>
       <c r="E20" t="n">
-        <v>3.03</v>
+        <v>2.32</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.85</v>
+        <v>1.86</v>
       </c>
       <c r="E21" t="n">
-        <v>2.85</v>
+        <v>6.02</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,27 +1042,27 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>2.42</v>
+        <v>1.44</v>
       </c>
       <c r="E22" t="n">
-        <v>2.04</v>
+        <v>3.99</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SOLIBRA CI (SLBC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.32</v>
+        <v>1.31</v>
       </c>
       <c r="E23" t="n">
-        <v>2.32</v>
+        <v>-3.95</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,14 +1100,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.94</v>
+        <v>0.21</v>
       </c>
       <c r="E24" t="n">
-        <v>3.46</v>
+        <v>-3.2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.31</v>
+        <v>0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.95</v>
+        <v>-4.54</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>-0.79</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.16</v>
+        <v>4.72</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.21</v>
+        <v>-2.19</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.54</v>
+        <v>-6</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.79</v>
+        <v>-2.36</v>
       </c>
       <c r="E28" t="n">
-        <v>4.72</v>
+        <v>-2.36</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,27 +1245,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.19</v>
+        <v>-2.5</v>
       </c>
       <c r="E29" t="n">
-        <v>-6</v>
+        <v>-2.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.5</v>
+        <v>-2.56</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.5</v>
+        <v>-2.56</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,20 +1310,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SOCIETE IVOIRIENNE DE BANQUE  (SIBC)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.78</v>
+        <v>-3.53</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.78</v>
+        <v>-6.99</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
@@ -1368,20 +1368,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-4.22</v>
+        <v>-5.08</v>
       </c>
       <c r="E33" t="n">
-        <v>-4.98</v>
+        <v>-5.08</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1390,27 +1390,27 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>-5.08</v>
+        <v>-6.68</v>
       </c>
       <c r="E34" t="n">
-        <v>-5.08</v>
+        <v>3.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1419,14 +1419,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-5.7</v>
+        <v>-7.04</v>
       </c>
       <c r="E35" t="n">
-        <v>-5.7</v>
+        <v>-7.04</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1494,10 +1494,10 @@
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>-10.27</v>
+        <v>-9.08</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.04</v>
+        <v>-3.38</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1505,35 +1505,6 @@
         </is>
       </c>
       <c r="G37" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-10.48</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-6.48</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1572,7 +1543,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18981.84</v>
+        <v>18458.01</v>
       </c>
     </row>
     <row r="3">
@@ -1582,7 +1553,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14257.55</v>
+        <v>14164.57</v>
       </c>
     </row>
     <row r="4">
@@ -1592,7 +1563,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10905.06</v>
+        <v>10802.47</v>
       </c>
     </row>
     <row r="5">
@@ -1602,7 +1573,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9960.690000000001</v>
+        <v>9840.790000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1612,7 +1583,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8341.950000000001</v>
+        <v>8317.450000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1622,7 +1593,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6994.77</v>
+        <v>6809.94</v>
       </c>
     </row>
     <row r="8">
@@ -1632,7 +1603,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4772.04</v>
+        <v>4734.64</v>
       </c>
     </row>
     <row r="9">
@@ -1642,7 +1613,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4547.03</v>
+        <v>4564.56</v>
       </c>
     </row>
     <row r="10">
@@ -1652,7 +1623,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4076.59</v>
+        <v>4074.29</v>
       </c>
     </row>
     <row r="11">
@@ -1662,7 +1633,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3184.68</v>
+        <v>3168.19</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,13 +476,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1133.17</v>
+        <v>1507.84</v>
       </c>
       <c r="E2" t="n">
-        <v>376.08</v>
+        <v>374.67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1076.4</v>
+        <v>1061</v>
       </c>
       <c r="E3" t="n">
-        <v>265.97</v>
+        <v>257.63</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>982.38</v>
+        <v>1052.93</v>
       </c>
       <c r="E4" t="n">
-        <v>243.68</v>
+        <v>260.04</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>863.0599999999999</v>
+        <v>979.17</v>
       </c>
       <c r="E5" t="n">
-        <v>217.54</v>
+        <v>243.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>811.59</v>
+        <v>875.35</v>
       </c>
       <c r="E6" t="n">
-        <v>202.34</v>
+        <v>216.19</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,20 +614,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>792.89</v>
+        <v>865.96</v>
       </c>
       <c r="E7" t="n">
-        <v>264.55</v>
+        <v>219.56</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>753.3099999999999</v>
+        <v>806.77</v>
       </c>
       <c r="E8" t="n">
-        <v>185.62</v>
+        <v>198.79</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,20 +672,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>659.16</v>
+        <v>745.34</v>
       </c>
       <c r="E9" t="n">
-        <v>219.12</v>
+        <v>184.64</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>645.38</v>
+        <v>644.52</v>
       </c>
       <c r="E10" t="n">
-        <v>163.38</v>
+        <v>162.22</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>616.73</v>
+        <v>612.02</v>
       </c>
       <c r="E11" t="n">
-        <v>153.94</v>
+        <v>149.57</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,20 +759,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL      (**)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>380.78</v>
+        <v>11.36</v>
       </c>
       <c r="E12" t="n">
-        <v>380.78</v>
+        <v>6.83</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,20 +788,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>265.49</v>
+        <v>6.85</v>
       </c>
       <c r="E13" t="n">
-        <v>265.49</v>
+        <v>2.65</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,20 +817,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN      (**)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>220.93</v>
+        <v>3.85</v>
       </c>
       <c r="E14" t="n">
-        <v>220.93</v>
+        <v>3.85</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.36</v>
+        <v>3.11</v>
       </c>
       <c r="E15" t="n">
-        <v>6.83</v>
+        <v>3.11</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.359999999999999</v>
+        <v>2.67</v>
       </c>
       <c r="E16" t="n">
-        <v>2.04</v>
+        <v>2.67</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SOLIBRA CI (SLBC)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="E17" t="n">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ECOBANK TRANS. INCORP. TG (ETIT)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.03</v>
+        <v>2.04</v>
       </c>
       <c r="E18" t="n">
-        <v>3.03</v>
+        <v>2.04</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.67</v>
+        <v>1.86</v>
       </c>
       <c r="E19" t="n">
-        <v>2.67</v>
+        <v>6.02</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,27 +984,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SOLIBRA CI (SLBC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.32</v>
+        <v>0.55</v>
       </c>
       <c r="E20" t="n">
-        <v>2.32</v>
+        <v>3.23</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,14 +1013,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.86</v>
+        <v>0.21</v>
       </c>
       <c r="E21" t="n">
-        <v>6.02</v>
+        <v>-4.54</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,20 +1049,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.44</v>
+        <v>0.21</v>
       </c>
       <c r="E22" t="n">
-        <v>3.99</v>
+        <v>-3.2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.31</v>
+        <v>-0.76</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.95</v>
+        <v>3.19</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.21</v>
+        <v>-2.19</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2</v>
+        <v>-6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,20 +1136,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.21</v>
+        <v>-2.36</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.54</v>
+        <v>-2.36</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,27 +1158,27 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.79</v>
+        <v>-2.56</v>
       </c>
       <c r="E26" t="n">
-        <v>4.72</v>
+        <v>-2.56</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,27 +1187,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.19</v>
+        <v>-3.38</v>
       </c>
       <c r="E27" t="n">
-        <v>-6</v>
+        <v>-3.38</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.36</v>
+        <v>-3.53</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.36</v>
+        <v>-6.99</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.5</v>
+        <v>-4.14</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.5</v>
+        <v>-4.14</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.56</v>
+        <v>-5.3</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.56</v>
+        <v>-4.51</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,27 +1303,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.53</v>
+        <v>-6.37</v>
       </c>
       <c r="E31" t="n">
-        <v>-6.99</v>
+        <v>-6.37</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>-4.14</v>
+        <v>-6.87</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.14</v>
+        <v>-4.37</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-5.08</v>
+        <v>-7.48</v>
       </c>
       <c r="E33" t="n">
-        <v>-5.08</v>
+        <v>-7.48</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,116 +1397,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>-6.68</v>
+        <v>-8.94</v>
       </c>
       <c r="E34" t="n">
-        <v>3.8</v>
+        <v>-4.08</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>🟡 Observer</t>
+          <t>🔴 Vente</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SUCRIVOIRE (SCRC)</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="n">
-        <v>-7.04</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-7.04</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>PALM CI (PALC)</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-7.46</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-7.46</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>SAFCA CI (SAFC)</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-9.08</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-3.38</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
+          <t>⚠️ Risque de décrochage</t>
         </is>
       </c>
     </row>
@@ -1539,101 +1452,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18458.01</v>
+        <v>51650.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14164.57</v>
+        <v>17691.87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10802.47</v>
+        <v>17306.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9840.790000000001</v>
+        <v>14032.58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8317.450000000001</v>
+        <v>10233.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6809.94</v>
+        <v>9931.83</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4734.64</v>
+        <v>8183.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4564.56</v>
+        <v>6621.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4074.29</v>
+        <v>4549.31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3168.19</v>
+        <v>3996.97</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1507.84</v>
+        <v>1501.83</v>
       </c>
       <c r="E2" t="n">
-        <v>374.67</v>
+        <v>373.12</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1061</v>
+        <v>1049.71</v>
       </c>
       <c r="E3" t="n">
-        <v>257.63</v>
+        <v>258.53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1052.93</v>
+        <v>1049.51</v>
       </c>
       <c r="E4" t="n">
-        <v>260.04</v>
+        <v>261.41</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>979.17</v>
+        <v>976.29</v>
       </c>
       <c r="E5" t="n">
-        <v>243.7</v>
+        <v>243.49</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>875.35</v>
+        <v>871.65</v>
       </c>
       <c r="E6" t="n">
-        <v>216.19</v>
+        <v>216.6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>865.96</v>
+        <v>869.8200000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>219.56</v>
+        <v>216.22</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>806.77</v>
+        <v>803.8200000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>198.79</v>
+        <v>200.13</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>745.34</v>
+        <v>737.5</v>
       </c>
       <c r="E9" t="n">
-        <v>184.64</v>
+        <v>179.57</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>644.52</v>
+        <v>645.5599999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>162.22</v>
+        <v>160.13</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>612.02</v>
+        <v>608.36</v>
       </c>
       <c r="E11" t="n">
-        <v>149.57</v>
+        <v>150.72</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3.85</v>
+        <v>6.02</v>
       </c>
       <c r="E14" t="n">
-        <v>3.85</v>
+        <v>6.02</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3.11</v>
+        <v>3.88</v>
       </c>
       <c r="E15" t="n">
-        <v>3.11</v>
+        <v>3.88</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>2.67</v>
+        <v>3.85</v>
       </c>
       <c r="E16" t="n">
-        <v>2.67</v>
+        <v>3.85</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOLIBRA CI (SLBC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2.32</v>
+        <v>3.19</v>
       </c>
       <c r="E17" t="n">
-        <v>2.32</v>
+        <v>3.19</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.04</v>
+        <v>3.11</v>
       </c>
       <c r="E18" t="n">
-        <v>2.04</v>
+        <v>3.11</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1.86</v>
+        <v>2.67</v>
       </c>
       <c r="E19" t="n">
-        <v>6.02</v>
+        <v>2.67</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,27 +984,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.55</v>
+        <v>1.64</v>
       </c>
       <c r="E20" t="n">
-        <v>3.23</v>
+        <v>1.64</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,27 +1013,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>UNIWAX CI (UNXC)</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.21</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.54</v>
+        <v>1.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,27 +1042,27 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.21</v>
+        <v>0.55</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2</v>
+        <v>3.23</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1088,10 +1088,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.76</v>
+        <v>0.21</v>
       </c>
       <c r="E23" t="n">
-        <v>3.19</v>
+        <v>-4.51</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.19</v>
+        <v>0.21</v>
       </c>
       <c r="E24" t="n">
-        <v>-6</v>
+        <v>-3.2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,20 +1136,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.36</v>
+        <v>-1.52</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.36</v>
+        <v>4.85</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.38</v>
+        <v>-3.53</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.38</v>
+        <v>-6.99</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.53</v>
+        <v>-3.63</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.99</v>
+        <v>3.24</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-4.14</v>
+        <v>-4.54</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.14</v>
+        <v>-4.54</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-5.3</v>
+        <v>-4.76</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.51</v>
+        <v>-4.76</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,14 +1303,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-6.37</v>
+        <v>-4.92</v>
       </c>
       <c r="E31" t="n">
-        <v>-6.37</v>
+        <v>-4.92</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-6.87</v>
+        <v>-6</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.37</v>
+        <v>-6</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,20 +1368,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>-7.48</v>
+        <v>-7.29</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.48</v>
+        <v>-4.93</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,27 +1397,85 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>UNILEVER CI (UNLC)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SAFCA CI (SAFC)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-7.56</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>SETAO CI (STAC)</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="n">
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
         <v>3</v>
       </c>
-      <c r="D34" t="n">
-        <v>-8.94</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-4.08</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="D36" t="n">
+        <v>-9.82</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>🔴 Vente</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>⚠️ Risque de décrochage</t>
         </is>
@@ -1456,7 +1514,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51650.75</v>
+        <v>51001.61</v>
       </c>
     </row>
     <row r="3">
@@ -1466,7 +1524,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17691.87</v>
+        <v>17148.72</v>
       </c>
     </row>
     <row r="4">
@@ -1476,7 +1534,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17306.63</v>
+        <v>17143.46</v>
       </c>
     </row>
     <row r="5">
@@ -1486,7 +1544,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14032.58</v>
+        <v>13915.07</v>
       </c>
     </row>
     <row r="6">
@@ -1496,7 +1554,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10233.71</v>
+        <v>10114.33</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1564,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9931.83</v>
+        <v>10055.79</v>
       </c>
     </row>
     <row r="8">
@@ -1516,7 +1574,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8183.82</v>
+        <v>8103.19</v>
       </c>
     </row>
     <row r="9">
@@ -1526,7 +1584,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6621.73</v>
+        <v>6438.37</v>
       </c>
     </row>
     <row r="10">
@@ -1536,7 +1594,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4549.31</v>
+        <v>4567.97</v>
       </c>
     </row>
     <row r="11">
@@ -1546,7 +1604,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3996.97</v>
+        <v>3938.02</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,13 +476,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1501.83</v>
+        <v>1875.5</v>
       </c>
       <c r="E2" t="n">
-        <v>373.12</v>
+        <v>373.67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,20 +498,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1049.71</v>
+        <v>1308.27</v>
       </c>
       <c r="E3" t="n">
-        <v>258.53</v>
+        <v>258.76</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,20 +527,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1049.51</v>
+        <v>1302.98</v>
       </c>
       <c r="E4" t="n">
-        <v>261.41</v>
+        <v>253.27</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -563,13 +563,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>976.29</v>
+        <v>1219.61</v>
       </c>
       <c r="E5" t="n">
-        <v>243.49</v>
+        <v>243.32</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -592,13 +592,13 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>871.65</v>
+        <v>1086.21</v>
       </c>
       <c r="E6" t="n">
-        <v>216.6</v>
+        <v>214.56</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -621,13 +621,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>869.8200000000001</v>
+        <v>1079.14</v>
       </c>
       <c r="E7" t="n">
-        <v>216.22</v>
+        <v>209.32</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -650,13 +650,13 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>803.8200000000001</v>
+        <v>1000.77</v>
       </c>
       <c r="E8" t="n">
-        <v>200.13</v>
+        <v>196.95</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -679,13 +679,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>737.5</v>
+        <v>922.55</v>
       </c>
       <c r="E9" t="n">
-        <v>179.57</v>
+        <v>185.05</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>645.5599999999999</v>
+        <v>806.77</v>
       </c>
       <c r="E10" t="n">
-        <v>160.13</v>
+        <v>161.21</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>608.36</v>
+        <v>755.8200000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>150.72</v>
+        <v>147.46</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -763,45 +763,45 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>11.36</v>
+        <v>14.69</v>
       </c>
       <c r="E12" t="n">
-        <v>6.83</v>
+        <v>3.33</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟡 Observer</t>
+          <t>🟢 Achat</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>✅ Renforcer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>6.85</v>
+        <v>6.02</v>
       </c>
       <c r="E13" t="n">
-        <v>2.65</v>
+        <v>6.02</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>6.02</v>
+        <v>3.88</v>
       </c>
       <c r="E14" t="n">
-        <v>6.02</v>
+        <v>3.88</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="E15" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.85</v>
+        <v>3.19</v>
       </c>
       <c r="E16" t="n">
-        <v>3.85</v>
+        <v>3.19</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="E17" t="n">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.11</v>
+        <v>1.64</v>
       </c>
       <c r="E18" t="n">
-        <v>3.11</v>
+        <v>1.64</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>UNIWAX CI (UNXC)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2.67</v>
+        <v>1.4</v>
       </c>
       <c r="E19" t="n">
-        <v>2.67</v>
+        <v>1.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.64</v>
+        <v>0.55</v>
       </c>
       <c r="E20" t="n">
-        <v>1.64</v>
+        <v>3.23</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,27 +1013,27 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UNIWAX CI (UNXC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4</v>
+        <v>0.49</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4</v>
+        <v>-6.36</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,27 +1042,27 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.55</v>
+        <v>0.21</v>
       </c>
       <c r="E22" t="n">
-        <v>3.23</v>
+        <v>-4.51</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1091,7 +1091,7 @@
         <v>0.21</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.51</v>
+        <v>-3.2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,20 +1107,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2</v>
+        <v>7.41</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.52</v>
+        <v>-0.33</v>
       </c>
       <c r="E25" t="n">
-        <v>4.85</v>
+        <v>4.21</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.56</v>
+        <v>-1.48</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.56</v>
+        <v>3.28</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,14 +1187,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.53</v>
+        <v>-2.49</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.99</v>
+        <v>-5.16</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.63</v>
+        <v>-2.56</v>
       </c>
       <c r="E28" t="n">
-        <v>3.24</v>
+        <v>-2.56</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-4.54</v>
+        <v>-3.23</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.54</v>
+        <v>-3.23</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>-4.76</v>
+        <v>-3.26</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.76</v>
+        <v>6.56</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,27 +1303,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-4.92</v>
+        <v>-3.53</v>
       </c>
       <c r="E31" t="n">
-        <v>-4.92</v>
+        <v>-6.99</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>-6</v>
+        <v>-3.63</v>
       </c>
       <c r="E32" t="n">
-        <v>-6</v>
+        <v>3.24</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,27 +1361,27 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-7.29</v>
+        <v>-3.7</v>
       </c>
       <c r="E33" t="n">
-        <v>-4.93</v>
+        <v>-3.7</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-7.48</v>
+        <v>-4.92</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.48</v>
+        <v>-4.92</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,20 +1426,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
         <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>-7.56</v>
+        <v>-5.71</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.18</v>
+        <v>-4.19</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1448,36 +1448,94 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>ORAGROUP TOGO (ORGT)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-9.82</v>
+        <v>-6</v>
       </c>
       <c r="E36" t="n">
-        <v>-4.75</v>
+        <v>-6</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>🔴 Vente</t>
+          <t>🟡 Observer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>⚠️ Risque de décrochage</t>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>UNILEVER CI (UNLC)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SAFCA CI (SAFC)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-7.56</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-4.18</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1514,27 +1572,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51001.61</v>
+        <v>241953</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17148.72</v>
+        <v>61762.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17143.46</v>
+        <v>60834.54</v>
       </c>
     </row>
     <row r="5">
@@ -1544,7 +1602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13915.07</v>
+        <v>48016.55</v>
       </c>
     </row>
     <row r="6">
@@ -1554,7 +1612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10114.33</v>
+        <v>32030.21</v>
       </c>
     </row>
     <row r="7">
@@ -1564,7 +1622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10055.79</v>
+        <v>31313.9</v>
       </c>
     </row>
     <row r="8">
@@ -1574,7 +1632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8103.19</v>
+        <v>24259.36</v>
       </c>
     </row>
     <row r="9">
@@ -1584,7 +1642,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6438.37</v>
+        <v>18537.63</v>
       </c>
     </row>
     <row r="10">
@@ -1594,7 +1652,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4567.97</v>
+        <v>12093.21</v>
       </c>
     </row>
     <row r="11">
@@ -1604,7 +1662,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3938.02</v>
+        <v>9892.48</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1875.5</v>
+        <v>1497.54</v>
       </c>
       <c r="E2" t="n">
         <v>373.67</v>
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1308.27</v>
+        <v>1044.76</v>
       </c>
       <c r="E3" t="n">
         <v>258.76</v>
@@ -534,10 +534,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1302.98</v>
+        <v>1035.4</v>
       </c>
       <c r="E4" t="n">
         <v>253.27</v>
@@ -563,10 +563,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1219.61</v>
+        <v>974.1900000000001</v>
       </c>
       <c r="E5" t="n">
         <v>243.32</v>
@@ -592,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1086.21</v>
+        <v>866.47</v>
       </c>
       <c r="E6" t="n">
         <v>214.56</v>
@@ -621,10 +621,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1079.14</v>
+        <v>862.64</v>
       </c>
       <c r="E7" t="n">
         <v>209.32</v>
@@ -650,10 +650,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1000.77</v>
+        <v>798.21</v>
       </c>
       <c r="E8" t="n">
         <v>196.95</v>
@@ -679,10 +679,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>922.55</v>
+        <v>734.88</v>
       </c>
       <c r="E9" t="n">
         <v>185.05</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>806.77</v>
+        <v>646.9400000000001</v>
       </c>
       <c r="E10" t="n">
         <v>161.21</v>
@@ -737,10 +737,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>755.8200000000001</v>
+        <v>601.6900000000001</v>
       </c>
       <c r="E11" t="n">
         <v>147.46</v>
@@ -763,45 +763,45 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>14.69</v>
+        <v>10.16</v>
       </c>
       <c r="E12" t="n">
         <v>3.33</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢 Achat</t>
+          <t>🟡 Observer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>✅ Renforcer</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>6.02</v>
+        <v>7.03</v>
       </c>
       <c r="E13" t="n">
-        <v>6.02</v>
+        <v>3.23</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3.88</v>
+        <v>6.02</v>
       </c>
       <c r="E14" t="n">
-        <v>3.88</v>
+        <v>6.02</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3.85</v>
+        <v>4.21</v>
       </c>
       <c r="E15" t="n">
-        <v>3.85</v>
+        <v>4.21</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.19</v>
+        <v>3.88</v>
       </c>
       <c r="E16" t="n">
-        <v>3.19</v>
+        <v>3.88</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>3.11</v>
+        <v>3.85</v>
       </c>
       <c r="E17" t="n">
-        <v>3.11</v>
+        <v>3.85</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.64</v>
+        <v>3.19</v>
       </c>
       <c r="E18" t="n">
-        <v>1.64</v>
+        <v>3.19</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UNIWAX CI (UNXC)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4</v>
+        <v>3.11</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4</v>
+        <v>3.11</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.55</v>
+        <v>1.72</v>
       </c>
       <c r="E20" t="n">
-        <v>3.23</v>
+        <v>6.56</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.49</v>
+        <v>1.64</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.36</v>
+        <v>1.64</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,27 +1042,27 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>UNIWAX CI (UNXC)</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.21</v>
+        <v>1.4</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.51</v>
+        <v>1.4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1071,27 +1071,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2</v>
+        <v>7.41</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,20 +1107,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.12</v>
+        <v>-1.13</v>
       </c>
       <c r="E24" t="n">
-        <v>7.41</v>
+        <v>3.24</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.33</v>
+        <v>-1.48</v>
       </c>
       <c r="E25" t="n">
-        <v>4.21</v>
+        <v>3.28</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.48</v>
+        <v>-2.49</v>
       </c>
       <c r="E26" t="n">
-        <v>3.28</v>
+        <v>-5.16</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.49</v>
+        <v>-2.56</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.16</v>
+        <v>-2.56</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,14 +1216,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1233,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.56</v>
+        <v>-3.2</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.56</v>
+        <v>-3.2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-3.26</v>
+        <v>-3.7</v>
       </c>
       <c r="E30" t="n">
-        <v>6.56</v>
+        <v>-3.7</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,14 +1303,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.53</v>
+        <v>-3.71</v>
       </c>
       <c r="E31" t="n">
-        <v>-6.99</v>
+        <v>-6.36</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-3.63</v>
+        <v>-4.51</v>
       </c>
       <c r="E32" t="n">
-        <v>3.24</v>
+        <v>-4.51</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,14 +1361,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-3.7</v>
+        <v>-4.92</v>
       </c>
       <c r="E33" t="n">
-        <v>-3.7</v>
+        <v>-4.92</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,20 +1397,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>-4.92</v>
+        <v>-5.71</v>
       </c>
       <c r="E34" t="n">
-        <v>-4.92</v>
+        <v>-4.19</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1419,27 +1419,27 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-5.71</v>
+        <v>-6.99</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.19</v>
+        <v>-6.99</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1448,14 +1448,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ORAGROUP TOGO (ORGT)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1465,10 +1465,10 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-6</v>
+        <v>-7.48</v>
       </c>
       <c r="E36" t="n">
-        <v>-6</v>
+        <v>-7.48</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1484,20 +1484,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>-7.48</v>
+        <v>-7.56</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.48</v>
+        <v>-4.18</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1505,35 +1505,6 @@
         </is>
       </c>
       <c r="G37" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>SAFCA CI (SAFC)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-7.56</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-4.18</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1572,7 +1543,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>241953</v>
+        <v>50542.94</v>
       </c>
     </row>
     <row r="3">
@@ -1582,7 +1553,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61762.63</v>
+        <v>16918.14</v>
       </c>
     </row>
     <row r="4">
@@ -1592,7 +1563,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>60834.54</v>
+        <v>16477.22</v>
       </c>
     </row>
     <row r="5">
@@ -1602,7 +1573,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48016.55</v>
+        <v>13829.87</v>
       </c>
     </row>
     <row r="6">
@@ -1612,7 +1583,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32030.21</v>
+        <v>9948.85</v>
       </c>
     </row>
     <row r="7">
@@ -1622,7 +1593,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31313.9</v>
+        <v>9825.4</v>
       </c>
     </row>
     <row r="8">
@@ -1632,7 +1603,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24259.36</v>
+        <v>7951.08</v>
       </c>
     </row>
     <row r="9">
@@ -1642,7 +1613,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18537.63</v>
+        <v>6378.82</v>
       </c>
     </row>
     <row r="10">
@@ -1652,7 +1623,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12093.21</v>
+        <v>4592.77</v>
       </c>
     </row>
     <row r="11">
@@ -1662,7 +1633,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9892.48</v>
+        <v>3832.04</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1497.54</v>
+        <v>1121.46</v>
       </c>
       <c r="E2" t="n">
         <v>373.67</v>
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1044.76</v>
+        <v>1014.58</v>
       </c>
       <c r="E3" t="n">
-        <v>258.76</v>
+        <v>245.15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1035.4</v>
+        <v>973.04</v>
       </c>
       <c r="E4" t="n">
-        <v>253.27</v>
+        <v>242.53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>974.1900000000001</v>
+        <v>860.67</v>
       </c>
       <c r="E5" t="n">
-        <v>243.32</v>
+        <v>213.32</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>866.47</v>
+        <v>854.1</v>
       </c>
       <c r="E6" t="n">
-        <v>214.56</v>
+        <v>209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -624,10 +624,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>862.64</v>
+        <v>792.09</v>
       </c>
       <c r="E7" t="n">
-        <v>209.32</v>
+        <v>196.22</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>798.21</v>
+        <v>780.21</v>
       </c>
       <c r="E8" t="n">
-        <v>196.95</v>
+        <v>258.76</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>734.88</v>
+        <v>732.41</v>
       </c>
       <c r="E9" t="n">
-        <v>185.05</v>
+        <v>183.15</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>646.9400000000001</v>
+        <v>640.08</v>
       </c>
       <c r="E10" t="n">
-        <v>161.21</v>
+        <v>156.52</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>601.6900000000001</v>
+        <v>594.1799999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>147.46</v>
+        <v>146.43</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,20 +759,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>BRVM-PRINCIPAL       (**)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.16</v>
+        <v>371.06</v>
       </c>
       <c r="E12" t="n">
-        <v>3.33</v>
+        <v>371.06</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,20 +788,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.03</v>
+        <v>258.56</v>
       </c>
       <c r="E13" t="n">
-        <v>3.23</v>
+        <v>258.56</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>6.02</v>
+        <v>4.21</v>
       </c>
       <c r="E14" t="n">
-        <v>6.02</v>
+        <v>4.21</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4.21</v>
+        <v>3.88</v>
       </c>
       <c r="E15" t="n">
-        <v>4.21</v>
+        <v>3.88</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="E16" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>3.85</v>
+        <v>3.19</v>
       </c>
       <c r="E17" t="n">
-        <v>3.85</v>
+        <v>3.19</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="E18" t="n">
-        <v>3.19</v>
+        <v>3.11</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.11</v>
+        <v>2.48</v>
       </c>
       <c r="E19" t="n">
-        <v>3.11</v>
+        <v>7.41</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,27 +984,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>BANK OF AFRICA BN (BOAB)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1.72</v>
+        <v>2.22</v>
       </c>
       <c r="E20" t="n">
-        <v>6.56</v>
+        <v>2.22</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,14 +1013,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="E21" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UNIWAX CI (UNXC)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="E22" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.12</v>
+        <v>1.41</v>
       </c>
       <c r="E23" t="n">
-        <v>7.41</v>
+        <v>1.41</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,27 +1100,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>UNIWAX CI (UNXC)</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.13</v>
+        <v>1.4</v>
       </c>
       <c r="E24" t="n">
-        <v>3.24</v>
+        <v>1.4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.48</v>
+        <v>1.38</v>
       </c>
       <c r="E25" t="n">
-        <v>3.28</v>
+        <v>1.38</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,14 +1158,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.49</v>
+        <v>-1.03</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.16</v>
+        <v>-4.26</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.56</v>
+        <v>-1.13</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.56</v>
+        <v>3.24</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.2</v>
+        <v>-2.02</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.2</v>
+        <v>2.49</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,27 +1245,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.23</v>
+        <v>-2.27</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.23</v>
+        <v>6.56</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-3.7</v>
+        <v>-3.23</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.7</v>
+        <v>-3.23</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,20 +1310,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.71</v>
+        <v>-3.7</v>
       </c>
       <c r="E31" t="n">
-        <v>-6.36</v>
+        <v>-3.7</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-4.51</v>
+        <v>-3.71</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.51</v>
+        <v>-6.36</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,27 +1361,27 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-4.92</v>
+        <v>-3.93</v>
       </c>
       <c r="E33" t="n">
-        <v>-4.92</v>
+        <v>-7.26</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1390,27 +1390,27 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-5.71</v>
+        <v>-4.18</v>
       </c>
       <c r="E34" t="n">
-        <v>-4.19</v>
+        <v>-4.18</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1419,14 +1419,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-6.99</v>
+        <v>-4.31</v>
       </c>
       <c r="E35" t="n">
-        <v>-6.99</v>
+        <v>-4.31</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,20 +1455,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>-7.48</v>
+        <v>-4.65</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.48</v>
+        <v>-3.17</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1477,34 +1477,150 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>0</v>
       </c>
       <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-4.92</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NESTLE CI (NTLC)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-5.16</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SUCRIVOIRE (SCRC)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
         <v>2</v>
       </c>
-      <c r="D37" t="n">
-        <v>-7.56</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-4.18</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="D40" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-4.19</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>👀 À surveiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>UNILEVER CI (UNLC)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1539,81 +1655,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50542.94</v>
+        <v>15534.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16918.14</v>
+        <v>13783.26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16477.22</v>
+        <v>10537.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13829.87</v>
+        <v>9766.219999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9948.85</v>
+        <v>9558.469999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9825.4</v>
+        <v>7788.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7951.08</v>
+        <v>6322.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6378.82</v>
+        <v>4568.26</v>
       </c>
     </row>
     <row r="10">
@@ -1623,7 +1739,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4592.77</v>
+        <v>4470.54</v>
       </c>
     </row>
     <row r="11">
@@ -1633,7 +1749,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3832.04</v>
+        <v>3715.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1121.46</v>
+        <v>1116.95</v>
       </c>
       <c r="E2" t="n">
-        <v>373.67</v>
+        <v>370.16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1014.58</v>
+        <v>986.3099999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>245.15</v>
+        <v>229.36</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>973.04</v>
+        <v>971.85</v>
       </c>
       <c r="E4" t="n">
-        <v>242.53</v>
+        <v>242.51</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>860.67</v>
+        <v>855.79</v>
       </c>
       <c r="E5" t="n">
-        <v>213.32</v>
+        <v>211.31</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>854.1</v>
+        <v>847.23</v>
       </c>
       <c r="E6" t="n">
-        <v>209</v>
+        <v>212.69</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>792.09</v>
+        <v>787.5599999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>196.22</v>
+        <v>194.26</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>780.21</v>
+        <v>779.0700000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>258.76</v>
+        <v>258.9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>732.41</v>
+        <v>732.0700000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>183.15</v>
+        <v>184.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>640.08</v>
+        <v>632.25</v>
       </c>
       <c r="E10" t="n">
-        <v>156.52</v>
+        <v>154.39</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>594.1799999999999</v>
+        <v>587.75</v>
       </c>
       <c r="E11" t="n">
-        <v>146.43</v>
+        <v>143.14</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3.88</v>
+        <v>3.24</v>
       </c>
       <c r="E15" t="n">
-        <v>3.88</v>
+        <v>3.24</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LOTERIE NATIONALE DU BENIN (LNBB)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3.85</v>
+        <v>2.76</v>
       </c>
       <c r="E16" t="n">
-        <v>3.85</v>
+        <v>7.41</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -897,27 +897,27 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.19</v>
+        <v>2.48</v>
       </c>
       <c r="E17" t="n">
-        <v>3.19</v>
+        <v>7.41</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -926,27 +926,27 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.11</v>
+        <v>2.41</v>
       </c>
       <c r="E18" t="n">
-        <v>3.11</v>
+        <v>6.67</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -955,27 +955,27 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>BANK OF AFRICA BN (BOAB)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="E19" t="n">
-        <v>7.41</v>
+        <v>2.22</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,14 +984,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BN (BOAB)</t>
+          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="E20" t="n">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="E21" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="E22" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>UNIWAX CI (UNXC)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1088,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="E23" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UNIWAX CI (UNXC)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="E24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,20 +1136,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.38</v>
+        <v>0.83</v>
       </c>
       <c r="E25" t="n">
-        <v>1.38</v>
+        <v>4.53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,14 +1158,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.03</v>
+        <v>0.66</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.26</v>
+        <v>-4.19</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.13</v>
+        <v>0.42</v>
       </c>
       <c r="E27" t="n">
-        <v>3.24</v>
+        <v>4.35</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1233,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.02</v>
+        <v>-1.65</v>
       </c>
       <c r="E28" t="n">
-        <v>2.49</v>
+        <v>4.71</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,20 +1252,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.27</v>
+        <v>-2.91</v>
       </c>
       <c r="E29" t="n">
-        <v>6.56</v>
+        <v>-6.79</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.7</v>
+        <v>-4.18</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.7</v>
+        <v>-4.18</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>-3.71</v>
+        <v>-4.38</v>
       </c>
       <c r="E32" t="n">
-        <v>-6.36</v>
+        <v>-6.19</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-3.93</v>
+        <v>-4.54</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.26</v>
+        <v>-7.03</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-4.18</v>
+        <v>-4.92</v>
       </c>
       <c r="E34" t="n">
-        <v>-4.18</v>
+        <v>-4.92</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-4.31</v>
+        <v>-5.16</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.31</v>
+        <v>-5.16</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,20 +1455,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-4.65</v>
+        <v>-5.29</v>
       </c>
       <c r="E36" t="n">
-        <v>-3.17</v>
+        <v>-5.29</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1477,14 +1477,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1494,10 +1494,10 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>-4.92</v>
+        <v>-5.48</v>
       </c>
       <c r="E37" t="n">
-        <v>-4.92</v>
+        <v>-5.48</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1513,20 +1513,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>-5.16</v>
+        <v>-10.62</v>
       </c>
       <c r="E38" t="n">
-        <v>-5.16</v>
+        <v>-6.31</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1534,93 +1534,6 @@
         </is>
       </c>
       <c r="G38" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SUCRIVOIRE (SCRC)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-5.29</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-5.29</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-4.19</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>UNILEVER CI (UNLC)</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-7.48</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-7.48</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1659,7 +1572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15534.14</v>
+        <v>14298.29</v>
       </c>
     </row>
     <row r="3">
@@ -1669,7 +1582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13783.26</v>
+        <v>13735.19</v>
       </c>
     </row>
     <row r="4">
@@ -1679,7 +1592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10537.49</v>
+        <v>10436.41</v>
       </c>
     </row>
     <row r="5">
@@ -1689,7 +1602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9766.219999999999</v>
+        <v>9613.940000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1699,7 +1612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9558.469999999999</v>
+        <v>9350.83</v>
       </c>
     </row>
     <row r="7">
@@ -1709,7 +1622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7788.11</v>
+        <v>7668.52</v>
       </c>
     </row>
     <row r="8">
@@ -1719,7 +1632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6322.8</v>
+        <v>6315.12</v>
       </c>
     </row>
     <row r="9">
@@ -1729,7 +1642,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4568.26</v>
+        <v>4553.48</v>
       </c>
     </row>
     <row r="10">
@@ -1739,7 +1652,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4470.54</v>
+        <v>4334.06</v>
       </c>
     </row>
     <row r="11">
@@ -1749,7 +1662,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3715.75</v>
+        <v>3617.44</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1116.95</v>
+        <v>1110.47</v>
       </c>
       <c r="E2" t="n">
-        <v>370.16</v>
+        <v>366.64</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>986.3099999999999</v>
+        <v>968.12</v>
       </c>
       <c r="E3" t="n">
-        <v>229.36</v>
+        <v>239.76</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>971.85</v>
+        <v>948.62</v>
       </c>
       <c r="E4" t="n">
-        <v>242.51</v>
+        <v>220.84</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>855.79</v>
+        <v>848.78</v>
       </c>
       <c r="E5" t="n">
-        <v>211.31</v>
+        <v>209.59</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>847.23</v>
+        <v>841.8099999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>212.69</v>
+        <v>210.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>787.5599999999999</v>
+        <v>780.26</v>
       </c>
       <c r="E7" t="n">
-        <v>194.26</v>
+        <v>192.83</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>779.0700000000001</v>
+        <v>777</v>
       </c>
       <c r="E8" t="n">
-        <v>258.9</v>
+        <v>259.34</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>732.0700000000001</v>
+        <v>735.5</v>
       </c>
       <c r="E9" t="n">
-        <v>184.3</v>
+        <v>183</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>632.25</v>
+        <v>627.67</v>
       </c>
       <c r="E10" t="n">
-        <v>154.39</v>
+        <v>155.55</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>587.75</v>
+        <v>579.2</v>
       </c>
       <c r="E11" t="n">
-        <v>143.14</v>
+        <v>142.17</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -817,20 +817,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.21</v>
+        <v>7.52</v>
       </c>
       <c r="E14" t="n">
-        <v>4.21</v>
+        <v>7.41</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -839,14 +839,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3.24</v>
+        <v>7.41</v>
       </c>
       <c r="E15" t="n">
-        <v>3.24</v>
+        <v>7.41</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.76</v>
+        <v>4.59</v>
       </c>
       <c r="E16" t="n">
-        <v>7.41</v>
+        <v>4.22</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>2.48</v>
+        <v>4.35</v>
       </c>
       <c r="E17" t="n">
-        <v>7.41</v>
+        <v>4.35</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1020,20 +1020,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CORIS BANK INTERNATIONAL (CBIBF)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="E21" t="n">
-        <v>1.64</v>
+        <v>7.25</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UNIWAX CI (UNXC)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1088,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>SOLIBRA CI (SLBC)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="E24" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.66</v>
+        <v>0.43</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.19</v>
+        <v>-3.78</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.42</v>
+        <v>-1.65</v>
       </c>
       <c r="E27" t="n">
-        <v>4.35</v>
+        <v>4.71</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.65</v>
+        <v>-3.08</v>
       </c>
       <c r="E28" t="n">
-        <v>4.71</v>
+        <v>-3.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,20 +1252,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.91</v>
+        <v>-3.23</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.79</v>
+        <v>-3.23</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,27 +1274,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-3.23</v>
+        <v>-3.87</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.23</v>
+        <v>1.42</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,14 +1303,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-4.18</v>
+        <v>-4.19</v>
       </c>
       <c r="E31" t="n">
-        <v>-4.18</v>
+        <v>-4.19</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-4.38</v>
+        <v>-4.54</v>
       </c>
       <c r="E32" t="n">
-        <v>-6.19</v>
+        <v>-7.03</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,20 +1368,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-4.54</v>
+        <v>-5.16</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.03</v>
+        <v>-5.16</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1390,14 +1390,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1407,10 +1407,10 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-4.92</v>
+        <v>-5.29</v>
       </c>
       <c r="E34" t="n">
-        <v>-4.92</v>
+        <v>-5.29</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,20 +1426,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>-5.16</v>
+        <v>-10.16</v>
       </c>
       <c r="E35" t="n">
-        <v>-5.16</v>
+        <v>-3.37</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,87 +1455,29 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>-5.29</v>
+        <v>-14.47</v>
       </c>
       <c r="E36" t="n">
-        <v>-5.29</v>
+        <v>-3.85</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>🟡 Observer</t>
+          <t>🔴 Vente</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-5.48</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-5.48</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>CIE CI (CIEC)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-10.62</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
+          <t>⚠️ Risque de décrochage</t>
         </is>
       </c>
     </row>
@@ -1568,21 +1510,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14298.29</v>
+        <v>13584.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13735.19</v>
+        <v>12784.69</v>
       </c>
     </row>
     <row r="4">
@@ -1592,7 +1534,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10436.41</v>
+        <v>10292.1</v>
       </c>
     </row>
     <row r="5">
@@ -1602,7 +1544,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9613.940000000001</v>
+        <v>9398.860000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1612,7 +1554,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9350.83</v>
+        <v>9188.84</v>
       </c>
     </row>
     <row r="7">
@@ -1622,7 +1564,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7668.52</v>
+        <v>7479.57</v>
       </c>
     </row>
     <row r="8">
@@ -1632,7 +1574,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6315.12</v>
+        <v>6393.83</v>
       </c>
     </row>
     <row r="9">
@@ -1642,7 +1584,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4553.48</v>
+        <v>4526.82</v>
       </c>
     </row>
     <row r="10">
@@ -1652,7 +1594,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4334.06</v>
+        <v>4255.99</v>
       </c>
     </row>
     <row r="11">
@@ -1662,7 +1604,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3617.44</v>
+        <v>3490.67</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1110.47</v>
+        <v>736.8</v>
       </c>
       <c r="E2" t="n">
         <v>366.64</v>
@@ -505,10 +505,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>968.12</v>
+        <v>724.8</v>
       </c>
       <c r="E3" t="n">
         <v>239.76</v>
@@ -534,10 +534,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>948.62</v>
+        <v>695.35</v>
       </c>
       <c r="E4" t="n">
         <v>220.84</v>
@@ -563,10 +563,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>848.78</v>
+        <v>634.22</v>
       </c>
       <c r="E5" t="n">
         <v>209.59</v>
@@ -592,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>841.8099999999999</v>
+        <v>632.49</v>
       </c>
       <c r="E6" t="n">
         <v>210.8</v>
@@ -621,10 +621,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>780.26</v>
+        <v>583.3099999999999</v>
       </c>
       <c r="E7" t="n">
         <v>192.83</v>
@@ -643,7 +643,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -653,10 +653,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>777</v>
+        <v>550.45</v>
       </c>
       <c r="E8" t="n">
-        <v>259.34</v>
+        <v>183</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,20 +672,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>735.5</v>
+        <v>518.24</v>
       </c>
       <c r="E9" t="n">
-        <v>183</v>
+        <v>259.34</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>627.67</v>
+        <v>466.46</v>
       </c>
       <c r="E10" t="n">
         <v>155.55</v>
@@ -737,10 +737,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>579.2</v>
+        <v>431.74</v>
       </c>
       <c r="E11" t="n">
         <v>142.17</v>
@@ -817,20 +817,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>7.52</v>
+        <v>4.71</v>
       </c>
       <c r="E14" t="n">
-        <v>7.41</v>
+        <v>4.71</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -839,14 +839,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>7.41</v>
+        <v>4.53</v>
       </c>
       <c r="E15" t="n">
-        <v>7.41</v>
+        <v>4.53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4.59</v>
+        <v>4.35</v>
       </c>
       <c r="E16" t="n">
-        <v>4.22</v>
+        <v>4.35</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -897,27 +897,27 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.35</v>
+        <v>4.24</v>
       </c>
       <c r="E17" t="n">
-        <v>4.35</v>
+        <v>7.41</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.83</v>
+        <v>-1.97</v>
       </c>
       <c r="E25" t="n">
-        <v>4.53</v>
+        <v>4.22</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.43</v>
+        <v>-3.78</v>
       </c>
       <c r="E26" t="n">
         <v>-3.78</v>
@@ -1187,14 +1187,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.65</v>
+        <v>-3.87</v>
       </c>
       <c r="E27" t="n">
-        <v>4.71</v>
+        <v>1.42</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.08</v>
+        <v>-4.54</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.5</v>
+        <v>-7.03</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.23</v>
+        <v>-5.29</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.23</v>
+        <v>-5.29</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>-3.87</v>
+        <v>-6.41</v>
       </c>
       <c r="E30" t="n">
-        <v>1.42</v>
+        <v>-3.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,20 +1310,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>-4.19</v>
+        <v>-10.16</v>
       </c>
       <c r="E31" t="n">
-        <v>-4.19</v>
+        <v>-3.37</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,143 +1339,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>-4.54</v>
+        <v>-14.47</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.03</v>
+        <v>-3.85</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>🟡 Observer</t>
+          <t>🔴 Vente</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
-        <is>
-          <t>👀 À surveiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>NESTLE CI (NTLC)</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-5.29</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-5.29</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SODE CI (SDCC)</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="n">
-        <v>-10.16</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-3.37</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CIE CI (CIEC)</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-14.47</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>🔴 Vente</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
         <is>
           <t>⚠️ Risque de décrochage</t>
         </is>
@@ -1514,7 +1398,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13584.95</v>
+        <v>3886.06</v>
       </c>
     </row>
     <row r="3">
@@ -1524,87 +1408,87 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12784.69</v>
+        <v>3547.26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10292.1</v>
+        <v>2919.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9398.860000000001</v>
+        <v>2902.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9188.84</v>
+        <v>2452.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7479.57</v>
+        <v>2178.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6393.83</v>
+        <v>2093.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4526.82</v>
+        <v>1567.62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4255.99</v>
+        <v>1351.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3490.67</v>
+        <v>1189.67</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -476,13 +476,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>736.8</v>
+        <v>1105.86</v>
       </c>
       <c r="E2" t="n">
-        <v>366.64</v>
+        <v>369.06</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -508,10 +508,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>724.8</v>
+        <v>779.54</v>
       </c>
       <c r="E3" t="n">
-        <v>239.76</v>
+        <v>261.3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,10 +537,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>695.35</v>
+        <v>724.0700000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>220.84</v>
+        <v>241.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,10 +566,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>634.22</v>
+        <v>670.9299999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>209.59</v>
+        <v>220.73</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>632.49</v>
+        <v>636.13</v>
       </c>
       <c r="E6" t="n">
-        <v>210.8</v>
+        <v>212.64</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -624,10 +624,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>583.3099999999999</v>
+        <v>634.09</v>
       </c>
       <c r="E7" t="n">
-        <v>192.83</v>
+        <v>213.19</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -653,10 +653,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>550.45</v>
+        <v>583.6799999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>183</v>
+        <v>196.59</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,20 +672,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>518.24</v>
+        <v>549.5599999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>259.34</v>
+        <v>182.26</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>466.46</v>
+        <v>465.14</v>
       </c>
       <c r="E10" t="n">
-        <v>155.55</v>
+        <v>155.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>431.74</v>
+        <v>432.39</v>
       </c>
       <c r="E11" t="n">
-        <v>142.17</v>
+        <v>147.08</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,20 +759,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL       (**)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>371.06</v>
+        <v>7.47</v>
       </c>
       <c r="E12" t="n">
-        <v>371.06</v>
+        <v>7.47</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,20 +788,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE      (**)</t>
+          <t>ONATEL BF (ONTBF)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>258.56</v>
+        <v>7.41</v>
       </c>
       <c r="E13" t="n">
-        <v>258.56</v>
+        <v>7.41</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>4.71</v>
+        <v>6.67</v>
       </c>
       <c r="E14" t="n">
-        <v>4.71</v>
+        <v>6.67</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4.53</v>
+        <v>4.99</v>
       </c>
       <c r="E15" t="n">
-        <v>4.53</v>
+        <v>4.99</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4.35</v>
+        <v>4.71</v>
       </c>
       <c r="E16" t="n">
-        <v>4.35</v>
+        <v>4.71</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.24</v>
+        <v>4.68</v>
       </c>
       <c r="E17" t="n">
-        <v>7.41</v>
+        <v>3.26</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -926,27 +926,27 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.41</v>
+        <v>4.53</v>
       </c>
       <c r="E18" t="n">
-        <v>6.67</v>
+        <v>4.53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -955,14 +955,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BN (BOAB)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>2.22</v>
+        <v>4.4</v>
       </c>
       <c r="E19" t="n">
-        <v>2.22</v>
+        <v>4.4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ECOBANK COTE D''IVOIRE (ECOC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1.89</v>
+        <v>4.35</v>
       </c>
       <c r="E20" t="n">
-        <v>1.89</v>
+        <v>4.35</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>SOLIBRA CI (SLBC)</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1.77</v>
+        <v>1.21</v>
       </c>
       <c r="E21" t="n">
-        <v>7.25</v>
+        <v>1.21</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,27 +1042,27 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.41</v>
+        <v>0.85</v>
       </c>
       <c r="E22" t="n">
-        <v>1.41</v>
+        <v>-3.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1071,27 +1071,27 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.38</v>
+        <v>-1.97</v>
       </c>
       <c r="E23" t="n">
-        <v>1.38</v>
+        <v>4.22</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1100,27 +1100,27 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SOLIBRA CI (SLBC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>1.21</v>
+        <v>-2.02</v>
       </c>
       <c r="E24" t="n">
-        <v>1.21</v>
+        <v>-3.79</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.97</v>
+        <v>-3.42</v>
       </c>
       <c r="E25" t="n">
-        <v>4.22</v>
+        <v>-3.42</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.87</v>
+        <v>-4</v>
       </c>
       <c r="E27" t="n">
-        <v>1.42</v>
+        <v>-4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,27 +1216,27 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.54</v>
+        <v>-4.13</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.03</v>
+        <v>6.03</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-5.29</v>
+        <v>-4.34</v>
       </c>
       <c r="E29" t="n">
-        <v>-5.29</v>
+        <v>-4.34</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,20 +1281,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-6.41</v>
+        <v>-5.29</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.5</v>
+        <v>-5.29</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,14 +1303,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>-10.16</v>
+        <v>-9.26</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.37</v>
+        <v>-2.23</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1346,22 +1346,22 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>-14.47</v>
+        <v>-10.16</v>
       </c>
       <c r="E32" t="n">
         <v>-3.85</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>🔴 Vente</t>
+          <t>🟡 Observer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>⚠️ Risque de décrochage</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1394,101 +1394,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3886.06</v>
+        <v>10190.96</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3547.26</v>
+        <v>4559.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2919.73</v>
+        <v>3877.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2902.99</v>
+        <v>3289.21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2452.47</v>
+        <v>2938.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2178.14</v>
+        <v>2918.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2093.95</v>
+        <v>2455.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1567.62</v>
+        <v>2170.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1351.01</v>
+        <v>1559.04</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1189.67</v>
+        <v>1354.84</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1105.86</v>
+        <v>735.7</v>
       </c>
       <c r="E2" t="n">
         <v>369.06</v>
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -508,10 +508,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>779.54</v>
+        <v>721.66</v>
       </c>
       <c r="E3" t="n">
-        <v>261.3</v>
+        <v>240.1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,10 +537,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>724.0700000000001</v>
+        <v>659.74</v>
       </c>
       <c r="E4" t="n">
-        <v>241.8</v>
+        <v>218.17</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,10 +566,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>670.9299999999999</v>
+        <v>635.9299999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>220.73</v>
+        <v>212.49</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -595,10 +595,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>636.13</v>
+        <v>589.36</v>
       </c>
       <c r="E6" t="n">
-        <v>212.64</v>
+        <v>199.94</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -624,10 +624,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>634.09</v>
+        <v>542.08</v>
       </c>
       <c r="E7" t="n">
-        <v>213.19</v>
+        <v>176.82</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>583.6799999999999</v>
+        <v>520.64</v>
       </c>
       <c r="E8" t="n">
-        <v>196.59</v>
+        <v>261.3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -682,10 +682,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>549.5599999999999</v>
+        <v>466.47</v>
       </c>
       <c r="E9" t="n">
-        <v>182.26</v>
+        <v>155.72</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -711,10 +711,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>465.14</v>
+        <v>442.58</v>
       </c>
       <c r="E10" t="n">
-        <v>155.2</v>
+        <v>153.33</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -730,20 +730,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>432.39</v>
+        <v>422.78</v>
       </c>
       <c r="E11" t="n">
-        <v>147.08</v>
+        <v>213.19</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,20 +759,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>7.47</v>
+        <v>11.58</v>
       </c>
       <c r="E12" t="n">
-        <v>7.47</v>
+        <v>7.18</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ONATEL BF (ONTBF)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>7.41</v>
+        <v>4.99</v>
       </c>
       <c r="E13" t="n">
-        <v>7.41</v>
+        <v>4.99</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,20 +817,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>6.67</v>
+        <v>4.68</v>
       </c>
       <c r="E14" t="n">
-        <v>6.67</v>
+        <v>3.26</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>VIVO ENERGY CI (SHEC)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4.99</v>
+        <v>4.35</v>
       </c>
       <c r="E15" t="n">
-        <v>4.99</v>
+        <v>4.35</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4.71</v>
+        <v>4.22</v>
       </c>
       <c r="E16" t="n">
-        <v>4.71</v>
+        <v>4.22</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.68</v>
+        <v>4.12</v>
       </c>
       <c r="E17" t="n">
-        <v>3.26</v>
+        <v>4.12</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4.53</v>
+        <v>3.55</v>
       </c>
       <c r="E18" t="n">
-        <v>4.53</v>
+        <v>3.55</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.4</v>
+        <v>3.46</v>
       </c>
       <c r="E19" t="n">
-        <v>4.4</v>
+        <v>-3.79</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,27 +984,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.35</v>
+        <v>2.03</v>
       </c>
       <c r="E20" t="n">
-        <v>4.35</v>
+        <v>5.45</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.85</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5</v>
+        <v>-6.53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1088,10 +1088,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.97</v>
+        <v>0.17</v>
       </c>
       <c r="E23" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.02</v>
+        <v>-1.36</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.79</v>
+        <v>-4.02</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.42</v>
+        <v>-1.68</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.42</v>
+        <v>-1.68</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.78</v>
+        <v>-2.23</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.78</v>
+        <v>-2.23</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="E27" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>BICI CI (BICC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.13</v>
+        <v>-3.78</v>
       </c>
       <c r="E28" t="n">
-        <v>6.03</v>
+        <v>-3.78</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-4.34</v>
+        <v>-3.85</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.34</v>
+        <v>-3.85</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-5.29</v>
+        <v>-4.34</v>
       </c>
       <c r="E30" t="n">
-        <v>-5.29</v>
+        <v>-4.34</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,20 +1310,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-9.26</v>
+        <v>-5.29</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.23</v>
+        <v>-5.29</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-10.16</v>
+        <v>-5.92</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.85</v>
+        <v>-5.92</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1360,6 +1360,35 @@
         </is>
       </c>
       <c r="G32" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1394,101 +1423,101 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10190.96</v>
+        <v>3849.58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4559.58</v>
+        <v>3174.07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3877.57</v>
+        <v>2936.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3289.21</v>
+        <v>2504.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2938.36</v>
+        <v>2111.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2918.48</v>
+        <v>2088.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2455.66</v>
+        <v>1567.71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2170.98</v>
+        <v>1415.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1559.04</v>
+        <v>1198.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM – COMPOSITE TOTAL RETURN     (**)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1354.84</v>
+        <v>869.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,20 +469,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - SERVICES FINANCIERS</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>735.7</v>
+        <v>722.92</v>
       </c>
       <c r="E2" t="n">
-        <v>369.06</v>
+        <v>241.02</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES FINANCIERS</t>
+          <t>BRVM - SERVICES PUBLICS</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -508,10 +508,10 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>721.66</v>
+        <v>673.39</v>
       </c>
       <c r="E3" t="n">
-        <v>240.1</v>
+        <v>234.49</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRVM - SERVICES PUBLICS</t>
+          <t>BRVM - INDUSTRIELS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,10 +537,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>659.74</v>
+        <v>628</v>
       </c>
       <c r="E4" t="n">
-        <v>218.17</v>
+        <v>202.87</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRVM - INDUSTRIELS</t>
+          <t>BRVM-PRESTIGE</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -566,10 +566,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>635.9299999999999</v>
+        <v>595.39</v>
       </c>
       <c r="E5" t="n">
-        <v>212.49</v>
+        <v>198.86</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM-PRESTIGE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -595,10 +595,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>589.36</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>199.94</v>
+        <v>180.36</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -624,10 +624,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>542.08</v>
+        <v>467.24</v>
       </c>
       <c r="E7" t="n">
-        <v>176.82</v>
+        <v>156.32</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>520.64</v>
+        <v>450.55</v>
       </c>
       <c r="E8" t="n">
-        <v>261.3</v>
+        <v>150.14</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,20 +672,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>466.47</v>
+        <v>369.06</v>
       </c>
       <c r="E9" t="n">
-        <v>155.72</v>
+        <v>369.06</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -701,20 +701,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - CONSOMMATION DE BASE     (**)</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>442.58</v>
+        <v>261.3</v>
       </c>
       <c r="E10" t="n">
-        <v>153.33</v>
+        <v>261.3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -737,10 +737,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>422.78</v>
+        <v>213.19</v>
       </c>
       <c r="E11" t="n">
         <v>213.19</v>
@@ -759,20 +759,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.58</v>
+        <v>9.51</v>
       </c>
       <c r="E12" t="n">
-        <v>7.18</v>
+        <v>7.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -781,14 +781,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>4.99</v>
+        <v>7.47</v>
       </c>
       <c r="E13" t="n">
-        <v>4.99</v>
+        <v>7.47</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,20 +817,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>BANK OF AFRICA BF (BOABF)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>4.68</v>
+        <v>5.74</v>
       </c>
       <c r="E14" t="n">
-        <v>3.26</v>
+        <v>5.74</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VIVO ENERGY CI (SHEC)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.35</v>
+        <v>5.73</v>
       </c>
       <c r="E15" t="n">
-        <v>4.35</v>
+        <v>-5.85</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -868,14 +868,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>4.22</v>
+        <v>4.99</v>
       </c>
       <c r="E16" t="n">
-        <v>4.22</v>
+        <v>4.99</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="E18" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.46</v>
+        <v>3.55</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.79</v>
+        <v>3.55</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
@@ -1020,20 +1020,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOLIBRA CI (SLBC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.21</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>1.21</v>
+        <v>-6.53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,14 +1042,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.53</v>
+        <v>4.17</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1088,10 +1088,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.17</v>
+        <v>-1.11</v>
       </c>
       <c r="E23" t="n">
-        <v>4.17</v>
+        <v>4.81</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,20 +1107,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.36</v>
+        <v>-1.68</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.02</v>
+        <v>-1.68</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.68</v>
+        <v>-2.23</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.68</v>
+        <v>-2.23</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.23</v>
+        <v>-3.79</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.23</v>
+        <v>-3.79</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.5</v>
+        <v>-3.9</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.5</v>
+        <v>-3.9</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BICI CI (BICC)</t>
+          <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.78</v>
+        <v>-4.24</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.78</v>
+        <v>-7.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-3.85</v>
+        <v>-4.34</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.85</v>
+        <v>-4.34</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-4.34</v>
+        <v>-5.03</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.34</v>
+        <v>-5.03</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ERIUM CI (Ex AIR LIQUIDE CI) (SIVC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-5.29</v>
+        <v>-6.33</v>
       </c>
       <c r="E31" t="n">
-        <v>-5.29</v>
+        <v>-6.33</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1349,10 +1349,10 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-5.92</v>
+        <v>-7.49</v>
       </c>
       <c r="E32" t="n">
-        <v>-5.92</v>
+        <v>-7.49</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1360,35 +1360,6 @@
         </is>
       </c>
       <c r="G32" t="inlineStr">
-        <is>
-          <t>➖ Neutre</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-7.49</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-7.49</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1427,7 +1398,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3849.58</v>
+        <v>3864.23</v>
       </c>
     </row>
     <row r="3">
@@ -1437,7 +1408,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3174.07</v>
+        <v>3313.36</v>
       </c>
     </row>
     <row r="4">
@@ -1447,7 +1418,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2936.42</v>
+        <v>2858.95</v>
       </c>
     </row>
     <row r="5">
@@ -1457,7 +1428,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2504.99</v>
+        <v>2558.63</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1438,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2111.23</v>
+        <v>2090.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2088.82</v>
+        <v>1572.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1567.71</v>
+        <v>1465.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1415.81</v>
+        <v>369.06</v>
       </c>
     </row>
     <row r="10">
@@ -1507,7 +1478,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1198.3</v>
+        <v>261.3</v>
       </c>
     </row>
     <row r="11">
@@ -1517,7 +1488,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>869.6</v>
+        <v>213.19</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,13 +476,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>722.92</v>
+        <v>964.42</v>
       </c>
       <c r="E2" t="n">
-        <v>241.02</v>
+        <v>241.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>673.39</v>
+        <v>902.0700000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>234.49</v>
+        <v>228.68</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -534,13 +534,13 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>628</v>
+        <v>837.76</v>
       </c>
       <c r="E4" t="n">
-        <v>202.87</v>
+        <v>209.76</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -563,13 +563,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>595.39</v>
+        <v>792.01</v>
       </c>
       <c r="E5" t="n">
-        <v>198.86</v>
+        <v>196.62</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,20 +585,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>539.4400000000001</v>
+        <v>737.3200000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>180.36</v>
+        <v>368.26</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,20 +614,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>467.24</v>
+        <v>719.92</v>
       </c>
       <c r="E7" t="n">
-        <v>156.32</v>
+        <v>180.48</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>450.55</v>
+        <v>623.97</v>
       </c>
       <c r="E8" t="n">
-        <v>150.14</v>
+        <v>156.73</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,20 +672,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>369.06</v>
+        <v>597.8200000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>369.06</v>
+        <v>147.27</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>261.3</v>
+        <v>517.99</v>
       </c>
       <c r="E10" t="n">
-        <v>261.3</v>
+        <v>256.69</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>213.19</v>
+        <v>426.11</v>
       </c>
       <c r="E11" t="n">
-        <v>213.19</v>
+        <v>212.92</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -798,10 +798,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>7.47</v>
+        <v>6.67</v>
       </c>
       <c r="E13" t="n">
-        <v>7.47</v>
+        <v>6.67</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
+          <t>BANK OF AFRICA CI (BOAC)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>5.74</v>
+        <v>5.76</v>
       </c>
       <c r="E14" t="n">
-        <v>5.74</v>
+        <v>5.76</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,20 +846,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>BANK OF AFRICA BF (BOABF)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>5.73</v>
+        <v>5.74</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.85</v>
+        <v>5.74</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -868,27 +868,27 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.99</v>
+        <v>5.02</v>
       </c>
       <c r="E16" t="n">
-        <v>4.99</v>
+        <v>7.25</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -897,14 +897,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>SAPH CI (SPHC)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.12</v>
+        <v>4.99</v>
       </c>
       <c r="E17" t="n">
-        <v>4.12</v>
+        <v>4.99</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,20 +933,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.95</v>
+        <v>4.61</v>
       </c>
       <c r="E18" t="n">
-        <v>3.95</v>
+        <v>-2.86</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -955,14 +955,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.55</v>
+        <v>4.12</v>
       </c>
       <c r="E19" t="n">
-        <v>3.55</v>
+        <v>4.12</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,20 +991,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2.03</v>
+        <v>3.55</v>
       </c>
       <c r="E20" t="n">
-        <v>5.45</v>
+        <v>3.55</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,14 +1013,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.03</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.53</v>
+        <v>5.45</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.17</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>4.17</v>
+        <v>-6.53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.11</v>
+        <v>0.65</v>
       </c>
       <c r="E23" t="n">
-        <v>4.81</v>
+        <v>-5.08</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,20 +1107,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.68</v>
+        <v>0.45</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.68</v>
+        <v>4.35</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.23</v>
+        <v>0.17</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.23</v>
+        <v>4.17</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1158,27 +1158,27 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.79</v>
+        <v>-0.99</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.79</v>
+        <v>5.34</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1187,27 +1187,27 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.9</v>
+        <v>-1.05</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.9</v>
+        <v>-5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1216,14 +1216,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1233,10 +1233,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.24</v>
+        <v>-1.11</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.5</v>
+        <v>4.81</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-4.34</v>
+        <v>-1.68</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.34</v>
+        <v>-1.68</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>UNIWAX CI (UNXC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-5.03</v>
+        <v>-2.91</v>
       </c>
       <c r="E30" t="n">
-        <v>-5.03</v>
+        <v>-2.91</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-6.33</v>
+        <v>-3.79</v>
       </c>
       <c r="E31" t="n">
-        <v>-6.33</v>
+        <v>-3.79</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,27 +1339,114 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>SUCRIVOIRE (SCRC)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>👀 À surveiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SETAO CI (STAC)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-5.03</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-5.03</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
         <v>-7.49</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E34" t="n">
         <v>-7.49</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NESTLE CI (NTLC)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-7.92</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1398,7 +1485,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3864.23</v>
+        <v>13437.84</v>
       </c>
     </row>
     <row r="3">
@@ -1408,7 +1495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3313.36</v>
+        <v>11119.03</v>
       </c>
     </row>
     <row r="4">
@@ -1418,7 +1505,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2858.95</v>
+        <v>9065.629999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1428,7 +1515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2558.63</v>
+        <v>7786.04</v>
       </c>
     </row>
     <row r="6">
@@ -1438,7 +1525,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2090.6</v>
+        <v>6044.19</v>
       </c>
     </row>
     <row r="7">
@@ -1448,7 +1535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1572.74</v>
+        <v>4194.42</v>
       </c>
     </row>
     <row r="8">
@@ -1458,7 +1545,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1465.7</v>
+        <v>3771.5</v>
       </c>
     </row>
     <row r="9">
@@ -1468,7 +1555,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>369.06</v>
+        <v>2096.42</v>
       </c>
     </row>
     <row r="10">
@@ -1478,7 +1565,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>261.3</v>
+        <v>1188.72</v>
       </c>
     </row>
     <row r="11">
@@ -1488,7 +1575,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>213.19</v>
+        <v>880.03</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,10 +479,10 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>964.42</v>
+        <v>966.3200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>241.5</v>
+        <v>243.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>902.0700000000001</v>
+        <v>920.71</v>
       </c>
       <c r="E3" t="n">
-        <v>228.68</v>
+        <v>239.37</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>837.76</v>
+        <v>833.9</v>
       </c>
       <c r="E4" t="n">
-        <v>209.76</v>
+        <v>208.78</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>792.01</v>
+        <v>791.35</v>
       </c>
       <c r="E5" t="n">
-        <v>196.62</v>
+        <v>195.93</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>737.3200000000001</v>
+        <v>740.05</v>
       </c>
       <c r="E6" t="n">
-        <v>368.26</v>
+        <v>371.79</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>719.92</v>
+        <v>719.14</v>
       </c>
       <c r="E7" t="n">
-        <v>180.48</v>
+        <v>181.48</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>623.97</v>
+        <v>626.02</v>
       </c>
       <c r="E8" t="n">
-        <v>156.73</v>
+        <v>157.25</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>597.8200000000001</v>
+        <v>595.6</v>
       </c>
       <c r="E9" t="n">
-        <v>147.27</v>
+        <v>144.86</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>517.99</v>
+        <v>515.33</v>
       </c>
       <c r="E10" t="n">
-        <v>256.69</v>
+        <v>258.64</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>426.11</v>
+        <v>425.8</v>
       </c>
       <c r="E11" t="n">
-        <v>212.92</v>
+        <v>212.88</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -759,20 +759,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>BERNABE CI (BNBC)</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>9.51</v>
+        <v>14.55</v>
       </c>
       <c r="E12" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -781,27 +781,27 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NEI-CEDA CI (NEIC)</t>
+          <t>CIE CI (CIEC)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.67</v>
+        <v>10.49</v>
       </c>
       <c r="E13" t="n">
-        <v>6.67</v>
+        <v>5.88</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -810,27 +810,27 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA CI (BOAC)</t>
+          <t>BANK OF AFRICA NG (BOAN)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>5.76</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>5.76</v>
+        <v>4.02</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
+          <t>NEI-CEDA CI (NEIC)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -856,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>5.74</v>
+        <v>6.67</v>
       </c>
       <c r="E15" t="n">
-        <v>5.74</v>
+        <v>6.67</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,20 +875,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BERNABE CI (BNBC)</t>
+          <t>BANK OF AFRICA CI (BOAC)</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5.02</v>
+        <v>5.76</v>
       </c>
       <c r="E16" t="n">
-        <v>7.25</v>
+        <v>5.76</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -897,14 +897,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAPH CI (SPHC)</t>
+          <t>BANK OF AFRICA BF (BOABF)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.99</v>
+        <v>5.74</v>
       </c>
       <c r="E17" t="n">
-        <v>4.99</v>
+        <v>5.74</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,20 +933,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CIE CI (CIEC)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4.61</v>
+        <v>5.45</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.86</v>
+        <v>5.45</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -955,14 +955,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA NG (BOAN)</t>
+          <t>ECOBANK TRANS. INCORP. TG (ETIT)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.12</v>
+        <v>4.92</v>
       </c>
       <c r="E19" t="n">
-        <v>4.12</v>
+        <v>4.92</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1001,10 +1001,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="E20" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1020,20 +1020,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2.03</v>
+        <v>3.55</v>
       </c>
       <c r="E21" t="n">
-        <v>5.45</v>
+        <v>3.55</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1042,14 +1042,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1059,10 +1059,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.53</v>
+        <v>7.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1078,20 +1078,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>UNIWAX CI (UNXC)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.65</v>
+        <v>2.09</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.08</v>
+        <v>5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.17</v>
+        <v>-0.99</v>
       </c>
       <c r="E25" t="n">
-        <v>4.17</v>
+        <v>5.34</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1175,10 +1175,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.99</v>
+        <v>-1.05</v>
       </c>
       <c r="E26" t="n">
-        <v>5.34</v>
+        <v>-5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1204,10 +1204,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.05</v>
+        <v>-1.11</v>
       </c>
       <c r="E27" t="n">
-        <v>-5</v>
+        <v>4.81</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.11</v>
+        <v>-1.68</v>
       </c>
       <c r="E28" t="n">
-        <v>4.81</v>
+        <v>-1.68</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1262,10 +1262,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.68</v>
+        <v>-2.33</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.68</v>
+        <v>-2.33</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UNIWAX CI (UNXC)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.91</v>
+        <v>-2.34</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.91</v>
+        <v>-2.34</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TOTALENERGIES MARKETING SN (TTLS)</t>
+          <t>NESTLE CI (NTLC)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1320,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.79</v>
+        <v>-3.58</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.79</v>
+        <v>-3.58</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1339,20 +1339,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SUCRIVOIRE (SCRC)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>-4.24</v>
+        <v>-3.75</v>
       </c>
       <c r="E32" t="n">
-        <v>-7.5</v>
+        <v>-5.08</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-5.03</v>
+        <v>-6.53</v>
       </c>
       <c r="E33" t="n">
-        <v>-5.03</v>
+        <v>-6.53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,20 +1397,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>SETAO CI (STAC)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>-7.49</v>
+        <v>-7.54</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.49</v>
+        <v>-2.51</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1436,10 +1436,10 @@
         <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>-7.92</v>
+        <v>-9.33</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.58</v>
+        <v>-1.84</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1447,6 +1447,35 @@
         </is>
       </c>
       <c r="G35" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SUCRIVOIRE (SCRC)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-10.12</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1485,7 +1514,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13437.84</v>
+        <v>13513.09</v>
       </c>
     </row>
     <row r="3">
@@ -1495,7 +1524,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11119.03</v>
+        <v>11771.05</v>
       </c>
     </row>
     <row r="4">
@@ -1505,7 +1534,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9065.629999999999</v>
+        <v>8952.469999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1515,7 +1544,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7786.04</v>
+        <v>7768.49</v>
       </c>
     </row>
     <row r="6">
@@ -1525,7 +1554,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6044.19</v>
+        <v>6027.21</v>
       </c>
     </row>
     <row r="7">
@@ -1535,7 +1564,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4194.42</v>
+        <v>4228.92</v>
       </c>
     </row>
     <row r="8">
@@ -1545,7 +1574,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3771.5</v>
+        <v>3736.71</v>
       </c>
     </row>
     <row r="9">
@@ -1555,7 +1584,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2096.42</v>
+        <v>2109.2</v>
       </c>
     </row>
     <row r="10">
@@ -1565,7 +1594,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1188.72</v>
+        <v>1179.23</v>
       </c>
     </row>
     <row r="11">
@@ -1575,7 +1604,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>880.03</v>
+        <v>879.0599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/recommandations.xlsx
+++ b/data/recommandations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,13 +476,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>966.3200000000001</v>
+        <v>1208.29</v>
       </c>
       <c r="E2" t="n">
-        <v>243.7</v>
+        <v>241.97</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -505,13 +505,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>920.71</v>
+        <v>1164.07</v>
       </c>
       <c r="E3" t="n">
-        <v>239.37</v>
+        <v>243.36</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -534,13 +534,13 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>833.9</v>
+        <v>1046.8</v>
       </c>
       <c r="E4" t="n">
-        <v>208.78</v>
+        <v>212.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -563,13 +563,13 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>791.35</v>
+        <v>989.67</v>
       </c>
       <c r="E5" t="n">
-        <v>195.93</v>
+        <v>198.32</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -585,20 +585,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRVM-PRINCIPAL     (**)</t>
+          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>740.05</v>
+        <v>900.85</v>
       </c>
       <c r="E6" t="n">
-        <v>371.79</v>
+        <v>181.71</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -614,20 +614,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRVM - CONSOMMATION DISCRETIONNAIRE</t>
+          <t>BRVM - ENERGIE</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>719.14</v>
+        <v>784.61</v>
       </c>
       <c r="E7" t="n">
-        <v>181.48</v>
+        <v>158.59</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -643,20 +643,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRVM - ENERGIE</t>
+          <t>BRVM - TELECOMMUNICATIONS</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>626.02</v>
+        <v>745.17</v>
       </c>
       <c r="E8" t="n">
-        <v>157.25</v>
+        <v>149.57</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -672,20 +672,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRVM - TELECOMMUNICATIONS</t>
+          <t>BRVM-PRINCIPAL     (**)</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>595.6</v>
+        <v>740.05</v>
       </c>
       <c r="E9" t="n">
-        <v>144.86</v>
+        <v>371.79</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA CI (BOAC)</t>
+          <t>BANK OF AFRICA BF (BOABF)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -885,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>5.76</v>
+        <v>5.74</v>
       </c>
       <c r="E16" t="n">
-        <v>5.76</v>
+        <v>5.74</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA BF (BOABF)</t>
+          <t>BANK OF AFRICA ML (BOAM)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.74</v>
+        <v>5.45</v>
       </c>
       <c r="E17" t="n">
-        <v>5.74</v>
+        <v>5.45</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BANK OF AFRICA ML (BOAM)</t>
+          <t>SERVAIR ABIDJAN CI (ABJC)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5.45</v>
+        <v>3.55</v>
       </c>
       <c r="E18" t="n">
-        <v>5.45</v>
+        <v>3.55</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -962,20 +962,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ECOBANK TRANS. INCORP. TG (ETIT)</t>
+          <t>SODE CI (SDCC)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.92</v>
+        <v>3.48</v>
       </c>
       <c r="E19" t="n">
-        <v>4.92</v>
+        <v>7.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -984,27 +984,27 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PALM CI (PALC)</t>
+          <t>ECOBANK TRANS. INCORP. TG (ETIT)</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.17</v>
+        <v>3.36</v>
       </c>
       <c r="E20" t="n">
-        <v>4.17</v>
+        <v>-1.56</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1013,14 +1013,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SERVAIR ABIDJAN CI (ABJC)</t>
+          <t>SOLIBRA CI (SLBC)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="E21" t="n">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1049,20 +1049,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SODE CI (SDCC)</t>
+          <t>TOTALENERGIES MARKETING CI (TTLC)</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3.48</v>
+        <v>2.48</v>
       </c>
       <c r="E22" t="n">
-        <v>7.5</v>
+        <v>2.48</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1071,14 +1071,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UNIWAX CI (UNXC)</t>
+          <t>BANK OF AFRICA CI (BOAC)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1088,10 +1088,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>-3.31</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FILTISAC CI (FTSC)</t>
+          <t>PALM CI (PALC)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1117,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.45</v>
+        <v>2.3</v>
       </c>
       <c r="E24" t="n">
-        <v>4.35</v>
+        <v>-1.87</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
+          <t>UNIWAX CI (UNXC)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1146,10 +1146,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.99</v>
+        <v>2.09</v>
       </c>
       <c r="E25" t="n">
-        <v>5.34</v>
+        <v>5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1165,20 +1165,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SOGB CI (SOGC)</t>
+          <t>AFRICA GLOBAL LOGISTICS CI (SDSC)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.05</v>
+        <v>1.88</v>
       </c>
       <c r="E26" t="n">
-        <v>-5</v>
+        <v>2.87</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1194,20 +1194,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CFAO MOTORS CI (CFAC)</t>
+          <t>SONATEL SN (SNTS)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.11</v>
+        <v>1.07</v>
       </c>
       <c r="E27" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1223,20 +1223,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SAFCA CI (SAFC)</t>
+          <t>FILTISAC CI (FTSC)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.68</v>
+        <v>0.45</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.68</v>
+        <v>4.35</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1245,27 +1245,27 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
+          <t>UNILEVER CI (UNLC)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.33</v>
+        <v>-0.01</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.33</v>
+        <v>6.52</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1274,27 +1274,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SICABLE CI (CABC)</t>
+          <t>SOGB CI (SOGC)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.34</v>
+        <v>-1.05</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.34</v>
+        <v>-5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1303,27 +1303,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NESTLE CI (NTLC)</t>
+          <t>CFAO MOTORS CI (CFAC)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.58</v>
+        <v>-1.11</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.58</v>
+        <v>4.81</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>➖ Neutre</t>
+          <t>👀 À surveiller</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SONATEL SN (SNTS)</t>
+          <t>SAFCA CI (SAFC)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>-3.75</v>
+        <v>-1.68</v>
       </c>
       <c r="E32" t="n">
-        <v>-5.08</v>
+        <v>-1.68</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1361,14 +1361,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>👀 À surveiller</t>
+          <t>➖ Neutre</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UNILEVER CI (UNLC)</t>
+          <t>SOCIETE GENERALE COTE D'IVOIRE (SGBC)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1378,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-6.53</v>
+        <v>-1.93</v>
       </c>
       <c r="E33" t="n">
-        <v>-6.53</v>
+        <v>-1.93</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,20 +1397,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SETAO CI (STAC)</t>
+          <t>ORANGE COTE D'IVOIRE (ORAC)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-7.54</v>
+        <v>-2.33</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.51</v>
+        <v>-2.33</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1426,20 +1426,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+          <t>SICABLE CI (CABC)</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-9.33</v>
+        <v>-2.34</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.84</v>
+        <v>-2.34</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,27 +1455,143 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>TRACTAFRIC MOTORS CI (PRSC)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NESTLE CI (NTLC)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SETAO CI (STAC)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-7.54</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NSIA BANQUE COTE D'IVOIRE (NSBC)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-9.33</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>➖ Neutre</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>SUCRIVOIRE (SCRC)</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
         <v>2</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D40" t="n">
         <v>-10.12</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E40" t="n">
         <v>-2.62</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>🟡 Observer</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>🟡 Observer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>➖ Neutre</t>
         </is>
@@ -1514,7 +1630,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13513.09</v>
+        <v>46452.68</v>
       </c>
     </row>
     <row r="3">
@@ -1524,7 +1640,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11771.05</v>
+        <v>40660.43</v>
       </c>
     </row>
     <row r="4">
@@ -1534,7 +1650,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8952.469999999999</v>
+        <v>28225.16</v>
       </c>
     </row>
     <row r="5">
@@ -1544,7 +1660,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7768.49</v>
+        <v>23373.29</v>
       </c>
     </row>
     <row r="6">
@@ -1554,7 +1670,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6027.21</v>
+        <v>17160.97</v>
       </c>
     </row>
     <row r="7">
@@ -1564,7 +1680,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4228.92</v>
+        <v>11094.14</v>
       </c>
     </row>
     <row r="8">
@@ -1574,7 +1690,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3736.71</v>
+        <v>9475.280000000001</v>
       </c>
     </row>
     <row r="9">
